--- a/InputData/acronym-key.xlsx
+++ b/InputData/acronym-key.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7237423-EA6D-4B30-87A8-5E17635AFF40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{689CA091-282C-434F-9EC8-B18750BFFC58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1399" uniqueCount="811">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1436" uniqueCount="833">
   <si>
     <t>Top Level Folder</t>
   </si>
@@ -1375,9 +1375,6 @@
     <t>Quantization Size for Pollutants</t>
   </si>
   <si>
-    <t>BAU Imported Electricity, BAU Exported Electricity, Imported Electricity Price, BAU Exported Electricity Price</t>
-  </si>
-  <si>
     <t>EVCC</t>
   </si>
   <si>
@@ -2014,12 +2011,6 @@
     <t>BAU Zero Emis Credit for Nuc Plants</t>
   </si>
   <si>
-    <t>EDWP</t>
-  </si>
-  <si>
-    <t>Electricity Dispatch Weibull Parameters</t>
-  </si>
-  <si>
     <t>MLfPPR</t>
   </si>
   <si>
@@ -2101,12 +2092,6 @@
     <t>CCS Transportation and Storage Cost</t>
   </si>
   <si>
-    <t>BSpUESttGbGB</t>
-  </si>
-  <si>
-    <t>BAU Subsidy per Unit Electricity Supplied to the Grid by Grid Batteries</t>
-  </si>
-  <si>
     <t>BPSpUGBCD</t>
   </si>
   <si>
@@ -2230,9 +2215,6 @@
     <t>Capacity Supply Curve</t>
   </si>
   <si>
-    <t>Electricity Dispatch Weibull Parameter A, Electricity Dispatch Weibull Parameter B</t>
-  </si>
-  <si>
     <t>GBCGpUNR</t>
   </si>
   <si>
@@ -2380,15 +2362,6 @@
     <t>STfECCE</t>
   </si>
   <si>
-    <t>BUCMfNCR</t>
-  </si>
-  <si>
-    <t>Boolean Use Capacity Market for New Capacity Revenue</t>
-  </si>
-  <si>
-    <t>You wish the electricity sector to only collect capacity costs for new capacity and not pay them out to all resources in the market.</t>
-  </si>
-  <si>
     <t>FoICbCTBA</t>
   </si>
   <si>
@@ -2416,12 +2389,6 @@
     <t>Cap Ret per Unit Net Loss</t>
   </si>
   <si>
-    <t>ESUfRaLCD</t>
-  </si>
-  <si>
-    <t>Elec Sources Used for Rlbty and Lst Cst Dsptch</t>
-  </si>
-  <si>
     <t>BFoICbCTBA</t>
   </si>
   <si>
@@ -2465,6 +2432,105 @@
   </si>
   <si>
     <t>do not edit - QC file to automatically check specified files</t>
+  </si>
+  <si>
+    <t>CiDESCTY</t>
+  </si>
+  <si>
+    <t>Change in Distributed Electricity Source Capacity This Year</t>
+  </si>
+  <si>
+    <t>You plan on using a policy mandated change in distributed solar capacity additions</t>
+  </si>
+  <si>
+    <t>NBICP</t>
+  </si>
+  <si>
+    <t>Non BAU Industry CCS Parameters</t>
+  </si>
+  <si>
+    <t>Fraction of CCS Potential Achieved by Industry Energy, Fraction of CCS Potential Achieved by Industry Process, CCS Subsidies</t>
+  </si>
+  <si>
+    <t>You wish to use a policy lever to testalternate CCS subsidies for industries</t>
+  </si>
+  <si>
+    <t>NBRHPF</t>
+  </si>
+  <si>
+    <t>Non BAU Recipient Hydrogen Pathway Fractions</t>
+  </si>
+  <si>
+    <t>You wish for the non BAU hydrogen pathway shifting policy to shift hydrogen production to a pathway other than electrolysis</t>
+  </si>
+  <si>
+    <t>PEAAC</t>
+  </si>
+  <si>
+    <t>Process Emissions Additions and Costs</t>
+  </si>
+  <si>
+    <t>Process Emissions Additions and Costs, Marginal Cost Definitions</t>
+  </si>
+  <si>
+    <t>You want to test the addition rather than the reduction of process emissions for select industries</t>
+  </si>
+  <si>
+    <t>BRZSPbMR</t>
+  </si>
+  <si>
+    <t>BAU Required ZEV Sales Perc by Model Region</t>
+  </si>
+  <si>
+    <t>TACFMfPBTY</t>
+  </si>
+  <si>
+    <t>Time Adjusted Capacity Factor Multiplier for Plants Built This Year</t>
+  </si>
+  <si>
+    <t>FoGBPD</t>
+  </si>
+  <si>
+    <t>Fraction of Grid Batteries Produced Domestically</t>
+  </si>
+  <si>
+    <t>BSfGBP</t>
+  </si>
+  <si>
+    <t>BAU Subsidy for Grid Battery Production</t>
+  </si>
+  <si>
+    <t>BEEEfEPS</t>
+  </si>
+  <si>
+    <t>Boolean Exclude Electricity Exports from Elec Portfolio Stds</t>
+  </si>
+  <si>
+    <t>You wish to change the default behavior or whether electricity exports are included or excluded in RPS and CES policies.</t>
+  </si>
+  <si>
+    <t>MV</t>
+  </si>
+  <si>
+    <t>Modeled Vintages</t>
+  </si>
+  <si>
+    <t>You are using a different model start year than the US EPS (this file should note which vintages are for historical years rather than modeled years)</t>
+  </si>
+  <si>
+    <t>BAU Imported Electricity, BAU Exported Electricity, Imported Electricity Price</t>
+  </si>
+  <si>
+    <t>BPM</t>
+  </si>
+  <si>
+    <t>Battery Pack Markup</t>
+  </si>
+  <si>
+    <t>BPPM</t>
+  </si>
+  <si>
+    <t>Battery Pack Price Multiplier</t>
   </si>
 </sst>
 </file>
@@ -2946,82 +3012,82 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C70"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" customWidth="1"/>
+    <col min="1" max="1" width="10.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="8" t="s">
         <v>99</v>
       </c>
@@ -3029,32 +3095,32 @@
         <v>124</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B26" s="13" t="s">
         <v>250</v>
       </c>
@@ -3062,17 +3128,17 @@
         <v>253</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C27" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C28" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="10" t="s">
         <v>101</v>
       </c>
@@ -3080,42 +3146,42 @@
         <v>126</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B31" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B32" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B33" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B34" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B35" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B36" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B37" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" s="9" t="s">
         <v>100</v>
       </c>
@@ -3123,84 +3189,84 @@
         <v>134</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B40" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B41" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B42" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B43" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B44" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B45" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B46" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" s="15" t="s">
         <v>258</v>
       </c>
       <c r="B48" s="15"/>
       <c r="C48" s="15"/>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B49" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B50" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B51" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B52" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B53" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B54" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B55" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" s="11" t="s">
         <v>142</v>
       </c>
@@ -3208,62 +3274,62 @@
         <v>143</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B58" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B59" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B60" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" s="7" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>152</v>
       </c>
@@ -3276,20 +3342,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G294"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G302"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.5703125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.7109375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="49.140625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="17.54296875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.7265625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="49.1796875" style="2" customWidth="1"/>
     <col min="4" max="4" width="67" style="2" customWidth="1"/>
-    <col min="5" max="5" width="18.85546875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="37.5703125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="18.81640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="37.54296875" style="2" customWidth="1"/>
     <col min="7" max="7" width="54" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="8.85546875" style="2"/>
+    <col min="8" max="16384" width="8.81640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -3312,15 +3378,15 @@
         <v>318</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>538</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>539</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
@@ -3328,58 +3394,58 @@
         <v>99</v>
       </c>
       <c r="G2" s="24" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>535</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>536</v>
       </c>
       <c r="F3" s="16" t="s">
         <v>303</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>462</v>
-      </c>
       <c r="F4" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>581</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>582</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>142</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
@@ -3393,7 +3459,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="17" t="s">
         <v>4</v>
       </c>
@@ -3410,7 +3476,7 @@
       </c>
       <c r="G7" s="17"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
@@ -3424,7 +3490,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>9</v>
       </c>
@@ -3438,21 +3504,21 @@
         <v>250</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>717</v>
+        <v>712</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
@@ -3469,21 +3535,21 @@
         <v>316</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>611</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>612</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>9</v>
       </c>
@@ -3500,7 +3566,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>9</v>
       </c>
@@ -3514,4294 +3580,4423 @@
         <v>101</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>167</v>
+        <v>800</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+        <v>801</v>
+      </c>
+      <c r="F15" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>14</v>
+        <v>167</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>165</v>
+        <v>16</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>17</v>
+        <v>165</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>30</v>
+        <v>166</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>483</v>
+        <v>17</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>484</v>
+        <v>30</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>774</v>
+        <v>482</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>775</v>
+        <v>483</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>18</v>
+        <v>768</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F23" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>769</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="F24" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F25" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+      <c r="F26" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>354</v>
+        <v>22</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="F28" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>450</v>
+        <v>354</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>451</v>
+        <v>355</v>
       </c>
       <c r="F29" s="16" t="s">
         <v>303</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>450</v>
+      </c>
+      <c r="F30" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>505</v>
+        <v>454</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>455</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>243</v>
+        <v>504</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="F32" s="14" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+        <v>505</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>487</v>
+        <v>243</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+        <v>244</v>
+      </c>
+      <c r="F33" s="14" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B34" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A35" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="C34" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="E34" s="2" t="s">
+      <c r="E35" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F34" s="12" t="s">
+      <c r="F35" s="12" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="17" t="s">
+    <row r="36" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="B35" s="17" t="s">
+      <c r="B36" s="17" t="s">
+        <v>456</v>
+      </c>
+      <c r="C36" s="17" t="s">
         <v>457</v>
       </c>
-      <c r="C35" s="17" t="s">
-        <v>458</v>
-      </c>
-      <c r="D35" s="17"/>
-      <c r="E35" s="17" t="s">
+      <c r="D36" s="17"/>
+      <c r="E36" s="17" t="s">
         <v>164</v>
       </c>
-      <c r="F35" s="19" t="s">
+      <c r="F36" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="G35" s="17"/>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>616</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>617</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="G36" s="17"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>696</v>
+        <v>615</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>697</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>698</v>
-      </c>
-      <c r="F37" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+        <v>616</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>700</v>
+        <v>691</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>701</v>
-      </c>
-      <c r="F38" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="120" x14ac:dyDescent="0.25">
+        <v>692</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>37</v>
+        <v>695</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>699</v>
-      </c>
-      <c r="F39" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>696</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="116" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>409</v>
+        <v>37</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="F40" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>687</v>
+        <v>409</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>688</v>
+        <v>410</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>690</v>
       </c>
       <c r="F41" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>703</v>
+        <v>684</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>704</v>
-      </c>
-      <c r="F42" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" s="17" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="17" t="s">
+        <v>685</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A43" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B43" s="17" t="s">
-        <v>781</v>
-      </c>
-      <c r="C43" s="17" t="s">
-        <v>702</v>
-      </c>
-      <c r="F43" s="20" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B43" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>804</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="F43" s="21" t="s">
+        <v>303</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
-        <v>172</v>
+        <v>36</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>5</v>
+        <v>698</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>6</v>
+        <v>699</v>
       </c>
       <c r="F44" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" s="17" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A45" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="B45" s="17" t="s">
+        <v>775</v>
+      </c>
+      <c r="C45" s="17" t="s">
+        <v>697</v>
+      </c>
+      <c r="F45" s="20" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A46" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="B45" s="17" t="s">
+      <c r="B46" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A47" s="17" t="s">
+        <v>172</v>
+      </c>
+      <c r="B47" s="17" t="s">
         <v>439</v>
       </c>
-      <c r="C45" s="17" t="s">
+      <c r="C47" s="17" t="s">
         <v>440</v>
       </c>
-      <c r="D45" s="17"/>
-      <c r="E45" s="17"/>
-      <c r="F45" s="22" t="s">
+      <c r="D47" s="17"/>
+      <c r="E47" s="17"/>
+      <c r="F47" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="G45" s="17" t="s">
+      <c r="G47" s="17" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="17" t="s">
-        <v>485</v>
-      </c>
-      <c r="B46" s="17" t="s">
+    <row r="48" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A48" s="17" t="s">
+        <v>484</v>
+      </c>
+      <c r="B48" s="17" t="s">
         <v>445</v>
       </c>
-      <c r="C46" s="17" t="s">
+      <c r="C48" s="17" t="s">
         <v>446</v>
       </c>
-      <c r="D46" s="17"/>
-      <c r="E46" s="17"/>
-      <c r="F46" s="22" t="s">
+      <c r="D48" s="17"/>
+      <c r="E48" s="17"/>
+      <c r="F48" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="G46" s="17" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A47" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="F47" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>556</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="F48" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="G48" s="17" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
         <v>413</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>436</v>
+        <v>324</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>437</v>
+        <v>325</v>
       </c>
       <c r="F49" s="6" t="s">
         <v>180</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
         <v>413</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>342</v>
+        <v>555</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>343</v>
+        <v>556</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>180</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
         <v>413</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>251</v>
+        <v>436</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>252</v>
+        <v>437</v>
       </c>
       <c r="F51" s="6" t="s">
         <v>180</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
         <v>413</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>720</v>
+        <v>822</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>721</v>
+        <v>823</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>180</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
         <v>413</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>509</v>
+        <v>342</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>510</v>
+        <v>343</v>
       </c>
       <c r="F53" s="6" t="s">
         <v>180</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
         <v>413</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>180</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
         <v>413</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>571</v>
+        <v>715</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>572</v>
+        <v>716</v>
       </c>
       <c r="F55" s="6" t="s">
         <v>180</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
         <v>413</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>782</v>
+        <v>508</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>783</v>
+        <v>509</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>180</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
         <v>413</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>178</v>
+        <v>266</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>179</v>
+        <v>267</v>
       </c>
       <c r="F57" s="6" t="s">
         <v>180</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
         <v>413</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>578</v>
+        <v>571</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>180</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
         <v>413</v>
       </c>
       <c r="B59" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="F59" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A60" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A61" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="B61" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="C61" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="F59" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="17" t="s">
+      <c r="F61" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A62" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="B60" s="17" t="s">
+      <c r="B62" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="C62" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="C60" s="17" t="s">
+      <c r="D62" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="F62" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="G62" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D60" s="17" t="s">
-        <v>723</v>
-      </c>
-      <c r="E60" s="17"/>
-      <c r="F60" s="22" t="s">
-        <v>180</v>
-      </c>
-      <c r="G60" s="17" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F63" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="63" spans="1:7" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A63" s="17" t="s">
+        <v>413</v>
+      </c>
+      <c r="B63" s="17" t="s">
+        <v>825</v>
+      </c>
+      <c r="C63" s="17" t="s">
+        <v>826</v>
+      </c>
+      <c r="D63" s="17"/>
+      <c r="E63" s="17"/>
+      <c r="F63" s="21" t="s">
+        <v>303</v>
+      </c>
+      <c r="G63" s="17" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
         <v>38</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>545</v>
+        <v>39</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="F64" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A65" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B65" s="17" t="s">
-        <v>385</v>
-      </c>
-      <c r="C65" s="17" t="s">
-        <v>386</v>
-      </c>
-      <c r="D65" s="17"/>
-      <c r="E65" s="17"/>
-      <c r="F65" s="21" t="s">
-        <v>303</v>
-      </c>
-      <c r="G65" s="17" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B65" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>788</v>
+        <v>40</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>790</v>
+        <v>42</v>
       </c>
       <c r="F66" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>789</v>
+        <v>544</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>791</v>
+        <v>545</v>
       </c>
       <c r="F67" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A68" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>655</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>657</v>
-      </c>
-      <c r="F68" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A68" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B68" s="17" t="s">
+        <v>385</v>
+      </c>
+      <c r="C68" s="17" t="s">
+        <v>386</v>
+      </c>
+      <c r="D68" s="17"/>
+      <c r="E68" s="17"/>
+      <c r="F68" s="21" t="s">
+        <v>303</v>
+      </c>
+      <c r="G68" s="17" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>181</v>
+        <v>779</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>724</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>725</v>
+        <v>781</v>
       </c>
       <c r="F69" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>328</v>
+        <v>780</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="F70" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>782</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A71" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>603</v>
+        <v>654</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>602</v>
+        <v>655</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>656</v>
       </c>
       <c r="F71" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>684</v>
+        <v>181</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>685</v>
+        <v>719</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>686</v>
+        <v>720</v>
       </c>
       <c r="F72" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>175</v>
+        <v>328</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="F73" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G73" s="2" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+        <v>329</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>594</v>
+        <v>602</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>595</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>726</v>
-      </c>
-      <c r="F74" s="12" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+        <v>601</v>
+      </c>
+      <c r="F74" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>44</v>
+        <v>681</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F75" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+        <v>682</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>45</v>
+        <v>175</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>51</v>
+        <v>174</v>
       </c>
       <c r="F76" s="16" t="s">
         <v>303</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>754</v>
+        <v>593</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>755</v>
-      </c>
-      <c r="F77" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G77" s="2" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+        <v>594</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="F77" s="12" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>776</v>
+        <v>44</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>777</v>
-      </c>
-      <c r="F78" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>691</v>
+        <v>45</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>692</v>
-      </c>
-      <c r="F79" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+      <c r="F79" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>674</v>
+        <v>748</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>675</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>676</v>
-      </c>
-      <c r="E80" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="F80" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>749</v>
+      </c>
+      <c r="F80" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>689</v>
+        <v>770</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>690</v>
-      </c>
-      <c r="F81" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+        <v>771</v>
+      </c>
+      <c r="F81" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>160</v>
+        <v>686</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>161</v>
+        <v>687</v>
       </c>
       <c r="F82" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>658</v>
+        <v>671</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>659</v>
-      </c>
-      <c r="F83" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+        <v>672</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>46</v>
+        <v>820</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>727</v>
-      </c>
-      <c r="F84" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>821</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>728</v>
+        <v>160</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>729</v>
-      </c>
-      <c r="F85" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+        <v>161</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>513</v>
+        <v>657</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="F86" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="G86" s="2" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+        <v>658</v>
+      </c>
+      <c r="F86" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>792</v>
+        <v>46</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>793</v>
+        <v>52</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>722</v>
       </c>
       <c r="F87" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="88" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>730</v>
+        <v>723</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>731</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>764</v>
+        <v>724</v>
       </c>
       <c r="F88" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="89" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>647</v>
+        <v>512</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>648</v>
-      </c>
-      <c r="F89" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+        <v>513</v>
+      </c>
+      <c r="F89" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>309</v>
+        <v>783</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="F90" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+        <v>784</v>
+      </c>
+      <c r="F90" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>743</v>
+        <v>725</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>744</v>
-      </c>
-      <c r="F91" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>726</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>758</v>
+      </c>
+      <c r="F91" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>47</v>
+        <v>646</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>705</v>
-      </c>
-      <c r="F92" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>647</v>
+      </c>
+      <c r="F92" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="F93" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="94" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>660</v>
+        <v>737</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>661</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="F94" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>738</v>
+      </c>
+      <c r="F94" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>169</v>
+        <v>47</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>447</v>
+        <v>700</v>
       </c>
       <c r="F95" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>671</v>
+        <v>288</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>672</v>
+        <v>289</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>673</v>
+        <v>290</v>
       </c>
       <c r="F96" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>794</v>
+        <v>169</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>795</v>
-      </c>
-      <c r="F97" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+        <v>170</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="F97" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>733</v>
+        <v>668</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>734</v>
-      </c>
-      <c r="F98" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>669</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="F98" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>489</v>
+        <v>818</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>706</v>
+        <v>819</v>
       </c>
       <c r="F99" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="100" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>177</v>
+        <v>727</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="F100" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="G100" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+        <v>728</v>
+      </c>
+      <c r="F100" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>768</v>
+        <v>488</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>770</v>
-      </c>
-      <c r="F101" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+        <v>489</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A102" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="B102" s="2" t="s">
-        <v>769</v>
+        <v>177</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>771</v>
-      </c>
-      <c r="F102" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>176</v>
+      </c>
+      <c r="F102" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>715</v>
+        <v>762</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>716</v>
-      </c>
-      <c r="F103" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A104" s="2" t="s">
-        <v>43</v>
-      </c>
+        <v>764</v>
+      </c>
+      <c r="F103" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B104" s="2" t="s">
-        <v>735</v>
+        <v>763</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>736</v>
-      </c>
-      <c r="F104" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>765</v>
+      </c>
+      <c r="F104" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A105" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>592</v>
+        <v>710</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>593</v>
+        <v>711</v>
       </c>
       <c r="F105" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>605</v>
+        <v>729</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>606</v>
-      </c>
-      <c r="F106" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+        <v>730</v>
+      </c>
+      <c r="F106" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A107" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>752</v>
+        <v>591</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>753</v>
-      </c>
-      <c r="F107" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+        <v>592</v>
+      </c>
+      <c r="F107" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>596</v>
+        <v>604</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>597</v>
-      </c>
-      <c r="F108" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+        <v>605</v>
+      </c>
+      <c r="F108" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>662</v>
+        <v>746</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>663</v>
-      </c>
-      <c r="F109" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+        <v>747</v>
+      </c>
+      <c r="F109" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>48</v>
+        <v>595</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F110" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+        <v>596</v>
+      </c>
+      <c r="F110" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>196</v>
+        <v>659</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>208</v>
+        <v>660</v>
       </c>
       <c r="F111" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="112" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F112" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="G112" s="2" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+      <c r="F112" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>757</v>
+        <v>196</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>758</v>
-      </c>
-      <c r="F113" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="G113" s="2" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+      <c r="F113" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>750</v>
+        <v>49</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>751</v>
-      </c>
-      <c r="D114" s="2" t="s">
-        <v>765</v>
-      </c>
-      <c r="F114" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+      <c r="F114" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G114" s="2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A115" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>669</v>
+        <v>751</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>670</v>
-      </c>
-      <c r="D115" s="2" t="s">
-        <v>737</v>
-      </c>
-      <c r="F115" s="14" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+        <v>752</v>
+      </c>
+      <c r="F115" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G115" s="2" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>186</v>
+        <v>744</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="F116" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>759</v>
+      </c>
+      <c r="F116" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A117" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>579</v>
+        <v>666</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>580</v>
-      </c>
-      <c r="F117" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>667</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="F117" s="14" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>203</v>
+        <v>186</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="D118" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="F118" s="5" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+      <c r="F118" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A119" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>681</v>
+        <v>578</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>682</v>
-      </c>
-      <c r="D119" s="2" t="s">
-        <v>683</v>
-      </c>
-      <c r="F119" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+        <v>579</v>
+      </c>
+      <c r="F119" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>600</v>
+        <v>203</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>601</v>
+        <v>204</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>604</v>
-      </c>
-      <c r="F120" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>205</v>
+      </c>
+      <c r="F120" s="5" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A121" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="B121" s="2" t="s">
-        <v>667</v>
+        <v>678</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>668</v>
-      </c>
-      <c r="F121" s="14" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+        <v>679</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>680</v>
+      </c>
+      <c r="F121" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>452</v>
+        <v>599</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>453</v>
+        <v>600</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="F122" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A123" s="2" t="s">
-        <v>43</v>
-      </c>
+        <v>603</v>
+      </c>
+      <c r="F122" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="B123" s="2" t="s">
-        <v>679</v>
+        <v>664</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>680</v>
+        <v>665</v>
       </c>
       <c r="F123" s="14" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="124" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A124" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>651</v>
+        <v>451</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>652</v>
+        <v>452</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>453</v>
       </c>
       <c r="F124" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="125" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A125" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>653</v>
+        <v>676</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>654</v>
-      </c>
-      <c r="F125" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>677</v>
+      </c>
+      <c r="F125" s="14" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A126" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>574</v>
+        <v>650</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>575</v>
+        <v>651</v>
       </c>
       <c r="F126" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A127" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="F127" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="F127" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A128" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>598</v>
+        <v>573</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="E128" s="2" t="s">
-        <v>596</v>
-      </c>
-      <c r="F128" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>574</v>
+      </c>
+      <c r="F128" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>739</v>
-      </c>
-      <c r="D129" s="2" t="s">
-        <v>740</v>
+        <v>649</v>
       </c>
       <c r="F129" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="130" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>708</v>
+        <v>597</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>709</v>
-      </c>
-      <c r="F130" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A131" s="17" t="s">
+        <v>598</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="F130" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A131" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B131" s="17" t="s">
-        <v>347</v>
-      </c>
-      <c r="C131" s="17" t="s">
-        <v>348</v>
-      </c>
-      <c r="D131" s="17" t="s">
-        <v>349</v>
-      </c>
-      <c r="E131" s="17"/>
-      <c r="F131" s="21" t="s">
-        <v>303</v>
-      </c>
-      <c r="G131" s="17" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B131" s="2" t="s">
+        <v>732</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>733</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="F131" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A132" s="2" t="s">
-        <v>275</v>
+        <v>43</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>269</v>
+        <v>816</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="D132" s="2" t="s">
-        <v>707</v>
+        <v>817</v>
       </c>
       <c r="F132" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="133" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A133" s="2" t="s">
-        <v>275</v>
+        <v>43</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>273</v>
+        <v>703</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="D133" s="2" t="s">
-        <v>631</v>
-      </c>
-      <c r="F133" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A134" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="B134" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="C134" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="F134" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>704</v>
+      </c>
+      <c r="F133" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A134" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="B134" s="17" t="s">
+        <v>347</v>
+      </c>
+      <c r="C134" s="17" t="s">
+        <v>348</v>
+      </c>
+      <c r="D134" s="17" t="s">
+        <v>349</v>
+      </c>
+      <c r="E134" s="17"/>
+      <c r="F134" s="21" t="s">
+        <v>303</v>
+      </c>
+      <c r="G134" s="17" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135" s="2" t="s">
         <v>275</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>418</v>
+        <v>269</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="F135" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+        <v>270</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="F135" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A136" s="2" t="s">
         <v>275</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>183</v>
+        <v>273</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>182</v>
+        <v>274</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>630</v>
       </c>
       <c r="F136" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="137" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137" s="2" t="s">
         <v>275</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>184</v>
+        <v>271</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>185</v>
+        <v>272</v>
       </c>
       <c r="F137" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="138" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A138" s="17" t="s">
+    <row r="138" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A138" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="B138" s="17" t="s">
+      <c r="B138" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="F138" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A139" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="F139" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A140" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="F140" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A141" s="17" t="s">
+        <v>275</v>
+      </c>
+      <c r="B141" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="C138" s="17" t="s">
+      <c r="C141" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="D138" s="17"/>
-      <c r="E138" s="17"/>
-      <c r="F138" s="20" t="s">
+      <c r="D141" s="17"/>
+      <c r="E141" s="17"/>
+      <c r="F141" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="G138" s="17"/>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A139" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B139" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="C139" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="F139" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A140" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B140" s="2" t="s">
-        <v>796</v>
-      </c>
-      <c r="C140" s="2" t="s">
-        <v>799</v>
-      </c>
-      <c r="F140" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A141" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B141" s="2" t="s">
-        <v>797</v>
-      </c>
-      <c r="C141" s="2" t="s">
-        <v>800</v>
-      </c>
-      <c r="F141" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G141" s="17"/>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>798</v>
+        <v>470</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>801</v>
-      </c>
-      <c r="F142" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+        <v>471</v>
+      </c>
+      <c r="F142" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A143" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>473</v>
+        <v>785</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="D143" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="F143" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+        <v>788</v>
+      </c>
+      <c r="F143" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>380</v>
+        <v>786</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="F144" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+        <v>789</v>
+      </c>
+      <c r="F144" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>56</v>
+        <v>787</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D145" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="F145" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+        <v>790</v>
+      </c>
+      <c r="F145" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>313</v>
+        <v>472</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="F146" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>473</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="F146" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>785</v>
+        <v>380</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>786</v>
-      </c>
-      <c r="F147" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+        <v>381</v>
+      </c>
+      <c r="F147" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A148" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>629</v>
+        <v>56</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>630</v>
-      </c>
-      <c r="F148" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="F148" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>526</v>
+        <v>313</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>803</v>
-      </c>
-      <c r="E149" s="2" t="s">
-        <v>527</v>
+        <v>314</v>
       </c>
       <c r="F149" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A150" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>802</v>
+        <v>776</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>787</v>
+        <v>777</v>
       </c>
       <c r="F150" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>543</v>
+        <v>628</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="F151" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+        <v>629</v>
+      </c>
+      <c r="F151" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>607</v>
+        <v>525</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>608</v>
-      </c>
-      <c r="F152" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="153" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>792</v>
+      </c>
+      <c r="E152" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="F152" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>57</v>
+        <v>791</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F153" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="G153" s="2" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+        <v>778</v>
+      </c>
+      <c r="F153" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A154" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>311</v>
+        <v>542</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="F154" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="155" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>543</v>
+      </c>
+      <c r="F154" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A155" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>390</v>
+        <v>606</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="F155" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G155" s="2" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="156" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>607</v>
+      </c>
+      <c r="F155" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A156" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>391</v>
+        <v>57</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="F156" s="16" t="s">
-        <v>303</v>
+        <v>60</v>
+      </c>
+      <c r="F156" s="6" t="s">
+        <v>142</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>392</v>
+        <v>311</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="F157" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G157" s="2" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+        <v>312</v>
+      </c>
+      <c r="F157" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A158" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>58</v>
+        <v>390</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D158" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F158" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="159" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+        <v>393</v>
+      </c>
+      <c r="F158" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G158" s="2" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A159" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>376</v>
+        <v>391</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="D159" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="F159" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="160" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>394</v>
+      </c>
+      <c r="F159" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G159" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A160" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B160" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="F160" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G160" s="2" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A161" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F161" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A162" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="D162" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="F162" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A163" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B163" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="C160" s="2" t="s">
+      <c r="C163" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="F160" s="3" t="s">
+      <c r="F163" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="161" spans="1:7" s="17" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A161" s="17" t="s">
+    <row r="164" spans="1:7" s="17" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A164" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="B161" s="17" t="s">
+      <c r="B164" s="17" t="s">
         <v>441</v>
       </c>
-      <c r="C161" s="17" t="s">
+      <c r="C164" s="17" t="s">
         <v>442</v>
       </c>
-      <c r="F161" s="22" t="s">
+      <c r="F164" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="G161" s="17" t="s">
+      <c r="G164" s="17" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="162" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A162" s="2" t="s">
+    <row r="165" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A165" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="B162" s="2" t="s">
+      <c r="B165" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="C162" s="2" t="s">
+      <c r="C165" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="D162" s="2" t="s">
+      <c r="D165" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="F162" s="3" t="s">
+      <c r="F165" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="163" spans="1:7" s="17" customFormat="1" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A163" s="17" t="s">
-        <v>760</v>
-      </c>
-      <c r="B163" s="17" t="s">
-        <v>761</v>
-      </c>
-      <c r="C163" s="17" t="s">
-        <v>762</v>
-      </c>
-      <c r="D163" s="17" t="s">
-        <v>763</v>
-      </c>
-      <c r="F163" s="19" t="s">
+    <row r="166" spans="1:7" s="17" customFormat="1" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A166" s="17" t="s">
+        <v>754</v>
+      </c>
+      <c r="B166" s="17" t="s">
+        <v>755</v>
+      </c>
+      <c r="C166" s="17" t="s">
+        <v>756</v>
+      </c>
+      <c r="D166" s="17" t="s">
+        <v>757</v>
+      </c>
+      <c r="F166" s="19" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A164" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="B164" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="C164" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="F164" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A165" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="B165" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="C165" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="F165" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A166" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="B166" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="C166" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="F166" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="167" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A167" s="2" t="s">
         <v>357</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="D167" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="F167" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="168" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>366</v>
+      </c>
+      <c r="F167" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168" s="2" t="s">
         <v>357</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="F168" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169" s="2" t="s">
         <v>357</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="F169" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="G169" s="2" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="170" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>368</v>
+      </c>
+      <c r="F169" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A170" s="2" t="s">
         <v>357</v>
       </c>
       <c r="B170" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="C170" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="D170" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="F170" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A171" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C171" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="F171" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A172" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="C172" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="F172" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G172" s="2" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A173" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="C173" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="F173" s="6"/>
+      <c r="G173" s="2" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A174" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B174" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="C170" s="2" t="s">
+      <c r="C174" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="F170" s="6" t="s">
+      <c r="F174" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="G170" s="2" t="s">
+      <c r="G174" s="2" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="171" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A171" s="17" t="s">
+    <row r="175" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A175" s="17" t="s">
         <v>357</v>
       </c>
-      <c r="B171" s="17" t="s">
+      <c r="B175" s="17" t="s">
+        <v>498</v>
+      </c>
+      <c r="C175" s="17" t="s">
         <v>499</v>
       </c>
-      <c r="C171" s="17" t="s">
-        <v>500</v>
-      </c>
-      <c r="D171" s="17"/>
-      <c r="E171" s="17"/>
-      <c r="F171" s="20" t="s">
+      <c r="D175" s="17"/>
+      <c r="E175" s="17"/>
+      <c r="F175" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="G171" s="17"/>
-    </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A172" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B172" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="C172" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="F172" s="12" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="173" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A173" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B173" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="C173" s="2" t="s">
-        <v>520</v>
-      </c>
-      <c r="D173" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="F173" s="14" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="174" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A174" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B174" s="2" t="s">
-        <v>664</v>
-      </c>
-      <c r="C174" s="2" t="s">
-        <v>665</v>
-      </c>
-      <c r="D174" s="2" t="s">
-        <v>666</v>
-      </c>
-      <c r="F174" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="175" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A175" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B175" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="C175" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="E175" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="F175" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G175" s="2" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="176" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="G175" s="17"/>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>326</v>
+        <v>206</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="F176" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="177" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>207</v>
+      </c>
+      <c r="F176" s="12" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A177" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>64</v>
+        <v>518</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F177" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
+        <v>519</v>
+      </c>
+      <c r="D177" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="F177" s="14" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A178" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>497</v>
+        <v>661</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="F178" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+        <v>662</v>
+      </c>
+      <c r="D178" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="F178" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A179" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>65</v>
+        <v>197</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>68</v>
+        <v>198</v>
+      </c>
+      <c r="E179" s="2" t="s">
+        <v>206</v>
       </c>
       <c r="F179" s="16" t="s">
         <v>303</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A180" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>562</v>
+        <v>326</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>563</v>
+        <v>327</v>
       </c>
       <c r="F180" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A181" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>766</v>
+        <v>64</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>767</v>
+        <v>67</v>
       </c>
       <c r="F181" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A182" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>772</v>
+        <v>496</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>773</v>
-      </c>
-      <c r="F182" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="183" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+        <v>497</v>
+      </c>
+      <c r="F182" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>516</v>
+        <v>65</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="F183" s="6" t="s">
-        <v>102</v>
+        <v>68</v>
+      </c>
+      <c r="F183" s="16" t="s">
+        <v>303</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>199</v>
+        <v>561</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="F184" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="185" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>562</v>
+      </c>
+      <c r="F184" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>66</v>
+        <v>760</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D185" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="F185" s="14" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="186" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>761</v>
+      </c>
+      <c r="F185" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A186" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>190</v>
+        <v>766</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>191</v>
+        <v>767</v>
       </c>
       <c r="F186" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="187" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A187" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>277</v>
+        <v>515</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="F187" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="188" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>516</v>
+      </c>
+      <c r="F187" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G187" s="2" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>278</v>
+        <v>199</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="F188" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="189" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>200</v>
+      </c>
+      <c r="F188" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A189" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>279</v>
+        <v>810</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="F189" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="190" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>811</v>
+      </c>
+      <c r="D189" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="F189" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G189" s="2" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A190" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>567</v>
+        <v>66</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>568</v>
-      </c>
-      <c r="F190" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="191" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+      <c r="D190" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="F190" s="14" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>477</v>
+        <v>190</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>476</v>
+        <v>191</v>
       </c>
       <c r="F191" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="192" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A192" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B192" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="C192" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="F192" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A193" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C193" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="F193" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A194" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="C194" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="F194" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A195" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B195" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="C195" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="F195" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A196" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B196" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="C196" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="F196" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A197" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B197" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="C197" s="2" t="s">
         <v>493</v>
       </c>
-      <c r="C192" s="2" t="s">
+      <c r="F197" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A198" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="B198" s="17" t="s">
         <v>494</v>
       </c>
-      <c r="F192" s="4" t="s">
+      <c r="C198" s="17" t="s">
+        <v>495</v>
+      </c>
+      <c r="D198" s="17"/>
+      <c r="E198" s="17"/>
+      <c r="F198" s="20" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="193" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A193" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="B193" s="17" t="s">
-        <v>495</v>
-      </c>
-      <c r="C193" s="17" t="s">
-        <v>496</v>
-      </c>
-      <c r="D193" s="17"/>
-      <c r="E193" s="17"/>
-      <c r="F193" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="G193" s="17"/>
-    </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A194" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="B194" s="2" t="s">
-        <v>804</v>
-      </c>
-      <c r="C194" s="2" t="s">
-        <v>805</v>
-      </c>
-      <c r="F194" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="195" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A195" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="B195" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="C195" s="2" t="s">
-        <v>560</v>
-      </c>
-      <c r="D195" s="2" t="s">
-        <v>561</v>
-      </c>
-      <c r="F195" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A196" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="B196" s="2" t="s">
-        <v>713</v>
-      </c>
-      <c r="C196" s="2" t="s">
-        <v>714</v>
-      </c>
-      <c r="D196" s="2" t="s">
-        <v>712</v>
-      </c>
-      <c r="F196" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A197" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="B197" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="C197" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="F197" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A198" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="B198" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="C198" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="F198" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G198" s="17"/>
+    </row>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A199" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>401</v>
+        <v>793</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>402</v>
+        <v>794</v>
       </c>
       <c r="F199" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A200" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>432</v>
+        <v>558</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>433</v>
+        <v>559</v>
+      </c>
+      <c r="D200" s="2" t="s">
+        <v>560</v>
       </c>
       <c r="F200" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="201" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A201" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>613</v>
+        <v>708</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>615</v>
+        <v>709</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>614</v>
-      </c>
-      <c r="E201" s="2" t="s">
-        <v>434</v>
+        <v>707</v>
       </c>
       <c r="F201" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A202" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="F202" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A203" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="F203" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="204" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A204" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>530</v>
+        <v>401</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="F204" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G204" s="2" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="205" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>402</v>
+      </c>
+      <c r="F204" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A205" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>480</v>
+        <v>432</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="D205" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="F205" s="3"/>
-    </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
+        <v>433</v>
+      </c>
+      <c r="F205" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A206" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>528</v>
+        <v>612</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="F206" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="G206" s="2" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="207" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>614</v>
+      </c>
+      <c r="D206" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="E206" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="F206" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A207" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>503</v>
+        <v>434</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="E207" s="2" t="s">
-        <v>422</v>
+        <v>435</v>
       </c>
       <c r="F207" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A208" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>501</v>
+        <v>422</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="F208" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
+        <v>424</v>
+      </c>
+      <c r="F208" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A209" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>467</v>
+        <v>529</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="F209" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
+        <v>530</v>
+      </c>
+      <c r="F209" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G209" s="2" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A210" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>423</v>
+        <v>479</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="F210" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
+        <v>480</v>
+      </c>
+      <c r="D210" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="F210" s="3"/>
+    </row>
+    <row r="211" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A211" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>469</v>
+        <v>527</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="F211" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
+        <v>528</v>
+      </c>
+      <c r="F211" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G211" s="2" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A212" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>541</v>
+        <v>502</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>542</v>
+        <v>503</v>
+      </c>
+      <c r="E212" s="2" t="s">
+        <v>422</v>
       </c>
       <c r="F212" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="213" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A213" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>426</v>
+        <v>500</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="F213" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G213" s="2" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="214" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>501</v>
+      </c>
+      <c r="F213" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A214" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B214" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="C214" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="F214" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A215" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="B215" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="C215" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="F215" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A216" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="B216" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="C216" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="F216" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A217" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="B217" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="C217" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="F217" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A218" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="B218" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="C218" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="F218" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G218" s="2" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A219" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="B219" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="C219" s="2" t="s">
         <v>569</v>
       </c>
-      <c r="C214" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="F214" s="19" t="s">
+      <c r="F219" s="19" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="215" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A215" s="17" t="s">
+    <row r="220" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A220" s="17" t="s">
         <v>420</v>
       </c>
-      <c r="B215" s="17" t="s">
+      <c r="B220" s="17" t="s">
+        <v>490</v>
+      </c>
+      <c r="C220" s="17" t="s">
         <v>491</v>
       </c>
-      <c r="C215" s="17" t="s">
-        <v>492</v>
-      </c>
-      <c r="D215" s="17"/>
-      <c r="E215" s="17"/>
-      <c r="F215" s="19" t="s">
+      <c r="D220" s="17"/>
+      <c r="E220" s="17"/>
+      <c r="F220" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="G215" s="17"/>
-    </row>
-    <row r="216" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A216" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B216" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="C216" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="F216" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A217" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B217" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="C217" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="E217" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="F217" s="12" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="218" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A218" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B218" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="C218" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="F218" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="219" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A219" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B219" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="C219" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="F219" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G219" s="2" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="220" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A220" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B220" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="C220" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="F220" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G220" s="17"/>
+    </row>
+    <row r="221" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A221" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>94</v>
+        <v>209</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>97</v>
+        <v>210</v>
       </c>
       <c r="F221" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="222" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A222" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>216</v>
+        <v>304</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="F222" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="223" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>305</v>
+      </c>
+      <c r="E222" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F222" s="12" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A223" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B223" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C223" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="F223" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A224" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B224" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C224" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="F224" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G224" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A225" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B225" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="C225" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F225" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A226" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B226" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C226" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="F226" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A227" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B227" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C227" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="F227" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A228" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B228" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="C223" s="2" t="s">
+      <c r="C228" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="F223" s="12" t="s">
+      <c r="F228" s="12" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="224" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A224" s="17" t="s">
+    <row r="229" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A229" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="B224" s="17" t="s">
+      <c r="B229" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="C224" s="17" t="s">
+      <c r="C229" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D224" s="17"/>
-      <c r="E224" s="17"/>
-      <c r="F224" s="20" t="s">
+      <c r="D229" s="17"/>
+      <c r="E229" s="17"/>
+      <c r="F229" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="G224" s="17"/>
-    </row>
-    <row r="225" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A225" s="2" t="s">
+      <c r="G229" s="17"/>
+    </row>
+    <row r="230" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A230" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B225" s="2" t="s">
+      <c r="B230" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C225" s="2" t="s">
+      <c r="C230" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="F225" s="6" t="s">
+      <c r="F230" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="G225" s="2" t="s">
+      <c r="G230" s="2" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="226" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A226" s="2" t="s">
+    <row r="231" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A231" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B226" s="2" t="s">
+      <c r="B231" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="C226" s="2" t="s">
+      <c r="C231" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="F226" s="6" t="s">
+      <c r="F231" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="G226" s="2" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A227" s="2" t="s">
+      <c r="G231" s="2" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A232" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B227" s="2" t="s">
-        <v>747</v>
-      </c>
-      <c r="C227" s="2" t="s">
-        <v>748</v>
-      </c>
-      <c r="F227" s="6" t="s">
+      <c r="B232" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="C232" s="2" t="s">
+        <v>742</v>
+      </c>
+      <c r="F232" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="G227" s="2" t="s">
-        <v>749</v>
-      </c>
-    </row>
-    <row r="228" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A228" s="17" t="s">
+      <c r="G232" s="2" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A233" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="B228" s="17" t="s">
+      <c r="B233" s="17" t="s">
         <v>193</v>
       </c>
-      <c r="C228" s="17" t="s">
+      <c r="C233" s="17" t="s">
         <v>195</v>
       </c>
-      <c r="D228" s="17"/>
-      <c r="E228" s="17"/>
-      <c r="F228" s="22" t="s">
+      <c r="D233" s="17"/>
+      <c r="E233" s="17"/>
+      <c r="F233" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="G228" s="17" t="s">
+      <c r="G233" s="17" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A229" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B229" s="2" t="s">
-        <v>632</v>
-      </c>
-      <c r="C229" s="2" t="s">
-        <v>633</v>
-      </c>
-      <c r="F229" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A230" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B230" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="C230" s="2" t="s">
-        <v>551</v>
-      </c>
-      <c r="F230" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A231" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B231" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C231" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F231" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A232" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B232" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C232" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="F232" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="233" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A233" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B233" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="C233" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="F233" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A234" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>411</v>
+        <v>631</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>412</v>
+        <v>632</v>
       </c>
       <c r="F234" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A235" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>677</v>
+        <v>549</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>678</v>
-      </c>
-      <c r="F235" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
+        <v>550</v>
+      </c>
+      <c r="F235" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A236" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>552</v>
+        <v>74</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="F236" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+      <c r="F236" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A237" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>283</v>
+        <v>75</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="F237" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="238" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+      <c r="F237" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A238" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>256</v>
+        <v>553</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="F238" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="239" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>554</v>
+      </c>
+      <c r="F238" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A239" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>236</v>
+        <v>411</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="E239" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="F239" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
+        <v>412</v>
+      </c>
+      <c r="F239" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A240" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>806</v>
+        <v>674</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>807</v>
-      </c>
-      <c r="F240" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
+        <v>675</v>
+      </c>
+      <c r="F240" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A241" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>618</v>
+        <v>551</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>619</v>
+        <v>552</v>
       </c>
       <c r="F241" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A242" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>620</v>
+        <v>283</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>621</v>
-      </c>
-      <c r="F242" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
+        <v>284</v>
+      </c>
+      <c r="F242" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A243" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>232</v>
+        <v>256</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="F243" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
+        <v>257</v>
+      </c>
+      <c r="F243" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A244" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
+      </c>
+      <c r="E244" s="2" t="s">
+        <v>379</v>
       </c>
       <c r="F244" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A245" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>634</v>
+        <v>795</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="D245" s="2" t="s">
-        <v>636</v>
-      </c>
-      <c r="F245" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
+        <v>796</v>
+      </c>
+      <c r="F245" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A246" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="F246" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A247" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>710</v>
+        <v>619</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>711</v>
-      </c>
-      <c r="F247" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
+        <v>620</v>
+      </c>
+      <c r="F247" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A248" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>637</v>
+        <v>232</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>638</v>
-      </c>
-      <c r="F248" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
+        <v>233</v>
+      </c>
+      <c r="F248" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A249" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>609</v>
+        <v>228</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>610</v>
-      </c>
-      <c r="F249" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
+        <v>229</v>
+      </c>
+      <c r="F249" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A250" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>589</v>
+        <v>829</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>590</v>
+        <v>830</v>
       </c>
       <c r="F250" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A251" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>241</v>
+        <v>633</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="F251" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="252" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+        <v>634</v>
+      </c>
+      <c r="D251" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="F251" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A252" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>285</v>
+        <v>831</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="F252" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="G252" s="2" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
+        <v>832</v>
+      </c>
+      <c r="F252" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A253" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>76</v>
+        <v>621</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>84</v>
+        <v>622</v>
       </c>
       <c r="F253" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A254" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>77</v>
+        <v>814</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F254" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
+        <v>815</v>
+      </c>
+      <c r="F254" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A255" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>78</v>
+        <v>705</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F255" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
+        <v>706</v>
+      </c>
+      <c r="F255" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A256" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>79</v>
+        <v>636</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="F256" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="257" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>637</v>
+      </c>
+      <c r="F256" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A257" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>624</v>
+        <v>608</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>625</v>
-      </c>
-      <c r="D257" s="2" t="s">
-        <v>626</v>
-      </c>
-      <c r="F257" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
+        <v>609</v>
+      </c>
+      <c r="F257" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A258" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>448</v>
+        <v>588</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>449</v>
+        <v>589</v>
       </c>
       <c r="F258" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A259" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>478</v>
+        <v>241</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>479</v>
+        <v>242</v>
       </c>
       <c r="F259" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="260" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A260" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>639</v>
+        <v>285</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>640</v>
-      </c>
-      <c r="F260" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
+        <v>286</v>
+      </c>
+      <c r="F260" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="G260" s="2" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A261" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>741</v>
+        <v>76</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>742</v>
-      </c>
-      <c r="F261" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+      <c r="F261" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="262" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A262" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="F262" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+      <c r="F262" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A263" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>548</v>
+        <v>78</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>549</v>
+        <v>86</v>
       </c>
       <c r="F263" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="264" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A264" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>293</v>
+        <v>79</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="F264" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G264" s="2" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="265" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+      <c r="F264" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A265" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>295</v>
+        <v>623</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="F265" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G265" s="2" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="266" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+        <v>624</v>
+      </c>
+      <c r="D265" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="F265" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A266" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>239</v>
+        <v>447</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="F266" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G266" s="2" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
+        <v>448</v>
+      </c>
+      <c r="F266" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A267" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>230</v>
+        <v>477</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="E267" s="2" t="s">
-        <v>228</v>
+        <v>478</v>
       </c>
       <c r="F267" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="268" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A268" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>693</v>
+        <v>638</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>694</v>
+        <v>639</v>
       </c>
       <c r="F268" s="5" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="269" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A269" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>81</v>
+        <v>735</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="F269" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.25">
+        <v>736</v>
+      </c>
+      <c r="F269" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A270" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>745</v>
+        <v>80</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>746</v>
-      </c>
-      <c r="F270" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="271" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+      <c r="F270" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="271" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A271" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>443</v>
+        <v>547</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="F271" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="G271" s="2" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
+        <v>548</v>
+      </c>
+      <c r="F271" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A272" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>641</v>
+        <v>293</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>642</v>
-      </c>
-      <c r="F272" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
+        <v>294</v>
+      </c>
+      <c r="F272" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G272" s="2" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A273" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>507</v>
+        <v>295</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="F273" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="274" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+        <v>296</v>
+      </c>
+      <c r="F273" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G273" s="2" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A274" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>778</v>
+        <v>239</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>779</v>
+        <v>240</v>
       </c>
       <c r="F274" s="16" t="s">
         <v>303</v>
       </c>
       <c r="G274" s="2" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A275" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>245</v>
+        <v>230</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="F275" s="14" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
+        <v>231</v>
+      </c>
+      <c r="E275" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F275" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A276" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>298</v>
+        <v>688</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>297</v>
+        <v>689</v>
       </c>
       <c r="F276" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.25">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A277" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>643</v>
+        <v>81</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>644</v>
+        <v>89</v>
       </c>
       <c r="F277" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A278" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>234</v>
+        <v>739</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="F278" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+      <c r="F278" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A279" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>627</v>
+        <v>443</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>628</v>
-      </c>
-      <c r="F279" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.25">
+        <v>444</v>
+      </c>
+      <c r="F279" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G279" s="2" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A280" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>226</v>
+        <v>640</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="F280" s="12" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.25">
+        <v>641</v>
+      </c>
+      <c r="F280" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A281" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>524</v>
+        <v>506</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="F281" s="14" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.25">
+        <v>507</v>
+      </c>
+      <c r="F281" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A282" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>522</v>
+        <v>772</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="E282" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="F282" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.25">
+        <v>773</v>
+      </c>
+      <c r="F282" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G282" s="2" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A283" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>224</v>
+        <v>245</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="F283" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="284" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>246</v>
+      </c>
+      <c r="F283" s="14" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A284" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>645</v>
+        <v>298</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>646</v>
-      </c>
-      <c r="F284" s="20" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="285" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+        <v>297</v>
+      </c>
+      <c r="F284" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A285" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>584</v>
+        <v>642</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>586</v>
-      </c>
-      <c r="F285" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G285" s="2" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="286" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+        <v>643</v>
+      </c>
+      <c r="F285" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A286" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B286" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C286" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="F286" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A287" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B287" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="C287" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="F287" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="288" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A288" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B288" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C288" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="F288" s="12" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="289" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A289" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B289" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="C289" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="F289" s="14" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="290" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A290" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B290" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C290" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="E290" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="F290" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="291" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A291" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B291" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C291" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="F291" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="292" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A292" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B292" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="C292" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="F292" s="20" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="293" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A293" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B293" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="C293" s="2" t="s">
         <v>585</v>
       </c>
-      <c r="C286" s="2" t="s">
-        <v>588</v>
-      </c>
-      <c r="F286" s="16" t="s">
+      <c r="F293" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G293" s="2" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="294" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A294" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B294" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="C294" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="F294" s="16" t="s">
         <v>303</v>
       </c>
-      <c r="G286" s="2" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="287" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A287" s="17" t="s">
+      <c r="G294" s="2" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="295" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A295" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="B287" s="17" t="s">
+      <c r="B295" s="17" t="s">
         <v>306</v>
       </c>
-      <c r="C287" s="17" t="s">
+      <c r="C295" s="17" t="s">
         <v>307</v>
       </c>
-      <c r="D287" s="17"/>
-      <c r="E287" s="17"/>
-      <c r="F287" s="20" t="s">
+      <c r="D295" s="17"/>
+      <c r="E295" s="17"/>
+      <c r="F295" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="G287" s="17"/>
-    </row>
-    <row r="288" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A288" s="2" t="s">
+      <c r="G295" s="17"/>
+    </row>
+    <row r="296" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A296" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B288" s="2" t="s">
+      <c r="B296" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C288" s="2" t="s">
+      <c r="C296" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D288" s="2" t="s">
+      <c r="D296" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="F288" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A289" s="2" t="s">
+      <c r="F296" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="297" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A297" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B289" s="2" t="s">
+      <c r="B297" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="C289" s="2" t="s">
+      <c r="C297" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="D289" s="2" t="s">
+      <c r="D297" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="F289" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="290" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A290" s="2" t="s">
+      <c r="F297" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="298" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A298" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B290" s="2" t="s">
+      <c r="B298" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="C290" s="2" t="s">
+      <c r="C298" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="D290" s="2" t="s">
+      <c r="D298" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="F290" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="291" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A291" s="2" t="s">
+      <c r="F298" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="299" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A299" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B291" s="2" t="s">
-        <v>808</v>
-      </c>
-      <c r="C291" s="2" t="s">
-        <v>809</v>
-      </c>
-      <c r="F291" s="25" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A292" s="2" t="s">
+      <c r="B299" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="C299" s="2" t="s">
+        <v>798</v>
+      </c>
+      <c r="F299" s="25" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="300" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A300" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B292" s="2" t="s">
+      <c r="B300" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="C292" s="2" t="s">
+      <c r="C300" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="F292" s="4" t="s">
+      <c r="F300" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A293" s="2" t="s">
+    <row r="301" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A301" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B293" s="2" t="s">
+      <c r="B301" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="C301" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="C293" s="2" t="s">
+      <c r="D301" s="2" t="s">
         <v>565</v>
       </c>
-      <c r="D293" s="2" t="s">
-        <v>566</v>
-      </c>
-      <c r="F293" s="4" t="s">
+      <c r="F301" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="294" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A294" s="17" t="s">
+    <row r="302" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A302" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="B294" s="17" t="s">
+      <c r="B302" s="17" t="s">
         <v>291</v>
       </c>
-      <c r="C294" s="17" t="s">
+      <c r="C302" s="17" t="s">
         <v>292</v>
       </c>
-      <c r="D294" s="17" t="s">
+      <c r="D302" s="17" t="s">
         <v>308</v>
       </c>
-      <c r="E294" s="17"/>
-      <c r="F294" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="G294" s="17"/>
+      <c r="E302" s="17"/>
+      <c r="F302" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="G302" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7812,13 +8007,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.5703125" customWidth="1"/>
-    <col min="2" max="2" width="52.28515625" customWidth="1"/>
+    <col min="1" max="1" width="18.54296875" customWidth="1"/>
+    <col min="2" max="2" width="52.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7826,7 +8021,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -7834,7 +8029,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -7842,7 +8037,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>36</v>
       </c>
@@ -7850,7 +8045,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>172</v>
       </c>
@@ -7858,7 +8053,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>413</v>
       </c>
@@ -7866,15 +8061,15 @@
         <v>414</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
+        <v>484</v>
+      </c>
+      <c r="B7" t="s">
         <v>485</v>
       </c>
-      <c r="B7" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>38</v>
       </c>
@@ -7882,7 +8077,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>43</v>
       </c>
@@ -7890,7 +8085,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>275</v>
       </c>
@@ -7898,7 +8093,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -7906,7 +8101,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>404</v>
       </c>
@@ -7914,7 +8109,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>357</v>
       </c>
@@ -7922,7 +8117,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>63</v>
       </c>
@@ -7930,7 +8125,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>420</v>
       </c>
@@ -7938,7 +8133,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>93</v>
       </c>
@@ -7946,7 +8141,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>70</v>
       </c>
@@ -7954,7 +8149,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>73</v>
       </c>
@@ -7962,7 +8157,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>90</v>
       </c>

--- a/InputData/acronym-key.xlsx
+++ b/InputData/acronym-key.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanO'Brien\Models\EPS\US\eps-us\InputData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{689CA091-282C-434F-9EC8-B18750BFFC58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0106C665-AB98-46AA-99A6-AC85633E64FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-4275" yWindow="-13455" windowWidth="17325" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1436" uniqueCount="833">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1495" uniqueCount="863">
   <si>
     <t>Top Level Folder</t>
   </si>
@@ -226,18 +226,12 @@
     <t>indst</t>
   </si>
   <si>
-    <t>CtIEPpUESoS</t>
-  </si>
-  <si>
     <t>FLRbI</t>
   </si>
   <si>
     <t>PERAC</t>
   </si>
   <si>
-    <t>Cost to Implement Efficiency Policy per Unit Energy Saved or Shifted</t>
-  </si>
-  <si>
     <t>Foreign Leakage Rate by Industry</t>
   </si>
   <si>
@@ -625,12 +619,6 @@
     <t>MPPC</t>
   </si>
   <si>
-    <t>BPoIFUfE</t>
-  </si>
-  <si>
-    <t>BAU Proportion of Industrial Fuel Used for Energy</t>
-  </si>
-  <si>
     <t>MHV</t>
   </si>
   <si>
@@ -652,12 +640,6 @@
     <t>BAU RPS Qualifying Source Definitions, RPS Qualifying Source Definitions</t>
   </si>
   <si>
-    <t>BIFUbC</t>
-  </si>
-  <si>
-    <t>BAU Industrial Fuel Use before CCS</t>
-  </si>
-  <si>
     <t>Minimum Power Plant Capacity</t>
   </si>
   <si>
@@ -865,24 +847,6 @@
     <t>Endogenous Learning</t>
   </si>
   <si>
-    <t>PPRiFUfERoIF</t>
-  </si>
-  <si>
-    <t>PPRiFUfICaWHR</t>
-  </si>
-  <si>
-    <t>PPRiFUfIIaIoE</t>
-  </si>
-  <si>
-    <t>Potential Perc Reduction in Fuel Use from Early Retirement of Inefficient Facilities</t>
-  </si>
-  <si>
-    <t>Potential Perc Reduction in Fuel Use from Increased Cogen and Waste Heat Recovery</t>
-  </si>
-  <si>
-    <t>Potential Perc Reduction in Fuel Use from Improved Installation and Integration of Eqpt</t>
-  </si>
-  <si>
     <t>BAADTbVT</t>
   </si>
   <si>
@@ -1051,9 +1015,6 @@
     <t>medium (n/a for RPS Qualifying Source Definitions, as it is a policy lever)</t>
   </si>
   <si>
-    <t>You are including fuel used as a feedstock (not burned for energy) in indst/BIFUbC (otherwise set to zero)</t>
-  </si>
-  <si>
     <t>Pollutant Emissions Intensity Improvement Rate</t>
   </si>
   <si>
@@ -1375,6 +1336,9 @@
     <t>Quantization Size for Pollutants</t>
   </si>
   <si>
+    <t>BAU Imported Electricity, BAU Exported Electricity, Imported Electricity Price, BAU Exported Electricity Price</t>
+  </si>
+  <si>
     <t>EVCC</t>
   </si>
   <si>
@@ -1528,12 +1492,6 @@
     <t>Elasticities of Demand for Industrial Products</t>
   </si>
   <si>
-    <t>SoHPCCbRIC</t>
-  </si>
-  <si>
-    <t>Share of Hydrogen Production Capital Costs by Recipient ISIC Code</t>
-  </si>
-  <si>
     <t>HSR</t>
   </si>
   <si>
@@ -1579,12 +1537,6 @@
     <t>You wish to switch from the BAU plant retirement schedule to an alternative schedule you have specified in input data (rather than using the early retirement policy lever, which accelerates retirements and is additive to the BAU retirements)</t>
   </si>
   <si>
-    <t>IFStFS</t>
-  </si>
-  <si>
-    <t>Industrial Fuels Subject to Fuel Shifting</t>
-  </si>
-  <si>
     <t>You wish for the industrial fuel shifting policy lever to affect a different set of source (BAU) fuel types than the default set (which consists of the fossil fuels).</t>
   </si>
   <si>
@@ -2002,15 +1954,18 @@
     <t>BAU Cost of Electricity Sector Capital</t>
   </si>
   <si>
-    <t>BAU Cost of Electricity Sector Capital for Power Plants, BAU Cost of Electricity Sector Capital for Other Investments</t>
-  </si>
-  <si>
     <t>BZECfNP</t>
   </si>
   <si>
     <t>BAU Zero Emis Credit for Nuc Plants</t>
   </si>
   <si>
+    <t>EDWP</t>
+  </si>
+  <si>
+    <t>Electricity Dispatch Weibull Parameters</t>
+  </si>
+  <si>
     <t>MLfPPR</t>
   </si>
   <si>
@@ -2086,10 +2041,10 @@
     <t>Fraction of EVs Used for Grid Balancing on Average Day, Fraction of EV Battery Capacity Used for Grid Balancing when EV is Used for Grid Balancing</t>
   </si>
   <si>
-    <t>CCSTaSC</t>
-  </si>
-  <si>
-    <t>CCS Transportation and Storage Cost</t>
+    <t>BSpUESttGbGB</t>
+  </si>
+  <si>
+    <t>BAU Subsidy per Unit Electricity Supplied to the Grid by Grid Batteries</t>
   </si>
   <si>
     <t>BPSpUGBCD</t>
@@ -2215,6 +2170,9 @@
     <t>Capacity Supply Curve</t>
   </si>
   <si>
+    <t>Electricity Dispatch Weibull Parameter A, Electricity Dispatch Weibull Parameter B</t>
+  </si>
+  <si>
     <t>GBCGpUNR</t>
   </si>
   <si>
@@ -2362,6 +2320,15 @@
     <t>STfECCE</t>
   </si>
   <si>
+    <t>BUCMfNCR</t>
+  </si>
+  <si>
+    <t>Boolean Use Capacity Market for New Capacity Revenue</t>
+  </si>
+  <si>
+    <t>You wish the electricity sector to only collect capacity costs for new capacity and not pay them out to all resources in the market.</t>
+  </si>
+  <si>
     <t>FoICbCTBA</t>
   </si>
   <si>
@@ -2389,6 +2356,12 @@
     <t>Cap Ret per Unit Net Loss</t>
   </si>
   <si>
+    <t>ESUfRaLCD</t>
+  </si>
+  <si>
+    <t>Elec Sources Used for Rlbty and Lst Cst Dsptch</t>
+  </si>
+  <si>
     <t>BFoICbCTBA</t>
   </si>
   <si>
@@ -2434,6 +2407,144 @@
     <t>do not edit - QC file to automatically check specified files</t>
   </si>
   <si>
+    <t>BIFU</t>
+  </si>
+  <si>
+    <t>BAU Industrial Fuel Use for Energy, BAU Industrial Fuel Use as Feedstock</t>
+  </si>
+  <si>
+    <t>BAU Industrial Fuel Use</t>
+  </si>
+  <si>
+    <t>IESD</t>
+  </si>
+  <si>
+    <t>Industrial Equipment Survival Data</t>
+  </si>
+  <si>
+    <t>"Start Year Share of Industrial Equipment by Vintage" must be updated if changing the first simulated year (Initial Time)</t>
+  </si>
+  <si>
+    <t>EoIEECwEC</t>
+  </si>
+  <si>
+    <t>Elasticity of Industrial Equipment Energy Consumption with respect to Energy Cost</t>
+  </si>
+  <si>
+    <t>FYIESM</t>
+  </si>
+  <si>
+    <t>Final Year Industrial Equipment Shareweight Minimums</t>
+  </si>
+  <si>
+    <t>IELC</t>
+  </si>
+  <si>
+    <t>Industrial Equipment Logit Coefficient</t>
+  </si>
+  <si>
+    <t>CECpUES</t>
+  </si>
+  <si>
+    <t>CHP Equipment Cost per Unit Energy Shifted</t>
+  </si>
+  <si>
+    <t>IECCpUAEU</t>
+  </si>
+  <si>
+    <t>Industrial Equipment Capital Cost per Unit Annual Energy Use</t>
+  </si>
+  <si>
+    <t>Start Year Share of Industrial Equipment by Vintage, Retiring Fraction of Industrial Equipment Retiring by Age, Average Age at Which Equipment Retires</t>
+  </si>
+  <si>
+    <t>BCoISC</t>
+  </si>
+  <si>
+    <t>BAU Cost of Industry Sector Capital</t>
+  </si>
+  <si>
+    <t>Weighted Average Cost of Capital by Industry, Risk Premium for Equity</t>
+  </si>
+  <si>
+    <t>RPFfFISCC</t>
+  </si>
+  <si>
+    <t>Repayment Period for Financed Industry Sector Capital Costs</t>
+  </si>
+  <si>
+    <t>BCHPD</t>
+  </si>
+  <si>
+    <t>BAU Clean Heat PTC Duration</t>
+  </si>
+  <si>
+    <t>BCHPR</t>
+  </si>
+  <si>
+    <t>BAU Clean Heat PTC Rate</t>
+  </si>
+  <si>
+    <t>IFTQfS</t>
+  </si>
+  <si>
+    <t>SoFCTiBoSFbI</t>
+  </si>
+  <si>
+    <t>Share of Fuel Consumption that is Byproduct or Secondary Fuel by Industry</t>
+  </si>
+  <si>
+    <t>Industrial Fuels Qualifying for Support</t>
+  </si>
+  <si>
+    <t>Industrial Fuels Qualifying for PTC, Industrial Fuels Qualifying for ITC, Industrial Fuels Qualifying for Loans</t>
+  </si>
+  <si>
+    <t>BIEEI</t>
+  </si>
+  <si>
+    <t>BAU Industrial Equipment Efficiency Improvement</t>
+  </si>
+  <si>
+    <t>BAU Industrial Energy Use Reduction from Process Efficiency Improvements</t>
+  </si>
+  <si>
+    <t>BIEURfPEI</t>
+  </si>
+  <si>
+    <t>IEMUEF</t>
+  </si>
+  <si>
+    <t>Industrial Equipment Minimum Unit Energy Factor</t>
+  </si>
+  <si>
+    <t>SYIEUEFbIPaF</t>
+  </si>
+  <si>
+    <t>Start Year Industrial Equipment Unit Energy Factor by Industrial Process and Fuel</t>
+  </si>
+  <si>
+    <t>FYIbFP</t>
+  </si>
+  <si>
+    <t>First Year Impacted by Future Policies</t>
+  </si>
+  <si>
+    <t>2025 ends // or // you wish to model the impact of a policy package that will be passed in years after the present year (e.g., what if the next administration does XYZ)</t>
+  </si>
+  <si>
+    <t>CCSTaSCaS</t>
+  </si>
+  <si>
+    <t>CCS Transportation and Storage Cost and Subsidies</t>
+  </si>
+  <si>
+    <t>Repayment Period for Financing Buildings Sector Capital Costs</t>
+  </si>
+  <si>
+    <t>BAU Cost of Electricity Sector Capital for Power Plants, BAU Cost of Electricity Sector Capital for Other Investments, BAU Cost of Electricity Sector Capital for Distributed Solar Investments</t>
+  </si>
+  <si>
     <t>CiDESCTY</t>
   </si>
   <si>
@@ -2443,27 +2554,6 @@
     <t>You plan on using a policy mandated change in distributed solar capacity additions</t>
   </si>
   <si>
-    <t>NBICP</t>
-  </si>
-  <si>
-    <t>Non BAU Industry CCS Parameters</t>
-  </si>
-  <si>
-    <t>Fraction of CCS Potential Achieved by Industry Energy, Fraction of CCS Potential Achieved by Industry Process, CCS Subsidies</t>
-  </si>
-  <si>
-    <t>You wish to use a policy lever to testalternate CCS subsidies for industries</t>
-  </si>
-  <si>
-    <t>NBRHPF</t>
-  </si>
-  <si>
-    <t>Non BAU Recipient Hydrogen Pathway Fractions</t>
-  </si>
-  <si>
-    <t>You wish for the non BAU hydrogen pathway shifting policy to shift hydrogen production to a pathway other than electrolysis</t>
-  </si>
-  <si>
     <t>PEAAC</t>
   </si>
   <si>
@@ -2488,49 +2578,49 @@
     <t>Time Adjusted Capacity Factor Multiplier for Plants Built This Year</t>
   </si>
   <si>
+    <t>BSfGBP</t>
+  </si>
+  <si>
+    <t>BAU Subsidy for Grid Battery Production</t>
+  </si>
+  <si>
     <t>FoGBPD</t>
   </si>
   <si>
     <t>Fraction of Grid Batteries Produced Domestically</t>
   </si>
   <si>
-    <t>BSfGBP</t>
-  </si>
-  <si>
-    <t>BAU Subsidy for Grid Battery Production</t>
-  </si>
-  <si>
-    <t>BEEEfEPS</t>
-  </si>
-  <si>
-    <t>Boolean Exclude Electricity Exports from Elec Portfolio Stds</t>
-  </si>
-  <si>
-    <t>You wish to change the default behavior or whether electricity exports are included or excluded in RPS and CES policies.</t>
-  </si>
-  <si>
-    <t>MV</t>
-  </si>
-  <si>
-    <t>Modeled Vintages</t>
-  </si>
-  <si>
-    <t>You are using a different model start year than the US EPS (this file should note which vintages are for historical years rather than modeled years)</t>
-  </si>
-  <si>
-    <t>BAU Imported Electricity, BAU Exported Electricity, Imported Electricity Price</t>
-  </si>
-  <si>
-    <t>BPM</t>
-  </si>
-  <si>
-    <t>Battery Pack Markup</t>
-  </si>
-  <si>
-    <t>BPPM</t>
-  </si>
-  <si>
-    <t>Battery Pack Price Multiplier</t>
+    <t>NBICS</t>
+  </si>
+  <si>
+    <t>Non BAU Industry CCS Subsidy</t>
+  </si>
+  <si>
+    <t>You plan on using the non-BAU CCS subsidy boolean lever</t>
+  </si>
+  <si>
+    <t>CECRCbI</t>
+  </si>
+  <si>
+    <t>Cost Effective CCS Retrofit Capacity by Industry</t>
+  </si>
+  <si>
+    <t>SoCECRCSiaY</t>
+  </si>
+  <si>
+    <t>Share of Cost Effective CCS Retrofit Construction Started in a Year</t>
+  </si>
+  <si>
+    <t>CRDT</t>
+  </si>
+  <si>
+    <t>CCS Retrofit Deployment Time</t>
+  </si>
+  <si>
+    <t>IFStE</t>
+  </si>
+  <si>
+    <t>Industrial Fuels Subject to Electrification</t>
   </si>
 </sst>
 </file>
@@ -3019,319 +3109,319 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B19" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
-        <v>300</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B26" s="13" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="C26" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C27" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C28" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="10" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B30" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B31" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B32" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B33" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B34" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B35" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B36" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B37" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" s="9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B39" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B40" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B41" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B42" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B43" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B44" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B45" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B46" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" s="15" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="B48" s="15"/>
       <c r="C48" s="15"/>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B49" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B50" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B51" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B52" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B53" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B54" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B55" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" s="11" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B57" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B58" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B59" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B60" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -3342,7 +3432,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G302"/>
+  <dimension ref="A1:G316"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.54296875" style="2" customWidth="1"/>
@@ -3369,13 +3459,13 @@
         <v>3</v>
       </c>
       <c r="E1" s="23" t="s">
-        <v>378</v>
+        <v>365</v>
       </c>
       <c r="F1" s="23" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G1" s="23" t="s">
-        <v>318</v>
+        <v>306</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
@@ -3383,18 +3473,18 @@
         <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>537</v>
+        <v>521</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>538</v>
+        <v>522</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G2" s="24" t="s">
-        <v>539</v>
+        <v>523</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -3402,16 +3492,16 @@
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>534</v>
+        <v>518</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>535</v>
+        <v>519</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>536</v>
+        <v>520</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
@@ -3419,13 +3509,13 @@
         <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>460</v>
+        <v>448</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>461</v>
+        <v>449</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -3433,16 +3523,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>580</v>
+        <v>564</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>581</v>
+        <v>565</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>582</v>
+        <v>566</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
@@ -3456,7 +3546,7 @@
         <v>8</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3464,15 +3554,15 @@
         <v>4</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D7" s="17"/>
       <c r="E7" s="17"/>
       <c r="F7" s="18" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G7" s="17"/>
     </row>
@@ -3487,7 +3577,7 @@
         <v>23</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
@@ -3501,7 +3591,7 @@
         <v>24</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
@@ -3509,13 +3599,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>712</v>
+        <v>697</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>713</v>
+        <v>698</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
@@ -3529,10 +3619,10 @@
         <v>25</v>
       </c>
       <c r="F11" s="16" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>316</v>
+        <v>304</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
@@ -3540,13 +3630,13 @@
         <v>9</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>610</v>
+        <v>594</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>611</v>
+        <v>595</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
@@ -3554,16 +3644,16 @@
         <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>382</v>
+        <v>369</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>383</v>
+        <v>370</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>384</v>
+        <v>371</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
@@ -3577,7 +3667,7 @@
         <v>26</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -3585,16 +3675,16 @@
         <v>9</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>800</v>
+        <v>837</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>801</v>
+        <v>838</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>802</v>
+        <v>839</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -3602,16 +3692,16 @@
         <v>9</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>462</v>
+        <v>450</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
@@ -3625,7 +3715,7 @@
         <v>27</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
@@ -3639,7 +3729,7 @@
         <v>28</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
@@ -3653,7 +3743,7 @@
         <v>29</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -3661,13 +3751,13 @@
         <v>9</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
@@ -3681,7 +3771,7 @@
         <v>30</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -3689,13 +3779,13 @@
         <v>9</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
@@ -3703,13 +3793,13 @@
         <v>9</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>768</v>
+        <v>754</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>769</v>
+        <v>755</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -3723,10 +3813,10 @@
         <v>31</v>
       </c>
       <c r="F24" s="16" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>316</v>
+        <v>304</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -3740,7 +3830,7 @@
         <v>32</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -3754,10 +3844,10 @@
         <v>33</v>
       </c>
       <c r="F26" s="16" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>317</v>
+        <v>305</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -3771,7 +3861,7 @@
         <v>34</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -3785,7 +3875,7 @@
         <v>35</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -3793,61 +3883,61 @@
         <v>9</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>354</v>
+        <v>341</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="F29" s="16" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>449</v>
+        <v>562</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="F30" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>835</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>454</v>
+        <v>437</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+        <v>438</v>
+      </c>
+      <c r="F31" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>504</v>
+        <v>442</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="F32" s="5" t="s">
-        <v>101</v>
+        <v>443</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
@@ -3855,13 +3945,13 @@
         <v>9</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>243</v>
+        <v>490</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="F33" s="14" t="s">
-        <v>258</v>
+        <v>491</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
@@ -3869,13 +3959,13 @@
         <v>9</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>486</v>
+        <v>237</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>100</v>
+        <v>238</v>
+      </c>
+      <c r="F34" s="14" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
@@ -3883,701 +3973,688 @@
         <v>9</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>458</v>
+        <v>474</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="E35" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="E36" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F35" s="12" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="17" t="s">
+      <c r="F36" s="12" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="B36" s="17" t="s">
-        <v>456</v>
-      </c>
-      <c r="C36" s="17" t="s">
-        <v>457</v>
-      </c>
-      <c r="D36" s="17"/>
-      <c r="E36" s="17" t="s">
-        <v>164</v>
-      </c>
-      <c r="F36" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="G36" s="17"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A37" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>616</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="B37" s="17" t="s">
+        <v>444</v>
+      </c>
+      <c r="C37" s="17" t="s">
+        <v>445</v>
+      </c>
+      <c r="D37" s="17"/>
+      <c r="E37" s="17" t="s">
+        <v>162</v>
+      </c>
+      <c r="F37" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="G37" s="17"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>691</v>
+        <v>599</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>692</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>693</v>
-      </c>
-      <c r="F38" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+        <v>600</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>695</v>
+        <v>676</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>696</v>
-      </c>
-      <c r="F39" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="116" x14ac:dyDescent="0.35">
+        <v>677</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>37</v>
+        <v>680</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>694</v>
-      </c>
-      <c r="F40" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>681</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="116" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>409</v>
+        <v>37</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>690</v>
+        <v>679</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>684</v>
+        <v>396</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>685</v>
+        <v>397</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>675</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>803</v>
+        <v>833</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>804</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>805</v>
-      </c>
-      <c r="F43" s="21" t="s">
-        <v>303</v>
-      </c>
-      <c r="G43" s="2" t="s">
-        <v>806</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>834</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>698</v>
+        <v>855</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>699</v>
-      </c>
-      <c r="F44" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" s="17" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="17" t="s">
+        <v>856</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A45" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B45" s="17" t="s">
-        <v>775</v>
-      </c>
-      <c r="C45" s="17" t="s">
-        <v>697</v>
-      </c>
-      <c r="F45" s="20" t="s">
-        <v>100</v>
+      <c r="B45" s="2" t="s">
+        <v>859</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>860</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
-        <v>172</v>
+        <v>36</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>5</v>
+        <v>852</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F46" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="17" t="s">
-        <v>172</v>
-      </c>
-      <c r="B47" s="17" t="s">
-        <v>439</v>
-      </c>
-      <c r="C47" s="17" t="s">
-        <v>440</v>
-      </c>
-      <c r="D47" s="17"/>
-      <c r="E47" s="17"/>
-      <c r="F47" s="22" t="s">
-        <v>142</v>
-      </c>
-      <c r="G47" s="17" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="17" t="s">
-        <v>484</v>
-      </c>
-      <c r="B48" s="17" t="s">
-        <v>445</v>
-      </c>
-      <c r="C48" s="17" t="s">
-        <v>446</v>
-      </c>
-      <c r="D48" s="17"/>
-      <c r="E48" s="17"/>
-      <c r="F48" s="22" t="s">
-        <v>142</v>
-      </c>
-      <c r="G48" s="17" t="s">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="58" x14ac:dyDescent="0.35">
-      <c r="A49" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="F49" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="G49" s="2" t="s">
-        <v>330</v>
+        <v>853</v>
+      </c>
+      <c r="F46" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A47" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>857</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>858</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A48" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" s="17" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A49" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="B49" s="17" t="s">
+        <v>761</v>
+      </c>
+      <c r="C49" s="17" t="s">
+        <v>682</v>
+      </c>
+      <c r="F49" s="20" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
-        <v>413</v>
+        <v>170</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>555</v>
+        <v>5</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>556</v>
-      </c>
-      <c r="F50" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="G50" s="2" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="58" x14ac:dyDescent="0.35">
-      <c r="A51" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="F51" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A52" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>822</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>823</v>
-      </c>
-      <c r="F52" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="G52" s="2" t="s">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A51" s="17" t="s">
+        <v>170</v>
+      </c>
+      <c r="B51" s="17" t="s">
+        <v>426</v>
+      </c>
+      <c r="C51" s="17" t="s">
+        <v>427</v>
+      </c>
+      <c r="D51" s="17"/>
+      <c r="E51" s="17"/>
+      <c r="F51" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="G51" s="17" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A52" s="17" t="s">
+        <v>472</v>
+      </c>
+      <c r="B52" s="17" t="s">
+        <v>432</v>
+      </c>
+      <c r="C52" s="17" t="s">
+        <v>433</v>
+      </c>
+      <c r="D52" s="17"/>
+      <c r="E52" s="17"/>
+      <c r="F52" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="G52" s="17" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
-        <v>413</v>
+        <v>400</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>342</v>
+        <v>312</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>343</v>
+        <v>313</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
-        <v>413</v>
+        <v>400</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>251</v>
+        <v>539</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>252</v>
+        <v>540</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
-        <v>413</v>
+        <v>400</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>715</v>
+        <v>423</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>716</v>
+        <v>424</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
-        <v>413</v>
+        <v>400</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>508</v>
+        <v>329</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>509</v>
+        <v>330</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
-        <v>413</v>
+        <v>400</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>266</v>
+        <v>245</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>267</v>
+        <v>246</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
-        <v>413</v>
+        <v>400</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>570</v>
+        <v>700</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>571</v>
+        <v>701</v>
       </c>
       <c r="F58" s="6" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
-        <v>413</v>
+        <v>400</v>
       </c>
       <c r="B59" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="F59" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="C59" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="F59" s="6" t="s">
-        <v>180</v>
-      </c>
       <c r="G59" s="2" t="s">
-        <v>332</v>
+        <v>496</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
-        <v>413</v>
+        <v>400</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>575</v>
+        <v>260</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>577</v>
+        <v>261</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
-        <v>413</v>
+        <v>400</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>415</v>
+        <v>554</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="F61" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+        <v>555</v>
+      </c>
+      <c r="F61" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
-        <v>413</v>
+        <v>400</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>463</v>
+        <v>762</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>718</v>
+        <v>763</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" ht="44" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A63" s="17" t="s">
-        <v>413</v>
-      </c>
-      <c r="B63" s="17" t="s">
-        <v>825</v>
-      </c>
-      <c r="C63" s="17" t="s">
-        <v>826</v>
-      </c>
-      <c r="D63" s="17"/>
-      <c r="E63" s="17"/>
-      <c r="F63" s="21" t="s">
-        <v>303</v>
-      </c>
-      <c r="G63" s="17" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A63" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="F63" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A65" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="F65" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A66" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="F66" s="22" t="s">
+        <v>178</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="73" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A67" s="17" t="s">
+        <v>400</v>
+      </c>
+      <c r="B67" s="17" t="s">
+        <v>451</v>
+      </c>
+      <c r="C67" s="17" t="s">
+        <v>452</v>
+      </c>
+      <c r="D67" s="17" t="s">
+        <v>703</v>
+      </c>
+      <c r="E67" s="17"/>
+      <c r="F67" s="22" t="s">
+        <v>178</v>
+      </c>
+      <c r="G67" s="17" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A68" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="B68" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C64" s="2" t="s">
+      <c r="C68" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F64" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A65" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A66" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F66" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A67" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="F67" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A68" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="B68" s="17" t="s">
-        <v>385</v>
-      </c>
-      <c r="C68" s="17" t="s">
-        <v>386</v>
-      </c>
-      <c r="D68" s="17"/>
-      <c r="E68" s="17"/>
-      <c r="F68" s="21" t="s">
-        <v>303</v>
-      </c>
-      <c r="G68" s="17" t="s">
-        <v>387</v>
+      <c r="F68" s="3" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>779</v>
+        <v>197</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>781</v>
-      </c>
-      <c r="F69" s="4" t="s">
-        <v>100</v>
+        <v>198</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>780</v>
+        <v>803</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>782</v>
-      </c>
-      <c r="F70" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>804</v>
+      </c>
+      <c r="F70" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>654</v>
+        <v>40</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>655</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="F71" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>42</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>181</v>
+        <v>528</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>719</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>720</v>
+        <v>529</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A73" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="F73" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A73" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B73" s="17" t="s">
+        <v>372</v>
+      </c>
+      <c r="C73" s="17" t="s">
+        <v>373</v>
+      </c>
+      <c r="D73" s="17"/>
+      <c r="E73" s="17"/>
+      <c r="F73" s="21" t="s">
+        <v>291</v>
+      </c>
+      <c r="G73" s="17" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>602</v>
+        <v>768</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>601</v>
-      </c>
-      <c r="F74" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>770</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>681</v>
+        <v>769</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>682</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>683</v>
+        <v>771</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>175</v>
+        <v>638</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="F76" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G76" s="2" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
+        <v>639</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>836</v>
+      </c>
+      <c r="F76" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A77" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>593</v>
+        <v>179</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>594</v>
+        <v>704</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>721</v>
-      </c>
-      <c r="F77" s="12" t="s">
-        <v>250</v>
+        <v>705</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.35">
@@ -4585,75 +4662,78 @@
         <v>43</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>44</v>
+        <v>316</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>50</v>
+        <v>317</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>45</v>
+        <v>586</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F79" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G79" s="2" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+        <v>585</v>
+      </c>
+      <c r="F79" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>748</v>
+        <v>666</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>749</v>
-      </c>
-      <c r="F80" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G80" s="2" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
+        <v>667</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>770</v>
+        <v>173</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>771</v>
-      </c>
-      <c r="F81" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>172</v>
+      </c>
+      <c r="F81" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>686</v>
+        <v>577</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>687</v>
-      </c>
-      <c r="F82" s="3" t="s">
-        <v>99</v>
+        <v>578</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>706</v>
+      </c>
+      <c r="F82" s="12" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.35">
@@ -4661,47 +4741,47 @@
         <v>43</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>671</v>
+        <v>44</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>672</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>673</v>
-      </c>
-      <c r="E83" s="2" t="s">
-        <v>203</v>
+        <v>50</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>820</v>
+        <v>45</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>821</v>
-      </c>
-      <c r="F84" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
+        <v>51</v>
+      </c>
+      <c r="F84" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A85" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>160</v>
+        <v>734</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="F85" s="3" t="s">
-        <v>99</v>
+        <v>735</v>
+      </c>
+      <c r="F85" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>736</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.35">
@@ -4709,151 +4789,151 @@
         <v>43</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>657</v>
+        <v>756</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>658</v>
+        <v>757</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>46</v>
+        <v>671</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>722</v>
-      </c>
-      <c r="F87" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>672</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>723</v>
+        <v>656</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>724</v>
-      </c>
-      <c r="F88" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>657</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>512</v>
+        <v>848</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="F89" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="G89" s="2" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
+        <v>849</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>783</v>
+        <v>669</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>784</v>
-      </c>
-      <c r="F90" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+        <v>670</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>725</v>
+        <v>158</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>726</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>758</v>
-      </c>
-      <c r="F91" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>159</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>309</v>
+        <v>46</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="F93" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
+        <v>52</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="F93" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>737</v>
+        <v>708</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>738</v>
-      </c>
-      <c r="F94" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>709</v>
+      </c>
+      <c r="F94" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>47</v>
+        <v>498</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>700</v>
-      </c>
-      <c r="F95" s="3" t="s">
-        <v>99</v>
+        <v>499</v>
+      </c>
+      <c r="F95" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>500</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.35">
@@ -4861,50 +4941,44 @@
         <v>43</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>288</v>
+        <v>772</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="F96" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
+        <v>773</v>
+      </c>
+      <c r="F96" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>169</v>
+        <v>710</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>170</v>
+        <v>711</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>828</v>
-      </c>
-      <c r="F97" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
+        <v>744</v>
+      </c>
+      <c r="F97" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>668</v>
+        <v>630</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>669</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>670</v>
-      </c>
-      <c r="F98" s="4" t="s">
-        <v>100</v>
+        <v>631</v>
+      </c>
+      <c r="F98" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.35">
@@ -4912,13 +4986,13 @@
         <v>43</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>818</v>
+        <v>297</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>819</v>
-      </c>
-      <c r="F99" s="3" t="s">
-        <v>99</v>
+        <v>298</v>
+      </c>
+      <c r="F99" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.35">
@@ -4926,86 +5000,98 @@
         <v>43</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>728</v>
-      </c>
-      <c r="F100" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
+        <v>724</v>
+      </c>
+      <c r="F100" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A101" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>488</v>
+        <v>47</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>489</v>
+        <v>169</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>701</v>
+        <v>685</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>177</v>
+        <v>276</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="F102" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="G102" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
+        <v>277</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="F102" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>762</v>
+        <v>642</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>764</v>
+        <v>643</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>712</v>
       </c>
       <c r="F103" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A104" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="B104" s="2" t="s">
-        <v>763</v>
+        <v>167</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>765</v>
-      </c>
-      <c r="F104" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>168</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="F104" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>710</v>
+        <v>653</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>711</v>
+        <v>654</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>655</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.35">
@@ -5013,27 +5099,27 @@
         <v>43</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>729</v>
+        <v>774</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>730</v>
-      </c>
-      <c r="F106" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>775</v>
+      </c>
+      <c r="F106" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>591</v>
+        <v>850</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>592</v>
-      </c>
-      <c r="F107" s="4" t="s">
-        <v>100</v>
+        <v>851</v>
+      </c>
+      <c r="F107" s="3" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.35">
@@ -5041,12 +5127,12 @@
         <v>43</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>604</v>
+        <v>713</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>605</v>
-      </c>
-      <c r="F108" s="3" t="s">
+        <v>714</v>
+      </c>
+      <c r="F108" s="5" t="s">
         <v>99</v>
       </c>
     </row>
@@ -5055,27 +5141,33 @@
         <v>43</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>746</v>
+        <v>476</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>747</v>
+        <v>477</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>686</v>
       </c>
       <c r="F109" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>595</v>
+        <v>175</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>596</v>
-      </c>
-      <c r="F110" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="F110" s="6" t="s">
         <v>100</v>
+      </c>
+      <c r="G110" s="2" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.35">
@@ -5083,109 +5175,94 @@
         <v>43</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>659</v>
+        <v>748</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>660</v>
-      </c>
-      <c r="F111" s="4" t="s">
-        <v>100</v>
+        <v>750</v>
+      </c>
+      <c r="F111" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A112" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="B112" s="2" t="s">
-        <v>48</v>
+        <v>749</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F112" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
+        <v>751</v>
+      </c>
+      <c r="F112" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A113" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>196</v>
+        <v>695</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>208</v>
+        <v>696</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>49</v>
+        <v>715</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F114" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="G114" s="2" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>716</v>
+      </c>
+      <c r="F114" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A115" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>751</v>
+        <v>575</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>752</v>
-      </c>
-      <c r="F115" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="G115" s="2" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>576</v>
+      </c>
+      <c r="F115" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>744</v>
+        <v>588</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>745</v>
-      </c>
-      <c r="D116" s="2" t="s">
-        <v>759</v>
-      </c>
-      <c r="F116" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>589</v>
+      </c>
+      <c r="F116" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>666</v>
+        <v>732</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>667</v>
-      </c>
-      <c r="D117" s="2" t="s">
-        <v>731</v>
-      </c>
-      <c r="F117" s="14" t="s">
-        <v>258</v>
+        <v>733</v>
+      </c>
+      <c r="F117" s="3" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.35">
@@ -5193,106 +5270,106 @@
         <v>43</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>186</v>
+        <v>579</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>187</v>
+        <v>580</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>578</v>
+        <v>644</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>579</v>
+        <v>645</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>203</v>
+        <v>48</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="D120" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="F120" s="5" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>53</v>
+      </c>
+      <c r="F120" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>678</v>
+        <v>194</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>679</v>
-      </c>
-      <c r="D121" s="2" t="s">
-        <v>680</v>
-      </c>
-      <c r="F121" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
+        <v>202</v>
+      </c>
+      <c r="F121" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A122" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>599</v>
+        <v>49</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>600</v>
-      </c>
-      <c r="D122" s="2" t="s">
-        <v>603</v>
-      </c>
-      <c r="F122" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>54</v>
+      </c>
+      <c r="F122" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="G122" s="2" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A123" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="B123" s="2" t="s">
-        <v>664</v>
+        <v>737</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>665</v>
-      </c>
-      <c r="F123" s="14" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>738</v>
+      </c>
+      <c r="F123" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="G123" s="2" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A124" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>451</v>
+        <v>730</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>452</v>
+        <v>731</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="F124" s="4" t="s">
-        <v>100</v>
+        <v>745</v>
+      </c>
+      <c r="F124" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="125" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5300,27 +5377,30 @@
         <v>43</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>676</v>
+        <v>651</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>677</v>
+        <v>652</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>717</v>
       </c>
       <c r="F125" s="14" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>650</v>
+        <v>184</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>651</v>
+        <v>185</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="127" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5328,13 +5408,13 @@
         <v>43</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>652</v>
+        <v>562</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>653</v>
+        <v>563</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="128" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5342,26 +5422,32 @@
         <v>43</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>573</v>
+        <v>199</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>574</v>
-      </c>
-      <c r="F128" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
+        <v>200</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="F128" s="5" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A129" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>648</v>
+        <v>663</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>649</v>
-      </c>
-      <c r="F129" s="3" t="s">
+        <v>664</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="F129" s="5" t="s">
         <v>99</v>
       </c>
     </row>
@@ -5370,47 +5456,44 @@
         <v>43</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>597</v>
+        <v>583</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>598</v>
-      </c>
-      <c r="E130" s="2" t="s">
-        <v>595</v>
+        <v>584</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>587</v>
       </c>
       <c r="F130" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="131" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A131" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="B131" s="2" t="s">
-        <v>732</v>
+        <v>649</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>733</v>
-      </c>
-      <c r="D131" s="2" t="s">
-        <v>734</v>
-      </c>
-      <c r="F131" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>650</v>
+      </c>
+      <c r="F131" s="14" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A132" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>816</v>
+        <v>439</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>817</v>
+        <v>440</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>441</v>
       </c>
       <c r="F132" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="133" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5418,287 +5501,287 @@
         <v>43</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>703</v>
+        <v>661</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>704</v>
-      </c>
-      <c r="F133" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A134" s="17" t="s">
+        <v>662</v>
+      </c>
+      <c r="F133" s="14" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A134" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B134" s="17" t="s">
-        <v>347</v>
-      </c>
-      <c r="C134" s="17" t="s">
-        <v>348</v>
-      </c>
-      <c r="D134" s="17" t="s">
-        <v>349</v>
-      </c>
-      <c r="E134" s="17"/>
-      <c r="F134" s="21" t="s">
-        <v>303</v>
-      </c>
-      <c r="G134" s="17" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B134" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="F134" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A135" s="2" t="s">
-        <v>275</v>
+        <v>43</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>269</v>
+        <v>636</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="D135" s="2" t="s">
-        <v>702</v>
+        <v>637</v>
       </c>
       <c r="F135" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="136" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A136" s="2" t="s">
-        <v>275</v>
+        <v>43</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>273</v>
+        <v>557</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="D136" s="2" t="s">
-        <v>630</v>
+        <v>558</v>
       </c>
       <c r="F136" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137" s="2" t="s">
-        <v>275</v>
+        <v>43</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>271</v>
+        <v>632</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="F137" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>633</v>
+      </c>
+      <c r="F137" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138" s="2" t="s">
-        <v>275</v>
+        <v>43</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>418</v>
+        <v>581</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="F138" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
+        <v>582</v>
+      </c>
+      <c r="E138" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="F138" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A139" s="2" t="s">
-        <v>275</v>
+        <v>43</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>183</v>
+        <v>718</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="F139" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.35">
+        <v>719</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="F139" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A140" s="2" t="s">
-        <v>275</v>
+        <v>43</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>184</v>
+        <v>846</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>185</v>
+        <v>847</v>
       </c>
       <c r="F140" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A141" s="17" t="s">
-        <v>275</v>
-      </c>
-      <c r="B141" s="17" t="s">
-        <v>188</v>
-      </c>
-      <c r="C141" s="17" t="s">
-        <v>189</v>
-      </c>
-      <c r="D141" s="17"/>
-      <c r="E141" s="17"/>
-      <c r="F141" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="G141" s="17"/>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A142" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B142" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="C142" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="F142" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A141" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="F141" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A142" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="B142" s="17" t="s">
+        <v>334</v>
+      </c>
+      <c r="C142" s="17" t="s">
+        <v>335</v>
+      </c>
+      <c r="D142" s="17" t="s">
+        <v>336</v>
+      </c>
+      <c r="E142" s="17"/>
+      <c r="F142" s="21" t="s">
+        <v>291</v>
+      </c>
+      <c r="G142" s="17" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143" s="2" t="s">
-        <v>55</v>
+        <v>269</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>785</v>
+        <v>263</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>788</v>
-      </c>
-      <c r="F143" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
+        <v>264</v>
+      </c>
+      <c r="D143" s="2" t="s">
+        <v>687</v>
+      </c>
+      <c r="F143" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A144" s="2" t="s">
-        <v>55</v>
+        <v>269</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>786</v>
+        <v>267</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>789</v>
-      </c>
-      <c r="F144" s="5" t="s">
-        <v>101</v>
+        <v>268</v>
+      </c>
+      <c r="D144" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="F144" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145" s="2" t="s">
-        <v>55</v>
+        <v>269</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>787</v>
+        <v>265</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>790</v>
-      </c>
-      <c r="F145" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.35">
+        <v>266</v>
+      </c>
+      <c r="F145" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A146" s="2" t="s">
-        <v>55</v>
+        <v>269</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>472</v>
+        <v>405</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="D146" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="F146" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="F146" s="5" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147" s="2" t="s">
-        <v>55</v>
+        <v>269</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>380</v>
+        <v>181</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="F147" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>180</v>
+      </c>
+      <c r="F147" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148" s="2" t="s">
-        <v>55</v>
+        <v>269</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>56</v>
+        <v>182</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D148" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="F148" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A149" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B149" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="C149" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="F149" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>183</v>
+      </c>
+      <c r="F148" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A149" s="17" t="s">
+        <v>269</v>
+      </c>
+      <c r="B149" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="C149" s="17" t="s">
+        <v>187</v>
+      </c>
+      <c r="D149" s="17"/>
+      <c r="E149" s="17"/>
+      <c r="F149" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="G149" s="17"/>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>776</v>
+        <v>458</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>777</v>
-      </c>
-      <c r="F150" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.35">
+        <v>459</v>
+      </c>
+      <c r="F150" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A151" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>628</v>
+        <v>776</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>629</v>
+        <v>779</v>
       </c>
       <c r="F151" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.35">
@@ -5706,16 +5789,13 @@
         <v>55</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>525</v>
+        <v>777</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>792</v>
-      </c>
-      <c r="E152" s="2" t="s">
-        <v>526</v>
+        <v>780</v>
       </c>
       <c r="F152" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.35">
@@ -5723,13 +5803,13 @@
         <v>55</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>791</v>
+        <v>778</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="F153" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.35">
@@ -5737,13 +5817,16 @@
         <v>55</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>542</v>
+        <v>460</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>543</v>
+        <v>461</v>
+      </c>
+      <c r="D154" s="2" t="s">
+        <v>462</v>
       </c>
       <c r="F154" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.35">
@@ -5751,13 +5834,13 @@
         <v>55</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>606</v>
+        <v>367</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>607</v>
-      </c>
-      <c r="F155" s="4" t="s">
-        <v>100</v>
+        <v>368</v>
+      </c>
+      <c r="F155" s="3" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="156" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5765,16 +5848,16 @@
         <v>55</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F156" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="G156" s="2" t="s">
-        <v>337</v>
+        <v>59</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="F156" s="3" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.35">
@@ -5782,13 +5865,13 @@
         <v>55</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="F157" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="158" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5796,384 +5879,374 @@
         <v>55</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>390</v>
+        <v>765</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="F158" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G158" s="2" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="159" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>766</v>
+      </c>
+      <c r="F158" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>391</v>
+        <v>612</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="F159" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G159" s="2" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="160" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>613</v>
+      </c>
+      <c r="F159" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>392</v>
+        <v>509</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="F160" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G160" s="2" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="161" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>783</v>
+      </c>
+      <c r="E160" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="F160" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>58</v>
+        <v>782</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D161" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F161" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="162" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>767</v>
+      </c>
+      <c r="F161" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>376</v>
+        <v>526</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="D162" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="F162" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="163" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+        <v>527</v>
+      </c>
+      <c r="F162" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>388</v>
+        <v>590</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="F163" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="164" spans="1:7" s="17" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A164" s="17" t="s">
+        <v>591</v>
+      </c>
+      <c r="F163" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A164" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B164" s="17" t="s">
-        <v>441</v>
-      </c>
-      <c r="C164" s="17" t="s">
-        <v>442</v>
-      </c>
-      <c r="F164" s="22" t="s">
-        <v>142</v>
-      </c>
-      <c r="G164" s="17" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="165" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="B164" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C164" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F164" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="G164" s="2" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A165" s="2" t="s">
-        <v>404</v>
+        <v>55</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>406</v>
+        <v>299</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="D165" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="F165" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="166" spans="1:7" s="17" customFormat="1" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A166" s="17" t="s">
-        <v>754</v>
-      </c>
-      <c r="B166" s="17" t="s">
-        <v>755</v>
-      </c>
-      <c r="C166" s="17" t="s">
-        <v>756</v>
-      </c>
-      <c r="D166" s="17" t="s">
-        <v>757</v>
-      </c>
-      <c r="F166" s="19" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.35">
+        <v>300</v>
+      </c>
+      <c r="F165" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A166" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="F166" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G166" s="2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A167" s="2" t="s">
-        <v>357</v>
+        <v>55</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>359</v>
+        <v>378</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="F167" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.35">
+        <v>381</v>
+      </c>
+      <c r="F167" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G167" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A168" s="2" t="s">
-        <v>357</v>
+        <v>55</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>360</v>
+        <v>379</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="F168" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.35">
+        <v>382</v>
+      </c>
+      <c r="F168" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G168" s="2" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A169" s="2" t="s">
-        <v>357</v>
+        <v>55</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>361</v>
+        <v>58</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="F169" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="170" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>61</v>
+      </c>
+      <c r="D169" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F169" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A170" s="2" t="s">
-        <v>357</v>
+        <v>55</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>369</v>
+        <v>327</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>373</v>
+        <v>328</v>
       </c>
       <c r="F170" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="171" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A171" s="2" t="s">
-        <v>357</v>
+        <v>55</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="F171" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A172" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="B172" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="C172" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="F172" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="G172" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
+      </c>
+      <c r="F171" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" s="17" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A172" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="B172" s="17" t="s">
+        <v>428</v>
+      </c>
+      <c r="C172" s="17" t="s">
+        <v>429</v>
+      </c>
+      <c r="F172" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="G172" s="17" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="173" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A173" s="2" t="s">
-        <v>357</v>
+        <v>391</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>807</v>
+        <v>393</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>808</v>
-      </c>
-      <c r="F173" s="6"/>
-      <c r="G173" s="2" t="s">
-        <v>809</v>
-      </c>
-    </row>
-    <row r="174" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A174" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="B174" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="C174" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="F174" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="G174" s="2" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="175" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A175" s="17" t="s">
-        <v>357</v>
-      </c>
-      <c r="B175" s="17" t="s">
-        <v>498</v>
-      </c>
-      <c r="C175" s="17" t="s">
-        <v>499</v>
-      </c>
-      <c r="D175" s="17"/>
-      <c r="E175" s="17"/>
-      <c r="F175" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="G175" s="17"/>
+        <v>394</v>
+      </c>
+      <c r="D173" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="F173" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" s="17" customFormat="1" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A174" s="17" t="s">
+        <v>740</v>
+      </c>
+      <c r="B174" s="17" t="s">
+        <v>741</v>
+      </c>
+      <c r="C174" s="17" t="s">
+        <v>742</v>
+      </c>
+      <c r="D174" s="17" t="s">
+        <v>743</v>
+      </c>
+      <c r="F174" s="19" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A175" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="C175" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="F175" s="5" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176" s="2" t="s">
-        <v>63</v>
+        <v>344</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>206</v>
+        <v>347</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="F176" s="12" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="177" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>354</v>
+      </c>
+      <c r="F176" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177" s="2" t="s">
-        <v>63</v>
+        <v>344</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>518</v>
+        <v>348</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="D177" s="2" t="s">
-        <v>520</v>
-      </c>
-      <c r="F177" s="14" t="s">
-        <v>400</v>
+        <v>355</v>
+      </c>
+      <c r="F177" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="178" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A178" s="2" t="s">
-        <v>63</v>
+        <v>344</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>661</v>
+        <v>349</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>662</v>
+        <v>356</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>663</v>
+        <v>360</v>
       </c>
       <c r="F178" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="179" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A179" s="2" t="s">
-        <v>63</v>
+        <v>344</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>197</v>
+        <v>350</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="E179" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="F179" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G179" s="2" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="180" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>357</v>
+      </c>
+      <c r="F179" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A180" s="2" t="s">
-        <v>63</v>
+        <v>344</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>326</v>
+        <v>351</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="F180" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="181" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A181" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B181" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C181" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F181" s="4" t="s">
-        <v>100</v>
+        <v>358</v>
+      </c>
+      <c r="F180" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="G180" s="2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" s="17" customFormat="1" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A181" s="17" t="s">
+        <v>344</v>
+      </c>
+      <c r="B181" s="17" t="s">
+        <v>352</v>
+      </c>
+      <c r="C181" s="17" t="s">
+        <v>359</v>
+      </c>
+      <c r="F181" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="G181" s="17" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.35">
@@ -6181,13 +6254,16 @@
         <v>63</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>496</v>
+        <v>808</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>497</v>
+        <v>809</v>
+      </c>
+      <c r="D182" s="2" t="s">
+        <v>810</v>
       </c>
       <c r="F182" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.35">
@@ -6195,16 +6271,13 @@
         <v>63</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>65</v>
+        <v>813</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>68</v>
+        <v>814</v>
       </c>
       <c r="F183" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G183" s="2" t="s">
-        <v>345</v>
+        <v>291</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.35">
@@ -6212,13 +6285,13 @@
         <v>63</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>561</v>
+        <v>815</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>562</v>
-      </c>
-      <c r="F184" s="5" t="s">
-        <v>101</v>
+        <v>816</v>
+      </c>
+      <c r="F184" s="16" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.35">
@@ -6226,58 +6299,61 @@
         <v>63</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>760</v>
+        <v>822</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>761</v>
-      </c>
-      <c r="F185" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.35">
+        <v>823</v>
+      </c>
+      <c r="F185" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A186" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>766</v>
+        <v>825</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>767</v>
-      </c>
-      <c r="F186" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="187" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>824</v>
+      </c>
+      <c r="F186" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>515</v>
+        <v>791</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="F187" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="G187" s="2" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.35">
+        <v>793</v>
+      </c>
+      <c r="D187" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="F187" s="12" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A188" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>199</v>
+        <v>502</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="F188" s="4" t="s">
-        <v>100</v>
+        <v>503</v>
+      </c>
+      <c r="D188" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="F188" s="14" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="189" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6285,19 +6361,16 @@
         <v>63</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>810</v>
+        <v>646</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>811</v>
+        <v>647</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>812</v>
-      </c>
-      <c r="F189" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G189" s="2" t="s">
-        <v>813</v>
+        <v>648</v>
+      </c>
+      <c r="F189" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="190" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6305,16 +6378,13 @@
         <v>63</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>66</v>
+        <v>314</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D190" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="F190" s="14" t="s">
-        <v>400</v>
+        <v>315</v>
+      </c>
+      <c r="F190" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.35">
@@ -6322,13 +6392,13 @@
         <v>63</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>190</v>
+        <v>484</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="F191" s="4" t="s">
-        <v>100</v>
+        <v>485</v>
+      </c>
+      <c r="F191" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="192" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6336,41 +6406,44 @@
         <v>63</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>277</v>
+        <v>797</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="F192" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="193" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>798</v>
+      </c>
+      <c r="F192" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A193" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>278</v>
+        <v>64</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="F193" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="194" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>66</v>
+      </c>
+      <c r="F193" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G193" s="2" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A194" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>279</v>
+        <v>799</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="F194" s="4" t="s">
-        <v>100</v>
+        <v>800</v>
+      </c>
+      <c r="F194" s="14" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="195" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6378,13 +6451,13 @@
         <v>63</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>566</v>
+        <v>805</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>567</v>
+        <v>806</v>
       </c>
       <c r="F195" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.35">
@@ -6392,1611 +6465,1828 @@
         <v>63</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>476</v>
+        <v>801</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="F196" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="197" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>802</v>
+      </c>
+      <c r="F196" s="14" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A197" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>492</v>
+        <v>826</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>493</v>
+        <v>827</v>
       </c>
       <c r="F197" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="198" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A198" s="17" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A198" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B198" s="17" t="s">
-        <v>494</v>
-      </c>
-      <c r="C198" s="17" t="s">
-        <v>495</v>
-      </c>
-      <c r="D198" s="17"/>
-      <c r="E198" s="17"/>
-      <c r="F198" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="G198" s="17"/>
+      <c r="B198" s="2" t="s">
+        <v>794</v>
+      </c>
+      <c r="C198" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="D198" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="F198" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="G198" s="2" t="s">
+        <v>796</v>
+      </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A199" s="2" t="s">
-        <v>420</v>
+        <v>63</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>793</v>
+        <v>545</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>794</v>
-      </c>
-      <c r="F199" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="200" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>546</v>
+      </c>
+      <c r="F199" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A200" s="2" t="s">
-        <v>420</v>
+        <v>63</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>558</v>
+        <v>746</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="D200" s="2" t="s">
-        <v>560</v>
-      </c>
-      <c r="F200" s="3" t="s">
-        <v>99</v>
+        <v>747</v>
+      </c>
+      <c r="F200" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A201" s="2" t="s">
-        <v>420</v>
+        <v>63</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>708</v>
+        <v>752</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>709</v>
-      </c>
-      <c r="D201" s="2" t="s">
-        <v>707</v>
-      </c>
-      <c r="F201" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.35">
+        <v>753</v>
+      </c>
+      <c r="F201" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A202" s="2" t="s">
-        <v>420</v>
+        <v>63</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>428</v>
+        <v>861</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="F202" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.35">
+        <v>862</v>
+      </c>
+      <c r="F202" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="G202" s="2" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A203" s="2" t="s">
-        <v>420</v>
+        <v>63</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>430</v>
+        <v>817</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="F203" s="3" t="s">
-        <v>99</v>
+        <v>820</v>
+      </c>
+      <c r="D203" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="F203" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A204" s="2" t="s">
-        <v>420</v>
+        <v>63</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>401</v>
+        <v>195</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="F204" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.35">
+        <v>196</v>
+      </c>
+      <c r="F204" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A205" s="2" t="s">
-        <v>420</v>
+        <v>63</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>432</v>
+        <v>840</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="F205" s="3" t="s">
-        <v>99</v>
+        <v>841</v>
+      </c>
+      <c r="D205" s="2" t="s">
+        <v>842</v>
+      </c>
+      <c r="F205" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G205" s="2" t="s">
+        <v>843</v>
       </c>
     </row>
     <row r="206" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A206" s="2" t="s">
-        <v>420</v>
+        <v>63</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>612</v>
+        <v>65</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>614</v>
+        <v>67</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>613</v>
-      </c>
-      <c r="E206" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="F206" s="3" t="s">
-        <v>99</v>
+        <v>386</v>
+      </c>
+      <c r="F206" s="14" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A207" s="2" t="s">
-        <v>420</v>
+        <v>63</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>434</v>
+        <v>188</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="F207" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.35">
+        <v>189</v>
+      </c>
+      <c r="F207" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A208" s="2" t="s">
-        <v>420</v>
+        <v>63</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>422</v>
+        <v>550</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="F208" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="F208" s="5" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="209" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A209" s="2" t="s">
-        <v>420</v>
+        <v>63</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>529</v>
+        <v>811</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="F209" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G209" s="2" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="210" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>812</v>
+      </c>
+      <c r="F209" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A210" s="2" t="s">
-        <v>420</v>
+        <v>63</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>479</v>
+        <v>464</v>
       </c>
       <c r="C210" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="F210" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A211" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B211" s="2" t="s">
         <v>480</v>
       </c>
-      <c r="D210" s="2" t="s">
+      <c r="C211" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="F210" s="3"/>
-    </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A211" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="B211" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="C211" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="F211" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="G211" s="2" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F211" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A212" s="2" t="s">
-        <v>420</v>
+        <v>63</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>502</v>
+        <v>818</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="E212" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="F212" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.35">
+        <v>819</v>
+      </c>
+      <c r="F212" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A213" s="2" t="s">
-        <v>420</v>
+        <v>63</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>500</v>
+        <v>482</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="F213" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A214" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="B214" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="C214" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="F214" s="5" t="s">
-        <v>101</v>
-      </c>
+        <v>483</v>
+      </c>
+      <c r="F213" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A214" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="B214" s="17" t="s">
+        <v>828</v>
+      </c>
+      <c r="C214" s="17" t="s">
+        <v>829</v>
+      </c>
+      <c r="D214" s="17"/>
+      <c r="E214" s="17"/>
+      <c r="F214" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="G214" s="17"/>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A215" s="2" t="s">
-        <v>420</v>
+        <v>407</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>423</v>
+        <v>784</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="F215" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.35">
+        <v>785</v>
+      </c>
+      <c r="F215" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A216" s="2" t="s">
-        <v>420</v>
+        <v>407</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>468</v>
+        <v>542</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="F216" s="5" t="s">
-        <v>101</v>
+        <v>543</v>
+      </c>
+      <c r="D216" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="F216" s="3" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A217" s="2" t="s">
-        <v>420</v>
+        <v>407</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>540</v>
+        <v>693</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>541</v>
+        <v>694</v>
+      </c>
+      <c r="D217" s="2" t="s">
+        <v>692</v>
       </c>
       <c r="F217" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="218" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A218" s="2" t="s">
-        <v>420</v>
+        <v>407</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>426</v>
+        <v>415</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="F218" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G218" s="2" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="219" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>416</v>
+      </c>
+      <c r="F218" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A219" s="2" t="s">
-        <v>420</v>
+        <v>407</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>568</v>
+        <v>417</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="F219" s="19" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="220" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A220" s="17" t="s">
-        <v>420</v>
-      </c>
-      <c r="B220" s="17" t="s">
-        <v>490</v>
-      </c>
-      <c r="C220" s="17" t="s">
-        <v>491</v>
-      </c>
-      <c r="D220" s="17"/>
-      <c r="E220" s="17"/>
-      <c r="F220" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="G220" s="17"/>
+        <v>418</v>
+      </c>
+      <c r="F219" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A220" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="B220" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="C220" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="F220" s="3" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A221" s="2" t="s">
-        <v>93</v>
+        <v>407</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>209</v>
+        <v>419</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="F221" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.35">
+        <v>420</v>
+      </c>
+      <c r="F221" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A222" s="2" t="s">
-        <v>93</v>
+        <v>407</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>304</v>
+        <v>596</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>305</v>
+        <v>598</v>
+      </c>
+      <c r="D222" s="2" t="s">
+        <v>597</v>
       </c>
       <c r="E222" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="F222" s="12" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="223" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>421</v>
+      </c>
+      <c r="F222" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A223" s="2" t="s">
-        <v>93</v>
+        <v>407</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>211</v>
+        <v>421</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="F223" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="224" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>422</v>
+      </c>
+      <c r="F223" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A224" s="2" t="s">
-        <v>93</v>
+        <v>407</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>213</v>
+        <v>409</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="F224" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G224" s="2" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.35">
+        <v>411</v>
+      </c>
+      <c r="F224" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A225" s="2" t="s">
-        <v>93</v>
+        <v>407</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>215</v>
+        <v>513</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="F225" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.35">
+        <v>514</v>
+      </c>
+      <c r="F225" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G225" s="2" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A226" s="2" t="s">
-        <v>93</v>
+        <v>407</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>94</v>
+        <v>467</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="F226" s="5" t="s">
-        <v>101</v>
-      </c>
+        <v>468</v>
+      </c>
+      <c r="D226" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="F226" s="3"/>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A227" s="2" t="s">
-        <v>93</v>
+        <v>407</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>216</v>
+        <v>511</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="F227" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="228" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>512</v>
+      </c>
+      <c r="F227" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="G227" s="2" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A228" s="2" t="s">
-        <v>93</v>
+        <v>407</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>218</v>
+        <v>488</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="F228" s="12" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="229" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A229" s="17" t="s">
-        <v>93</v>
-      </c>
-      <c r="B229" s="17" t="s">
-        <v>95</v>
-      </c>
-      <c r="C229" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="D229" s="17"/>
-      <c r="E229" s="17"/>
-      <c r="F229" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="G229" s="17"/>
-    </row>
-    <row r="230" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>489</v>
+      </c>
+      <c r="E228" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="F228" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A229" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="B229" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="C229" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="F229" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A230" s="2" t="s">
-        <v>70</v>
+        <v>407</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>71</v>
+        <v>454</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F230" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="G230" s="2" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="231" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>455</v>
+      </c>
+      <c r="F230" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A231" s="2" t="s">
-        <v>70</v>
+        <v>407</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>192</v>
+        <v>410</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="F231" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="G231" s="2" t="s">
-        <v>546</v>
+        <v>412</v>
+      </c>
+      <c r="F231" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A232" s="2" t="s">
-        <v>70</v>
+        <v>407</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>741</v>
+        <v>456</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>742</v>
-      </c>
-      <c r="F232" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="G232" s="2" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="233" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A233" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="B233" s="17" t="s">
-        <v>193</v>
-      </c>
-      <c r="C233" s="17" t="s">
-        <v>195</v>
-      </c>
-      <c r="D233" s="17"/>
-      <c r="E233" s="17"/>
-      <c r="F233" s="22" t="s">
-        <v>142</v>
-      </c>
-      <c r="G233" s="17" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.35">
+        <v>457</v>
+      </c>
+      <c r="F232" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A233" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="B233" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="C233" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="F233" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A234" s="2" t="s">
-        <v>73</v>
+        <v>407</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>631</v>
+        <v>413</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>632</v>
-      </c>
-      <c r="F234" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.35">
+        <v>414</v>
+      </c>
+      <c r="F234" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G234" s="2" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A235" s="2" t="s">
-        <v>73</v>
+        <v>407</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="F235" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A236" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B236" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C236" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F236" s="4" t="s">
-        <v>100</v>
-      </c>
+        <v>553</v>
+      </c>
+      <c r="F235" s="19" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A236" s="17" t="s">
+        <v>407</v>
+      </c>
+      <c r="B236" s="17" t="s">
+        <v>478</v>
+      </c>
+      <c r="C236" s="17" t="s">
+        <v>479</v>
+      </c>
+      <c r="D236" s="17"/>
+      <c r="E236" s="17"/>
+      <c r="F236" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="G236" s="17"/>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A237" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B237" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C237" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="F237" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A238" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B238" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C238" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="E238" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F238" s="12" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A239" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B239" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C239" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="F239" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A240" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B240" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C240" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="F240" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G240" s="2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A241" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B241" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C241" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="F241" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A242" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B242" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C242" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F242" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A243" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B243" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C243" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="F243" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A244" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B244" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C244" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F244" s="12" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A245" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="B245" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="C245" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="D245" s="17"/>
+      <c r="E245" s="17"/>
+      <c r="F245" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="G245" s="17"/>
+    </row>
+    <row r="246" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A246" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B246" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C246" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F246" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="G246" s="2" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A247" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B247" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C247" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="F247" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="G247" s="2" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A248" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B248" s="2" t="s">
+        <v>727</v>
+      </c>
+      <c r="C248" s="2" t="s">
+        <v>728</v>
+      </c>
+      <c r="F248" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="G248" s="2" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A249" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="B249" s="17" t="s">
+        <v>191</v>
+      </c>
+      <c r="C249" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="D249" s="17"/>
+      <c r="E249" s="17"/>
+      <c r="F249" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="G249" s="17" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A250" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B250" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="C250" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="F250" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A251" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B251" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="C251" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="F251" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A252" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B252" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C252" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F252" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A253" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B253" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B237" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C237" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="F237" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="238" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A238" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B238" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="C238" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="F238" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A239" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B239" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="C239" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="F239" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A240" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B240" s="2" t="s">
-        <v>674</v>
-      </c>
-      <c r="C240" s="2" t="s">
-        <v>675</v>
-      </c>
-      <c r="F240" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A241" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B241" s="2" t="s">
-        <v>551</v>
-      </c>
-      <c r="C241" s="2" t="s">
-        <v>552</v>
-      </c>
-      <c r="F241" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A242" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B242" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="C242" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="F242" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A243" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B243" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="C243" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="F243" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="244" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A244" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B244" s="2" t="s">
+      <c r="C253" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F253" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A254" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B254" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="C254" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="F254" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A255" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B255" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="C255" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="F255" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A256" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B256" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="C256" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="F256" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A257" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B257" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="C257" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="F257" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A258" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B258" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C258" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="F258" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A259" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B259" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="C259" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="F259" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A260" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B260" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C260" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="E260" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="F260" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A261" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B261" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="C261" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="F261" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A262" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B262" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="C262" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="F262" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A263" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B263" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="C263" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="F263" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A264" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B264" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C264" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="F264" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A265" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B265" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C265" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F265" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A266" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B266" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="C266" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="D266" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="F266" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A267" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B267" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="C267" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="F267" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A268" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B268" s="2" t="s">
+        <v>844</v>
+      </c>
+      <c r="C268" s="2" t="s">
+        <v>845</v>
+      </c>
+      <c r="F268" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A269" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B269" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="C269" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="F269" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A270" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B270" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="C270" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="F270" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A271" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B271" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="C271" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="F271" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A272" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B272" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="C272" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="F272" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A273" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B273" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C273" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="C244" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="E244" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="F244" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A245" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B245" s="2" t="s">
-        <v>795</v>
-      </c>
-      <c r="C245" s="2" t="s">
-        <v>796</v>
-      </c>
-      <c r="F245" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A246" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B246" s="2" t="s">
-        <v>617</v>
-      </c>
-      <c r="C246" s="2" t="s">
-        <v>618</v>
-      </c>
-      <c r="F246" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A247" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B247" s="2" t="s">
-        <v>619</v>
-      </c>
-      <c r="C247" s="2" t="s">
-        <v>620</v>
-      </c>
-      <c r="F247" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A248" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B248" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="C248" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="F248" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A249" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B249" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="C249" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="F249" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A250" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B250" s="2" t="s">
-        <v>829</v>
-      </c>
-      <c r="C250" s="2" t="s">
-        <v>830</v>
-      </c>
-      <c r="F250" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A251" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B251" s="2" t="s">
-        <v>633</v>
-      </c>
-      <c r="C251" s="2" t="s">
-        <v>634</v>
-      </c>
-      <c r="D251" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="F251" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A252" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B252" s="2" t="s">
-        <v>831</v>
-      </c>
-      <c r="C252" s="2" t="s">
-        <v>832</v>
-      </c>
-      <c r="F252" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A253" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B253" s="2" t="s">
-        <v>621</v>
-      </c>
-      <c r="C253" s="2" t="s">
-        <v>622</v>
-      </c>
-      <c r="F253" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A254" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B254" s="2" t="s">
-        <v>814</v>
-      </c>
-      <c r="C254" s="2" t="s">
-        <v>815</v>
-      </c>
-      <c r="F254" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A255" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B255" s="2" t="s">
-        <v>705</v>
-      </c>
-      <c r="C255" s="2" t="s">
-        <v>706</v>
-      </c>
-      <c r="F255" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A256" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B256" s="2" t="s">
-        <v>636</v>
-      </c>
-      <c r="C256" s="2" t="s">
-        <v>637</v>
-      </c>
-      <c r="F256" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A257" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B257" s="2" t="s">
-        <v>608</v>
-      </c>
-      <c r="C257" s="2" t="s">
-        <v>609</v>
-      </c>
-      <c r="F257" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A258" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B258" s="2" t="s">
-        <v>588</v>
-      </c>
-      <c r="C258" s="2" t="s">
-        <v>589</v>
-      </c>
-      <c r="F258" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A259" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B259" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="C259" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="F259" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="260" spans="1:7" ht="58" x14ac:dyDescent="0.35">
-      <c r="A260" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B260" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="C260" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="F260" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="G260" s="2" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A261" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B261" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C261" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="F261" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A262" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B262" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C262" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F262" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A263" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B263" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C263" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F263" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A264" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B264" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C264" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="F264" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A265" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B265" s="2" t="s">
-        <v>623</v>
-      </c>
-      <c r="C265" s="2" t="s">
-        <v>624</v>
-      </c>
-      <c r="D265" s="2" t="s">
-        <v>625</v>
-      </c>
-      <c r="F265" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A266" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B266" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="C266" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="F266" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A267" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B267" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="C267" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="F267" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="268" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A268" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B268" s="2" t="s">
-        <v>638</v>
-      </c>
-      <c r="C268" s="2" t="s">
-        <v>639</v>
-      </c>
-      <c r="F268" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A269" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B269" s="2" t="s">
-        <v>735</v>
-      </c>
-      <c r="C269" s="2" t="s">
-        <v>736</v>
-      </c>
-      <c r="F269" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A270" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B270" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C270" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="F270" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A271" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B271" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="C271" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="F271" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="272" spans="1:7" ht="58" x14ac:dyDescent="0.35">
-      <c r="A272" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B272" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="C272" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="F272" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G272" s="2" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="273" spans="1:7" ht="58" x14ac:dyDescent="0.35">
-      <c r="A273" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B273" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="C273" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="F273" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G273" s="2" t="s">
-        <v>335</v>
+      <c r="F273" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="274" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A274" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>239</v>
+        <v>273</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="F274" s="16" t="s">
-        <v>303</v>
+        <v>274</v>
+      </c>
+      <c r="F274" s="6" t="s">
+        <v>275</v>
       </c>
       <c r="G274" s="2" t="s">
-        <v>335</v>
+        <v>322</v>
       </c>
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A275" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>230</v>
+        <v>74</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="E275" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="F275" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="276" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>82</v>
+      </c>
+      <c r="F275" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A276" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>688</v>
+        <v>75</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>689</v>
+        <v>83</v>
       </c>
       <c r="F276" s="5" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="277" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A277" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="F277" s="4" t="s">
-        <v>100</v>
+        <v>84</v>
+      </c>
+      <c r="F277" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A278" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>739</v>
+        <v>77</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>740</v>
+        <v>85</v>
       </c>
       <c r="F278" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="279" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A279" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>443</v>
+        <v>607</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="F279" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="G279" s="2" t="s">
-        <v>377</v>
+        <v>608</v>
+      </c>
+      <c r="D279" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="F279" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A280" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>640</v>
+        <v>435</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>641</v>
-      </c>
-      <c r="F280" s="5" t="s">
-        <v>101</v>
+        <v>436</v>
+      </c>
+      <c r="F280" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A281" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>506</v>
+        <v>465</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="F281" s="5" t="s">
-        <v>101</v>
+        <v>466</v>
+      </c>
+      <c r="F281" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="282" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A282" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>772</v>
+        <v>622</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>773</v>
-      </c>
-      <c r="F282" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G282" s="2" t="s">
-        <v>774</v>
+        <v>623</v>
+      </c>
+      <c r="F282" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A283" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>245</v>
+        <v>721</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="F283" s="14" t="s">
-        <v>258</v>
+        <v>722</v>
+      </c>
+      <c r="F283" s="3" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A284" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>298</v>
+        <v>78</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="F284" s="5" t="s">
-        <v>101</v>
+        <v>86</v>
+      </c>
+      <c r="F284" s="3" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A285" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>642</v>
+        <v>531</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>643</v>
-      </c>
-      <c r="F285" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.35">
+        <v>532</v>
+      </c>
+      <c r="F285" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A286" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B286" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C286" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="F286" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G286" s="2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A287" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B287" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C287" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="F287" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G287" s="2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="288" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A288" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B288" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C288" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="C286" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="F286" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A287" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B287" s="2" t="s">
-        <v>626</v>
-      </c>
-      <c r="C287" s="2" t="s">
-        <v>627</v>
-      </c>
-      <c r="F287" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A288" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B288" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="C288" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="F288" s="12" t="s">
-        <v>250</v>
+      <c r="F288" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G288" s="2" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A289" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>523</v>
+        <v>224</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="F289" s="14" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.35">
+        <v>225</v>
+      </c>
+      <c r="E289" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F289" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="290" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A290" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>521</v>
+        <v>673</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>522</v>
-      </c>
-      <c r="E290" s="2" t="s">
-        <v>226</v>
+        <v>674</v>
       </c>
       <c r="F290" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.35">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="291" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A291" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>224</v>
+        <v>79</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="F291" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="292" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>87</v>
+      </c>
+      <c r="F291" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="292" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A292" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>644</v>
+        <v>725</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>645</v>
-      </c>
-      <c r="F292" s="20" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="293" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>726</v>
+      </c>
+      <c r="F292" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="293" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A293" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>583</v>
+        <v>430</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="F293" s="3" t="s">
-        <v>99</v>
+        <v>431</v>
+      </c>
+      <c r="F293" s="6" t="s">
+        <v>140</v>
       </c>
       <c r="G293" s="2" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="294" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="294" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A294" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>584</v>
+        <v>624</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>587</v>
-      </c>
-      <c r="F294" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G294" s="2" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="295" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A295" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="B295" s="17" t="s">
-        <v>306</v>
-      </c>
-      <c r="C295" s="17" t="s">
-        <v>307</v>
-      </c>
-      <c r="D295" s="17"/>
-      <c r="E295" s="17"/>
-      <c r="F295" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="G295" s="17"/>
+        <v>625</v>
+      </c>
+      <c r="F294" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="295" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A295" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B295" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="C295" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="F295" s="5" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="296" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A296" s="2" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>91</v>
+        <v>758</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="D296" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="F296" s="5" t="s">
-        <v>101</v>
+        <v>759</v>
+      </c>
+      <c r="F296" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G296" s="2" t="s">
+        <v>760</v>
       </c>
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A297" s="2" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="D297" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="F297" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="298" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>240</v>
+      </c>
+      <c r="F297" s="14" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="298" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A298" s="2" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>247</v>
+        <v>286</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="D298" s="2" t="s">
-        <v>249</v>
+        <v>285</v>
       </c>
       <c r="F298" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="299" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="299" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A299" s="2" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>797</v>
+        <v>626</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>798</v>
-      </c>
-      <c r="F299" s="25" t="s">
-        <v>799</v>
+        <v>627</v>
+      </c>
+      <c r="F299" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A300" s="2" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>351</v>
+        <v>228</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="F300" s="4" t="s">
-        <v>100</v>
+        <v>229</v>
+      </c>
+      <c r="F300" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A301" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B301" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="C301" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="F301" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="302" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A302" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B302" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C302" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="F302" s="12" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="303" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A303" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B303" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="C303" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="F303" s="14" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="304" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A304" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B304" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="C304" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="E304" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F304" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="305" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A305" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B305" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C305" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="F305" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="306" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A306" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B306" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="C306" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="F306" s="20" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="307" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A307" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B307" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="C307" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="F307" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="G307" s="2" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="308" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A308" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B308" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="C308" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="F308" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G308" s="2" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="309" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A309" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="B309" s="17" t="s">
+        <v>294</v>
+      </c>
+      <c r="C309" s="17" t="s">
+        <v>295</v>
+      </c>
+      <c r="D309" s="17"/>
+      <c r="E309" s="17"/>
+      <c r="F309" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="G309" s="17"/>
+    </row>
+    <row r="310" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A310" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B310" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C310" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B301" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="C301" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="D301" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="F301" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="302" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A302" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="B302" s="17" t="s">
-        <v>291</v>
-      </c>
-      <c r="C302" s="17" t="s">
-        <v>292</v>
-      </c>
-      <c r="D302" s="17" t="s">
-        <v>308</v>
-      </c>
-      <c r="E302" s="17"/>
-      <c r="F302" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="G302" s="17"/>
+      <c r="D310" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="F310" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="311" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A311" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B311" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C311" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D311" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="F311" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="312" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A312" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B312" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C312" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="D312" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="F312" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="313" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A313" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B313" s="2" t="s">
+        <v>788</v>
+      </c>
+      <c r="C313" s="2" t="s">
+        <v>789</v>
+      </c>
+      <c r="F313" s="25" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="314" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A314" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B314" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C314" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="F314" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="315" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A315" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B315" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="C315" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="D315" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="F315" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="316" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A316" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="B316" s="17" t="s">
+        <v>279</v>
+      </c>
+      <c r="C316" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="D316" s="17" t="s">
+        <v>296</v>
+      </c>
+      <c r="E316" s="17"/>
+      <c r="F316" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="G316" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8018,7 +8308,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
@@ -8026,7 +8316,7 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -8034,7 +8324,7 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -8042,31 +8332,31 @@
         <v>36</v>
       </c>
       <c r="B4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>413</v>
+        <v>400</v>
       </c>
       <c r="B6" t="s">
-        <v>414</v>
+        <v>401</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>484</v>
+        <v>472</v>
       </c>
       <c r="B7" t="s">
-        <v>485</v>
+        <v>473</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
@@ -8074,7 +8364,7 @@
         <v>38</v>
       </c>
       <c r="B8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
@@ -8082,15 +8372,15 @@
         <v>43</v>
       </c>
       <c r="B9" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="B10" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
@@ -8098,23 +8388,23 @@
         <v>55</v>
       </c>
       <c r="B11" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>404</v>
+        <v>391</v>
       </c>
       <c r="B12" t="s">
-        <v>405</v>
+        <v>392</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>357</v>
+        <v>344</v>
       </c>
       <c r="B13" t="s">
-        <v>358</v>
+        <v>345</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
@@ -8122,47 +8412,47 @@
         <v>63</v>
       </c>
       <c r="B14" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>420</v>
+        <v>407</v>
       </c>
       <c r="B15" t="s">
-        <v>421</v>
+        <v>408</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B16" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B18" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B19" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/InputData/acronym-key.xlsx
+++ b/InputData/acronym-key.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanO'Brien\Models\EPS\US\eps-us\InputData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0106C665-AB98-46AA-99A6-AC85633E64FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9F5458D-FD54-4D41-8C5F-134816A8CA9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-4275" yWindow="-13455" windowWidth="17325" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1495" uniqueCount="863">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1440" uniqueCount="835">
   <si>
     <t>Top Level Folder</t>
   </si>
@@ -226,12 +226,18 @@
     <t>indst</t>
   </si>
   <si>
+    <t>CtIEPpUESoS</t>
+  </si>
+  <si>
     <t>FLRbI</t>
   </si>
   <si>
     <t>PERAC</t>
   </si>
   <si>
+    <t>Cost to Implement Efficiency Policy per Unit Energy Saved or Shifted</t>
+  </si>
+  <si>
     <t>Foreign Leakage Rate by Industry</t>
   </si>
   <si>
@@ -619,6 +625,12 @@
     <t>MPPC</t>
   </si>
   <si>
+    <t>BPoIFUfE</t>
+  </si>
+  <si>
+    <t>BAU Proportion of Industrial Fuel Used for Energy</t>
+  </si>
+  <si>
     <t>MHV</t>
   </si>
   <si>
@@ -640,6 +652,12 @@
     <t>BAU RPS Qualifying Source Definitions, RPS Qualifying Source Definitions</t>
   </si>
   <si>
+    <t>BIFUbC</t>
+  </si>
+  <si>
+    <t>BAU Industrial Fuel Use before CCS</t>
+  </si>
+  <si>
     <t>Minimum Power Plant Capacity</t>
   </si>
   <si>
@@ -847,6 +865,24 @@
     <t>Endogenous Learning</t>
   </si>
   <si>
+    <t>PPRiFUfERoIF</t>
+  </si>
+  <si>
+    <t>PPRiFUfICaWHR</t>
+  </si>
+  <si>
+    <t>PPRiFUfIIaIoE</t>
+  </si>
+  <si>
+    <t>Potential Perc Reduction in Fuel Use from Early Retirement of Inefficient Facilities</t>
+  </si>
+  <si>
+    <t>Potential Perc Reduction in Fuel Use from Increased Cogen and Waste Heat Recovery</t>
+  </si>
+  <si>
+    <t>Potential Perc Reduction in Fuel Use from Improved Installation and Integration of Eqpt</t>
+  </si>
+  <si>
     <t>BAADTbVT</t>
   </si>
   <si>
@@ -1015,6 +1051,9 @@
     <t>medium (n/a for RPS Qualifying Source Definitions, as it is a policy lever)</t>
   </si>
   <si>
+    <t>You are including fuel used as a feedstock (not burned for energy) in indst/BIFUbC (otherwise set to zero)</t>
+  </si>
+  <si>
     <t>Pollutant Emissions Intensity Improvement Rate</t>
   </si>
   <si>
@@ -1336,9 +1375,6 @@
     <t>Quantization Size for Pollutants</t>
   </si>
   <si>
-    <t>BAU Imported Electricity, BAU Exported Electricity, Imported Electricity Price, BAU Exported Electricity Price</t>
-  </si>
-  <si>
     <t>EVCC</t>
   </si>
   <si>
@@ -1492,6 +1528,12 @@
     <t>Elasticities of Demand for Industrial Products</t>
   </si>
   <si>
+    <t>SoHPCCbRIC</t>
+  </si>
+  <si>
+    <t>Share of Hydrogen Production Capital Costs by Recipient ISIC Code</t>
+  </si>
+  <si>
     <t>HSR</t>
   </si>
   <si>
@@ -1537,6 +1579,12 @@
     <t>You wish to switch from the BAU plant retirement schedule to an alternative schedule you have specified in input data (rather than using the early retirement policy lever, which accelerates retirements and is additive to the BAU retirements)</t>
   </si>
   <si>
+    <t>IFStFS</t>
+  </si>
+  <si>
+    <t>Industrial Fuels Subject to Fuel Shifting</t>
+  </si>
+  <si>
     <t>You wish for the industrial fuel shifting policy lever to affect a different set of source (BAU) fuel types than the default set (which consists of the fossil fuels).</t>
   </si>
   <si>
@@ -1954,18 +2002,15 @@
     <t>BAU Cost of Electricity Sector Capital</t>
   </si>
   <si>
+    <t>BAU Cost of Electricity Sector Capital for Power Plants, BAU Cost of Electricity Sector Capital for Other Investments</t>
+  </si>
+  <si>
     <t>BZECfNP</t>
   </si>
   <si>
     <t>BAU Zero Emis Credit for Nuc Plants</t>
   </si>
   <si>
-    <t>EDWP</t>
-  </si>
-  <si>
-    <t>Electricity Dispatch Weibull Parameters</t>
-  </si>
-  <si>
     <t>MLfPPR</t>
   </si>
   <si>
@@ -2041,10 +2086,10 @@
     <t>Fraction of EVs Used for Grid Balancing on Average Day, Fraction of EV Battery Capacity Used for Grid Balancing when EV is Used for Grid Balancing</t>
   </si>
   <si>
-    <t>BSpUESttGbGB</t>
-  </si>
-  <si>
-    <t>BAU Subsidy per Unit Electricity Supplied to the Grid by Grid Batteries</t>
+    <t>CCSTaSC</t>
+  </si>
+  <si>
+    <t>CCS Transportation and Storage Cost</t>
   </si>
   <si>
     <t>BPSpUGBCD</t>
@@ -2170,9 +2215,6 @@
     <t>Capacity Supply Curve</t>
   </si>
   <si>
-    <t>Electricity Dispatch Weibull Parameter A, Electricity Dispatch Weibull Parameter B</t>
-  </si>
-  <si>
     <t>GBCGpUNR</t>
   </si>
   <si>
@@ -2320,15 +2362,6 @@
     <t>STfECCE</t>
   </si>
   <si>
-    <t>BUCMfNCR</t>
-  </si>
-  <si>
-    <t>Boolean Use Capacity Market for New Capacity Revenue</t>
-  </si>
-  <si>
-    <t>You wish the electricity sector to only collect capacity costs for new capacity and not pay them out to all resources in the market.</t>
-  </si>
-  <si>
     <t>FoICbCTBA</t>
   </si>
   <si>
@@ -2356,12 +2389,6 @@
     <t>Cap Ret per Unit Net Loss</t>
   </si>
   <si>
-    <t>ESUfRaLCD</t>
-  </si>
-  <si>
-    <t>Elec Sources Used for Rlbty and Lst Cst Dsptch</t>
-  </si>
-  <si>
     <t>BFoICbCTBA</t>
   </si>
   <si>
@@ -2407,144 +2434,6 @@
     <t>do not edit - QC file to automatically check specified files</t>
   </si>
   <si>
-    <t>BIFU</t>
-  </si>
-  <si>
-    <t>BAU Industrial Fuel Use for Energy, BAU Industrial Fuel Use as Feedstock</t>
-  </si>
-  <si>
-    <t>BAU Industrial Fuel Use</t>
-  </si>
-  <si>
-    <t>IESD</t>
-  </si>
-  <si>
-    <t>Industrial Equipment Survival Data</t>
-  </si>
-  <si>
-    <t>"Start Year Share of Industrial Equipment by Vintage" must be updated if changing the first simulated year (Initial Time)</t>
-  </si>
-  <si>
-    <t>EoIEECwEC</t>
-  </si>
-  <si>
-    <t>Elasticity of Industrial Equipment Energy Consumption with respect to Energy Cost</t>
-  </si>
-  <si>
-    <t>FYIESM</t>
-  </si>
-  <si>
-    <t>Final Year Industrial Equipment Shareweight Minimums</t>
-  </si>
-  <si>
-    <t>IELC</t>
-  </si>
-  <si>
-    <t>Industrial Equipment Logit Coefficient</t>
-  </si>
-  <si>
-    <t>CECpUES</t>
-  </si>
-  <si>
-    <t>CHP Equipment Cost per Unit Energy Shifted</t>
-  </si>
-  <si>
-    <t>IECCpUAEU</t>
-  </si>
-  <si>
-    <t>Industrial Equipment Capital Cost per Unit Annual Energy Use</t>
-  </si>
-  <si>
-    <t>Start Year Share of Industrial Equipment by Vintage, Retiring Fraction of Industrial Equipment Retiring by Age, Average Age at Which Equipment Retires</t>
-  </si>
-  <si>
-    <t>BCoISC</t>
-  </si>
-  <si>
-    <t>BAU Cost of Industry Sector Capital</t>
-  </si>
-  <si>
-    <t>Weighted Average Cost of Capital by Industry, Risk Premium for Equity</t>
-  </si>
-  <si>
-    <t>RPFfFISCC</t>
-  </si>
-  <si>
-    <t>Repayment Period for Financed Industry Sector Capital Costs</t>
-  </si>
-  <si>
-    <t>BCHPD</t>
-  </si>
-  <si>
-    <t>BAU Clean Heat PTC Duration</t>
-  </si>
-  <si>
-    <t>BCHPR</t>
-  </si>
-  <si>
-    <t>BAU Clean Heat PTC Rate</t>
-  </si>
-  <si>
-    <t>IFTQfS</t>
-  </si>
-  <si>
-    <t>SoFCTiBoSFbI</t>
-  </si>
-  <si>
-    <t>Share of Fuel Consumption that is Byproduct or Secondary Fuel by Industry</t>
-  </si>
-  <si>
-    <t>Industrial Fuels Qualifying for Support</t>
-  </si>
-  <si>
-    <t>Industrial Fuels Qualifying for PTC, Industrial Fuels Qualifying for ITC, Industrial Fuels Qualifying for Loans</t>
-  </si>
-  <si>
-    <t>BIEEI</t>
-  </si>
-  <si>
-    <t>BAU Industrial Equipment Efficiency Improvement</t>
-  </si>
-  <si>
-    <t>BAU Industrial Energy Use Reduction from Process Efficiency Improvements</t>
-  </si>
-  <si>
-    <t>BIEURfPEI</t>
-  </si>
-  <si>
-    <t>IEMUEF</t>
-  </si>
-  <si>
-    <t>Industrial Equipment Minimum Unit Energy Factor</t>
-  </si>
-  <si>
-    <t>SYIEUEFbIPaF</t>
-  </si>
-  <si>
-    <t>Start Year Industrial Equipment Unit Energy Factor by Industrial Process and Fuel</t>
-  </si>
-  <si>
-    <t>FYIbFP</t>
-  </si>
-  <si>
-    <t>First Year Impacted by Future Policies</t>
-  </si>
-  <si>
-    <t>2025 ends // or // you wish to model the impact of a policy package that will be passed in years after the present year (e.g., what if the next administration does XYZ)</t>
-  </si>
-  <si>
-    <t>CCSTaSCaS</t>
-  </si>
-  <si>
-    <t>CCS Transportation and Storage Cost and Subsidies</t>
-  </si>
-  <si>
-    <t>Repayment Period for Financing Buildings Sector Capital Costs</t>
-  </si>
-  <si>
-    <t>BAU Cost of Electricity Sector Capital for Power Plants, BAU Cost of Electricity Sector Capital for Other Investments, BAU Cost of Electricity Sector Capital for Distributed Solar Investments</t>
-  </si>
-  <si>
     <t>CiDESCTY</t>
   </si>
   <si>
@@ -2554,6 +2443,27 @@
     <t>You plan on using a policy mandated change in distributed solar capacity additions</t>
   </si>
   <si>
+    <t>NBICP</t>
+  </si>
+  <si>
+    <t>Non BAU Industry CCS Parameters</t>
+  </si>
+  <si>
+    <t>Fraction of CCS Potential Achieved by Industry Energy, Fraction of CCS Potential Achieved by Industry Process, CCS Subsidies</t>
+  </si>
+  <si>
+    <t>You wish to use a policy lever to testalternate CCS subsidies for industries</t>
+  </si>
+  <si>
+    <t>NBRHPF</t>
+  </si>
+  <si>
+    <t>Non BAU Recipient Hydrogen Pathway Fractions</t>
+  </si>
+  <si>
+    <t>You wish for the non BAU hydrogen pathway shifting policy to shift hydrogen production to a pathway other than electrolysis</t>
+  </si>
+  <si>
     <t>PEAAC</t>
   </si>
   <si>
@@ -2578,49 +2488,55 @@
     <t>Time Adjusted Capacity Factor Multiplier for Plants Built This Year</t>
   </si>
   <si>
+    <t>FoGBPD</t>
+  </si>
+  <si>
+    <t>Fraction of Grid Batteries Produced Domestically</t>
+  </si>
+  <si>
     <t>BSfGBP</t>
   </si>
   <si>
     <t>BAU Subsidy for Grid Battery Production</t>
   </si>
   <si>
-    <t>FoGBPD</t>
-  </si>
-  <si>
-    <t>Fraction of Grid Batteries Produced Domestically</t>
-  </si>
-  <si>
-    <t>NBICS</t>
-  </si>
-  <si>
-    <t>Non BAU Industry CCS Subsidy</t>
-  </si>
-  <si>
-    <t>You plan on using the non-BAU CCS subsidy boolean lever</t>
-  </si>
-  <si>
-    <t>CECRCbI</t>
-  </si>
-  <si>
-    <t>Cost Effective CCS Retrofit Capacity by Industry</t>
-  </si>
-  <si>
-    <t>SoCECRCSiaY</t>
-  </si>
-  <si>
-    <t>Share of Cost Effective CCS Retrofit Construction Started in a Year</t>
-  </si>
-  <si>
-    <t>CRDT</t>
-  </si>
-  <si>
-    <t>CCS Retrofit Deployment Time</t>
-  </si>
-  <si>
-    <t>IFStE</t>
-  </si>
-  <si>
-    <t>Industrial Fuels Subject to Electrification</t>
+    <t>BEEEfEPS</t>
+  </si>
+  <si>
+    <t>Boolean Exclude Electricity Exports from Elec Portfolio Stds</t>
+  </si>
+  <si>
+    <t>You wish to change the default behavior or whether electricity exports are included or excluded in RPS and CES policies.</t>
+  </si>
+  <si>
+    <t>MV</t>
+  </si>
+  <si>
+    <t>Modeled Vintages</t>
+  </si>
+  <si>
+    <t>You are using a different model start year than the US EPS (this file should note which vintages are for historical years rather than modeled years)</t>
+  </si>
+  <si>
+    <t>BAU Imported Electricity, BAU Exported Electricity, Imported Electricity Price</t>
+  </si>
+  <si>
+    <t>BPM</t>
+  </si>
+  <si>
+    <t>Battery Pack Markup</t>
+  </si>
+  <si>
+    <t>BPPM</t>
+  </si>
+  <si>
+    <t>Battery Pack Price Multiplier</t>
+  </si>
+  <si>
+    <t>UFDfGBS</t>
+  </si>
+  <si>
+    <t>Usage Factor Discount for Grid Battery Storage</t>
   </si>
 </sst>
 </file>
@@ -3109,319 +3025,319 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="8" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B19" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
-        <v>287</v>
+        <v>299</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
-        <v>289</v>
+        <v>301</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B26" s="13" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="C26" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C27" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C28" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="10" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B30" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B31" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B32" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B33" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B34" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B35" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B36" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B37" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" s="9" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B39" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B40" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B41" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B42" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B43" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B44" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B45" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B46" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" s="15" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="B48" s="15"/>
       <c r="C48" s="15"/>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B49" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B50" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B51" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B52" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B53" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B54" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B55" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" s="11" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B57" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B58" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B59" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B60" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" s="7" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
   </sheetData>
@@ -3432,7 +3348,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G316"/>
+  <dimension ref="A1:G303"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.54296875" style="2" customWidth="1"/>
@@ -3459,13 +3375,13 @@
         <v>3</v>
       </c>
       <c r="E1" s="23" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
       <c r="F1" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G1" s="23" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
@@ -3473,18 +3389,18 @@
         <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>521</v>
+        <v>537</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>522</v>
+        <v>538</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G2" s="24" t="s">
-        <v>523</v>
+        <v>539</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -3492,16 +3408,16 @@
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>518</v>
+        <v>534</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>519</v>
+        <v>535</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>520</v>
+        <v>536</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
@@ -3509,13 +3425,13 @@
         <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>449</v>
+        <v>461</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -3523,16 +3439,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>564</v>
+        <v>580</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>565</v>
+        <v>581</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>566</v>
+        <v>582</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
@@ -3546,7 +3462,7 @@
         <v>8</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3554,15 +3470,15 @@
         <v>4</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D7" s="17"/>
       <c r="E7" s="17"/>
       <c r="F7" s="18" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G7" s="17"/>
     </row>
@@ -3577,7 +3493,7 @@
         <v>23</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
@@ -3591,7 +3507,7 @@
         <v>24</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
@@ -3599,13 +3515,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>697</v>
+        <v>712</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>698</v>
+        <v>713</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
@@ -3619,10 +3535,10 @@
         <v>25</v>
       </c>
       <c r="F11" s="16" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>304</v>
+        <v>316</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
@@ -3630,13 +3546,13 @@
         <v>9</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>594</v>
+        <v>610</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>595</v>
+        <v>611</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
@@ -3644,16 +3560,16 @@
         <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>369</v>
+        <v>382</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>370</v>
+        <v>383</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>371</v>
+        <v>384</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
@@ -3667,7 +3583,7 @@
         <v>26</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -3675,16 +3591,16 @@
         <v>9</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>837</v>
+        <v>800</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>838</v>
+        <v>801</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>839</v>
+        <v>802</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -3692,16 +3608,16 @@
         <v>9</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
@@ -3715,7 +3631,7 @@
         <v>27</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
@@ -3729,7 +3645,7 @@
         <v>28</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
@@ -3743,7 +3659,7 @@
         <v>29</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -3751,13 +3667,13 @@
         <v>9</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
@@ -3771,7 +3687,7 @@
         <v>30</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -3779,13 +3695,13 @@
         <v>9</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>470</v>
+        <v>482</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>471</v>
+        <v>483</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
@@ -3793,13 +3709,13 @@
         <v>9</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>754</v>
+        <v>768</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>755</v>
+        <v>769</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -3813,10 +3729,10 @@
         <v>31</v>
       </c>
       <c r="F24" s="16" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>304</v>
+        <v>316</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -3830,7 +3746,7 @@
         <v>32</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -3844,10 +3760,10 @@
         <v>33</v>
       </c>
       <c r="F26" s="16" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -3861,7 +3777,7 @@
         <v>34</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -3875,7 +3791,7 @@
         <v>35</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -3883,61 +3799,61 @@
         <v>9</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>341</v>
+        <v>354</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>342</v>
+        <v>355</v>
       </c>
       <c r="F29" s="16" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>562</v>
+        <v>449</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>835</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+        <v>450</v>
+      </c>
+      <c r="F30" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>437</v>
+        <v>454</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="F31" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>455</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>442</v>
+        <v>504</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>98</v>
+        <v>505</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
@@ -3945,13 +3861,13 @@
         <v>9</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>490</v>
+        <v>243</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="F33" s="5" t="s">
-        <v>99</v>
+        <v>244</v>
+      </c>
+      <c r="F33" s="14" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
@@ -3959,13 +3875,13 @@
         <v>9</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>237</v>
+        <v>486</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="F34" s="14" t="s">
-        <v>252</v>
+        <v>487</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
@@ -3973,688 +3889,701 @@
         <v>9</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>474</v>
+        <v>458</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A36" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F35" s="12" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F36" s="12" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="B37" s="17" t="s">
-        <v>444</v>
-      </c>
-      <c r="C37" s="17" t="s">
-        <v>445</v>
-      </c>
-      <c r="D37" s="17"/>
-      <c r="E37" s="17" t="s">
-        <v>162</v>
-      </c>
-      <c r="F37" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="G37" s="17"/>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B36" s="17" t="s">
+        <v>456</v>
+      </c>
+      <c r="C36" s="17" t="s">
+        <v>457</v>
+      </c>
+      <c r="D36" s="17"/>
+      <c r="E36" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="F36" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="G36" s="17"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A37" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>599</v>
+        <v>691</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>600</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>692</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>676</v>
+        <v>695</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>677</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>678</v>
-      </c>
-      <c r="F39" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+        <v>696</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="116" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>680</v>
+        <v>37</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>681</v>
-      </c>
-      <c r="F40" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="116" x14ac:dyDescent="0.35">
+        <v>417</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>37</v>
+        <v>409</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>679</v>
+        <v>690</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>396</v>
+        <v>684</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>675</v>
+        <v>685</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A43" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>833</v>
+        <v>803</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>834</v>
-      </c>
-      <c r="F43" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+        <v>804</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="F43" s="21" t="s">
+        <v>303</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>855</v>
+        <v>698</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>856</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A45" s="2" t="s">
+        <v>699</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" s="17" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A45" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>859</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>860</v>
-      </c>
-      <c r="F45" s="4" t="s">
-        <v>98</v>
+      <c r="B45" s="17" t="s">
+        <v>775</v>
+      </c>
+      <c r="C45" s="17" t="s">
+        <v>697</v>
+      </c>
+      <c r="F45" s="20" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
-        <v>36</v>
+        <v>172</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>852</v>
+        <v>5</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>853</v>
-      </c>
-      <c r="F46" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>854</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A47" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>857</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>858</v>
-      </c>
-      <c r="F47" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A48" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>683</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>684</v>
-      </c>
-      <c r="F48" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" s="17" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="B49" s="17" t="s">
-        <v>761</v>
-      </c>
-      <c r="C49" s="17" t="s">
-        <v>682</v>
-      </c>
-      <c r="F49" s="20" t="s">
-        <v>98</v>
+        <v>6</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A47" s="17" t="s">
+        <v>172</v>
+      </c>
+      <c r="B47" s="17" t="s">
+        <v>439</v>
+      </c>
+      <c r="C47" s="17" t="s">
+        <v>440</v>
+      </c>
+      <c r="D47" s="17"/>
+      <c r="E47" s="17"/>
+      <c r="F47" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="G47" s="17" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A48" s="17" t="s">
+        <v>484</v>
+      </c>
+      <c r="B48" s="17" t="s">
+        <v>445</v>
+      </c>
+      <c r="C48" s="17" t="s">
+        <v>446</v>
+      </c>
+      <c r="D48" s="17"/>
+      <c r="E48" s="17"/>
+      <c r="F48" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="G48" s="17" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A49" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="F49" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
-        <v>170</v>
+        <v>413</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>5</v>
+        <v>555</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F50" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="17" t="s">
-        <v>170</v>
-      </c>
-      <c r="B51" s="17" t="s">
-        <v>426</v>
-      </c>
-      <c r="C51" s="17" t="s">
-        <v>427</v>
-      </c>
-      <c r="D51" s="17"/>
-      <c r="E51" s="17"/>
-      <c r="F51" s="22" t="s">
-        <v>140</v>
-      </c>
-      <c r="G51" s="17" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="17" t="s">
-        <v>472</v>
-      </c>
-      <c r="B52" s="17" t="s">
-        <v>432</v>
-      </c>
-      <c r="C52" s="17" t="s">
-        <v>433</v>
-      </c>
-      <c r="D52" s="17"/>
-      <c r="E52" s="17"/>
-      <c r="F52" s="22" t="s">
-        <v>140</v>
-      </c>
-      <c r="G52" s="17" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>556</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A51" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="F51" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A52" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>822</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>823</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
-        <v>400</v>
+        <v>413</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>312</v>
+        <v>342</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>313</v>
+        <v>343</v>
       </c>
       <c r="F53" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A54" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A55" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>715</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="F55" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A56" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A57" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="F57" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A58" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="F58" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A59" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="B59" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="G53" s="2" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A54" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="F54" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="G54" s="2" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" ht="58" x14ac:dyDescent="0.35">
-      <c r="A55" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="F55" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="G55" s="2" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A56" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="F56" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="G56" s="2" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A57" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="F57" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="G57" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A58" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>700</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>701</v>
-      </c>
-      <c r="F58" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="G58" s="2" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="58" x14ac:dyDescent="0.35">
-      <c r="A59" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>494</v>
-      </c>
       <c r="C59" s="2" t="s">
-        <v>495</v>
+        <v>179</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>496</v>
+        <v>332</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
-        <v>400</v>
+        <v>413</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>260</v>
+        <v>575</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>261</v>
+        <v>577</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
-        <v>400</v>
+        <v>413</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>554</v>
+        <v>415</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="F61" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="G61" s="2" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>416</v>
+      </c>
+      <c r="F61" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
-        <v>400</v>
+        <v>413</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>762</v>
+        <v>463</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>763</v>
+        <v>464</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>718</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A63" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="F63" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="G63" s="2" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A63" s="17" t="s">
+        <v>413</v>
+      </c>
+      <c r="B63" s="17" t="s">
+        <v>825</v>
+      </c>
+      <c r="C63" s="17" t="s">
+        <v>826</v>
+      </c>
+      <c r="D63" s="17"/>
+      <c r="E63" s="17"/>
+      <c r="F63" s="21" t="s">
+        <v>303</v>
+      </c>
+      <c r="G63" s="17" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
-        <v>400</v>
+        <v>38</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>559</v>
+        <v>39</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>561</v>
-      </c>
-      <c r="F64" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="G64" s="2" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>41</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
-        <v>400</v>
+        <v>38</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>402</v>
+        <v>201</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="F65" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="F65" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
-        <v>400</v>
+        <v>38</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>830</v>
+        <v>40</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>831</v>
-      </c>
-      <c r="F66" s="22" t="s">
-        <v>178</v>
-      </c>
-      <c r="G66" s="2" t="s">
-        <v>832</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" ht="73" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A67" s="17" t="s">
-        <v>400</v>
-      </c>
-      <c r="B67" s="17" t="s">
-        <v>451</v>
-      </c>
-      <c r="C67" s="17" t="s">
-        <v>452</v>
-      </c>
-      <c r="D67" s="17" t="s">
-        <v>703</v>
-      </c>
-      <c r="E67" s="17"/>
-      <c r="F67" s="22" t="s">
-        <v>178</v>
-      </c>
-      <c r="G67" s="17" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A68" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A67" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B68" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F68" s="3" t="s">
-        <v>97</v>
+      <c r="B67" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A68" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B68" s="17" t="s">
+        <v>385</v>
+      </c>
+      <c r="C68" s="17" t="s">
+        <v>386</v>
+      </c>
+      <c r="D68" s="17"/>
+      <c r="E68" s="17"/>
+      <c r="F68" s="21" t="s">
+        <v>303</v>
+      </c>
+      <c r="G68" s="17" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>197</v>
+        <v>779</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="F69" s="3" t="s">
-        <v>97</v>
+        <v>781</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>803</v>
+        <v>780</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>804</v>
-      </c>
-      <c r="F70" s="5" t="s">
+        <v>782</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A71" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>655</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="F71" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A72" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A73" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="F73" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A71" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F71" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A72" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="F72" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A73" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="B73" s="17" t="s">
-        <v>372</v>
-      </c>
-      <c r="C73" s="17" t="s">
-        <v>373</v>
-      </c>
-      <c r="D73" s="17"/>
-      <c r="E73" s="17"/>
-      <c r="F73" s="21" t="s">
-        <v>291</v>
-      </c>
-      <c r="G73" s="17" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>768</v>
+        <v>602</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>770</v>
-      </c>
-      <c r="F74" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
+        <v>601</v>
+      </c>
+      <c r="F74" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>769</v>
+        <v>681</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>771</v>
+        <v>682</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>683</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>638</v>
+        <v>175</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>639</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>836</v>
-      </c>
-      <c r="F76" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>174</v>
+      </c>
+      <c r="F76" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>179</v>
+        <v>593</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>704</v>
+        <v>594</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>705</v>
-      </c>
-      <c r="F77" s="4" t="s">
-        <v>98</v>
+        <v>721</v>
+      </c>
+      <c r="F77" s="12" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.35">
@@ -4662,78 +4591,75 @@
         <v>43</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>316</v>
+        <v>44</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>317</v>
+        <v>50</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>586</v>
+        <v>45</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="F79" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>51</v>
+      </c>
+      <c r="F79" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>666</v>
+        <v>748</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>667</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>668</v>
-      </c>
-      <c r="F80" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>749</v>
+      </c>
+      <c r="F80" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>173</v>
+        <v>770</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="F81" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G81" s="2" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
+        <v>771</v>
+      </c>
+      <c r="F81" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>577</v>
+        <v>686</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>578</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>706</v>
-      </c>
-      <c r="F82" s="12" t="s">
-        <v>244</v>
+        <v>687</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.35">
@@ -4741,47 +4667,47 @@
         <v>43</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>44</v>
+        <v>671</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>50</v>
+        <v>672</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>203</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>45</v>
+        <v>820</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F84" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G84" s="2" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+        <v>821</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>734</v>
+        <v>160</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>735</v>
-      </c>
-      <c r="F85" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G85" s="2" t="s">
-        <v>736</v>
+        <v>161</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.35">
@@ -4789,151 +4715,151 @@
         <v>43</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>756</v>
+        <v>657</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>757</v>
+        <v>658</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>671</v>
+        <v>46</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>672</v>
-      </c>
-      <c r="F87" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
+        <v>52</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="F87" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>656</v>
+        <v>723</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>657</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>658</v>
-      </c>
-      <c r="E88" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="F88" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
+        <v>724</v>
+      </c>
+      <c r="F88" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>848</v>
+        <v>512</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>849</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>513</v>
+      </c>
+      <c r="F89" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>669</v>
+        <v>783</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>670</v>
-      </c>
-      <c r="F90" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
+        <v>784</v>
+      </c>
+      <c r="F90" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>158</v>
+        <v>725</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="F91" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
+        <v>726</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>758</v>
+      </c>
+      <c r="F91" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>46</v>
+        <v>309</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>707</v>
-      </c>
-      <c r="F93" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>310</v>
+      </c>
+      <c r="F93" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>708</v>
+        <v>737</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>709</v>
-      </c>
-      <c r="F94" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>738</v>
+      </c>
+      <c r="F94" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>498</v>
+        <v>47</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="F95" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="G95" s="2" t="s">
-        <v>500</v>
+        <v>171</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.35">
@@ -4941,44 +4867,50 @@
         <v>43</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>772</v>
+        <v>288</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>773</v>
-      </c>
-      <c r="F96" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+        <v>289</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="F96" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>710</v>
+        <v>169</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>711</v>
+        <v>170</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>744</v>
-      </c>
-      <c r="F97" s="5" t="s">
+        <v>828</v>
+      </c>
+      <c r="F97" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="98" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>630</v>
+        <v>668</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>631</v>
-      </c>
-      <c r="F98" s="5" t="s">
-        <v>99</v>
+        <v>669</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="F98" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.35">
@@ -4986,13 +4918,13 @@
         <v>43</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>297</v>
+        <v>818</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="F99" s="4" t="s">
-        <v>98</v>
+        <v>819</v>
+      </c>
+      <c r="F99" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.35">
@@ -5000,98 +4932,86 @@
         <v>43</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>724</v>
-      </c>
-      <c r="F100" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>728</v>
+      </c>
+      <c r="F100" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>47</v>
+        <v>488</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>169</v>
+        <v>489</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>685</v>
+        <v>701</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>276</v>
+        <v>177</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="D102" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="F102" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>176</v>
+      </c>
+      <c r="F102" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>642</v>
+        <v>762</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>643</v>
-      </c>
-      <c r="D103" s="2" t="s">
-        <v>712</v>
+        <v>764</v>
       </c>
       <c r="F103" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A104" s="2" t="s">
-        <v>43</v>
-      </c>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B104" s="2" t="s">
-        <v>167</v>
+        <v>763</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="D104" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="F104" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
+        <v>765</v>
+      </c>
+      <c r="F104" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A105" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>653</v>
+        <v>710</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>654</v>
-      </c>
-      <c r="D105" s="2" t="s">
-        <v>655</v>
+        <v>711</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.35">
@@ -5099,27 +5019,27 @@
         <v>43</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>774</v>
+        <v>729</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>775</v>
-      </c>
-      <c r="F106" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
+        <v>730</v>
+      </c>
+      <c r="F106" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A107" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>850</v>
+        <v>591</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>851</v>
-      </c>
-      <c r="F107" s="3" t="s">
-        <v>97</v>
+        <v>592</v>
+      </c>
+      <c r="F107" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.35">
@@ -5127,12 +5047,12 @@
         <v>43</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>713</v>
+        <v>604</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>714</v>
-      </c>
-      <c r="F108" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F108" s="3" t="s">
         <v>99</v>
       </c>
     </row>
@@ -5141,33 +5061,27 @@
         <v>43</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>476</v>
+        <v>746</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="D109" s="2" t="s">
-        <v>686</v>
+        <v>747</v>
       </c>
       <c r="F109" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>175</v>
+        <v>595</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="F110" s="6" t="s">
+        <v>596</v>
+      </c>
+      <c r="F110" s="4" t="s">
         <v>100</v>
-      </c>
-      <c r="G110" s="2" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.35">
@@ -5175,94 +5089,109 @@
         <v>43</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>748</v>
+        <v>659</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>750</v>
-      </c>
-      <c r="F111" s="5" t="s">
+        <v>660</v>
+      </c>
+      <c r="F111" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A112" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F112" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B112" s="2" t="s">
-        <v>749</v>
-      </c>
-      <c r="C112" s="2" t="s">
-        <v>751</v>
-      </c>
-      <c r="F112" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>695</v>
+        <v>196</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>696</v>
+        <v>208</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>715</v>
+        <v>49</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>716</v>
-      </c>
-      <c r="F114" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>54</v>
+      </c>
+      <c r="F114" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G114" s="2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A115" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>575</v>
+        <v>751</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="F115" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
+        <v>752</v>
+      </c>
+      <c r="F115" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G115" s="2" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>588</v>
+        <v>744</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>589</v>
-      </c>
-      <c r="F116" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
+        <v>745</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>759</v>
+      </c>
+      <c r="F116" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A117" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>732</v>
+        <v>666</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>733</v>
-      </c>
-      <c r="F117" s="3" t="s">
-        <v>97</v>
+        <v>667</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="F117" s="14" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.35">
@@ -5270,106 +5199,106 @@
         <v>43</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>579</v>
+        <v>186</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>580</v>
+        <v>187</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A119" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>644</v>
+        <v>578</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>645</v>
+        <v>579</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>48</v>
+        <v>203</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F120" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
+        <v>204</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="F120" s="5" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A121" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>194</v>
+        <v>678</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="F121" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>679</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>680</v>
+      </c>
+      <c r="F121" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>49</v>
+        <v>599</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F122" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="G122" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7" ht="58" x14ac:dyDescent="0.35">
-      <c r="A123" s="2" t="s">
-        <v>43</v>
-      </c>
+        <v>600</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="F122" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="B123" s="2" t="s">
-        <v>737</v>
+        <v>664</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>738</v>
-      </c>
-      <c r="F123" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="G123" s="2" t="s">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>665</v>
+      </c>
+      <c r="F123" s="14" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A124" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>730</v>
+        <v>451</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>731</v>
+        <v>452</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>745</v>
-      </c>
-      <c r="F124" s="5" t="s">
-        <v>99</v>
+        <v>453</v>
+      </c>
+      <c r="F124" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="125" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5377,30 +5306,27 @@
         <v>43</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>651</v>
+        <v>676</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>652</v>
-      </c>
-      <c r="D125" s="2" t="s">
-        <v>717</v>
+        <v>677</v>
       </c>
       <c r="F125" s="14" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A126" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>184</v>
+        <v>650</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>185</v>
+        <v>651</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="127" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5408,13 +5334,13 @@
         <v>43</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>562</v>
+        <v>652</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>563</v>
+        <v>653</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="128" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5422,32 +5348,26 @@
         <v>43</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>199</v>
+        <v>573</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="D128" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="F128" s="5" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>574</v>
+      </c>
+      <c r="F128" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>663</v>
+        <v>648</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>664</v>
-      </c>
-      <c r="D129" s="2" t="s">
-        <v>665</v>
-      </c>
-      <c r="F129" s="5" t="s">
+        <v>649</v>
+      </c>
+      <c r="F129" s="3" t="s">
         <v>99</v>
       </c>
     </row>
@@ -5456,44 +5376,47 @@
         <v>43</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>583</v>
+        <v>597</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>584</v>
-      </c>
-      <c r="D130" s="2" t="s">
-        <v>587</v>
+        <v>598</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>595</v>
       </c>
       <c r="F130" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="131" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A131" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="B131" s="2" t="s">
-        <v>649</v>
+        <v>732</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="F131" s="14" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>733</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="F131" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A132" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>439</v>
+        <v>816</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="D132" s="2" t="s">
-        <v>441</v>
+        <v>817</v>
       </c>
       <c r="F132" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="133" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5501,273 +5424,273 @@
         <v>43</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>661</v>
+        <v>703</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>662</v>
-      </c>
-      <c r="F133" s="14" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>704</v>
+      </c>
+      <c r="F133" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>634</v>
+        <v>833</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="F134" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A135" s="2" t="s">
+        <v>834</v>
+      </c>
+      <c r="F134" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A135" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="B135" s="2" t="s">
-        <v>636</v>
-      </c>
-      <c r="C135" s="2" t="s">
-        <v>637</v>
-      </c>
-      <c r="F135" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="B135" s="17" t="s">
+        <v>347</v>
+      </c>
+      <c r="C135" s="17" t="s">
+        <v>348</v>
+      </c>
+      <c r="D135" s="17" t="s">
+        <v>349</v>
+      </c>
+      <c r="E135" s="17"/>
+      <c r="F135" s="21" t="s">
+        <v>303</v>
+      </c>
+      <c r="G135" s="17" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136" s="2" t="s">
-        <v>43</v>
+        <v>275</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>557</v>
+        <v>269</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>558</v>
+        <v>270</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>702</v>
       </c>
       <c r="F136" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A137" s="2" t="s">
-        <v>43</v>
+        <v>275</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>632</v>
+        <v>273</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>633</v>
-      </c>
-      <c r="F137" s="3" t="s">
-        <v>97</v>
+        <v>274</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="F137" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138" s="2" t="s">
-        <v>43</v>
+        <v>275</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>581</v>
+        <v>271</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>582</v>
-      </c>
-      <c r="E138" s="2" t="s">
-        <v>579</v>
-      </c>
-      <c r="F138" s="3" t="s">
-        <v>97</v>
+        <v>272</v>
+      </c>
+      <c r="F138" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="139" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A139" s="2" t="s">
-        <v>43</v>
+        <v>275</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>718</v>
+        <v>418</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>719</v>
-      </c>
-      <c r="D139" s="2" t="s">
-        <v>720</v>
-      </c>
-      <c r="F139" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>419</v>
+      </c>
+      <c r="F139" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140" s="2" t="s">
-        <v>43</v>
+        <v>275</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>846</v>
+        <v>183</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>847</v>
+        <v>182</v>
       </c>
       <c r="F140" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141" s="2" t="s">
-        <v>43</v>
+        <v>275</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>688</v>
+        <v>184</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>689</v>
-      </c>
-      <c r="F141" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+        <v>185</v>
+      </c>
+      <c r="F141" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A142" s="17" t="s">
-        <v>43</v>
+        <v>275</v>
       </c>
       <c r="B142" s="17" t="s">
-        <v>334</v>
+        <v>188</v>
       </c>
       <c r="C142" s="17" t="s">
-        <v>335</v>
-      </c>
-      <c r="D142" s="17" t="s">
-        <v>336</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="D142" s="17"/>
       <c r="E142" s="17"/>
-      <c r="F142" s="21" t="s">
-        <v>291</v>
-      </c>
-      <c r="G142" s="17" t="s">
-        <v>337</v>
-      </c>
+      <c r="F142" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="G142" s="17"/>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143" s="2" t="s">
-        <v>269</v>
+        <v>55</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>263</v>
+        <v>470</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="D143" s="2" t="s">
-        <v>687</v>
-      </c>
-      <c r="F143" s="4" t="s">
-        <v>98</v>
+        <v>471</v>
+      </c>
+      <c r="F143" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="144" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A144" s="2" t="s">
-        <v>269</v>
+        <v>55</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>267</v>
+        <v>785</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="D144" s="2" t="s">
-        <v>614</v>
-      </c>
-      <c r="F144" s="4" t="s">
-        <v>98</v>
+        <v>788</v>
+      </c>
+      <c r="F144" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145" s="2" t="s">
-        <v>269</v>
+        <v>55</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>265</v>
+        <v>786</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="F145" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>789</v>
+      </c>
+      <c r="F145" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146" s="2" t="s">
-        <v>269</v>
+        <v>55</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>405</v>
+        <v>787</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>406</v>
+        <v>790</v>
       </c>
       <c r="F146" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147" s="2" t="s">
-        <v>269</v>
+        <v>55</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>181</v>
+        <v>472</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="F147" s="4" t="s">
-        <v>98</v>
+        <v>473</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="F147" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148" s="2" t="s">
-        <v>269</v>
+        <v>55</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>182</v>
+        <v>380</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="F148" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A149" s="17" t="s">
-        <v>269</v>
-      </c>
-      <c r="B149" s="17" t="s">
-        <v>186</v>
-      </c>
-      <c r="C149" s="17" t="s">
-        <v>187</v>
-      </c>
-      <c r="D149" s="17"/>
-      <c r="E149" s="17"/>
-      <c r="F149" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="G149" s="17"/>
+        <v>381</v>
+      </c>
+      <c r="F148" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A149" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D149" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="F149" s="3" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>458</v>
+        <v>313</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="F150" s="3" t="s">
-        <v>97</v>
+        <v>314</v>
+      </c>
+      <c r="F150" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="151" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5778,10 +5701,10 @@
         <v>776</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="F151" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.35">
@@ -5789,13 +5712,13 @@
         <v>55</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>777</v>
+        <v>628</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>780</v>
+        <v>629</v>
       </c>
       <c r="F152" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.35">
@@ -5803,13 +5726,16 @@
         <v>55</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>778</v>
+        <v>525</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>781</v>
+        <v>792</v>
+      </c>
+      <c r="E153" s="2" t="s">
+        <v>526</v>
       </c>
       <c r="F153" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.35">
@@ -5817,16 +5743,13 @@
         <v>55</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>460</v>
+        <v>791</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="D154" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="F154" s="3" t="s">
-        <v>97</v>
+        <v>778</v>
+      </c>
+      <c r="F154" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.35">
@@ -5834,436 +5757,443 @@
         <v>55</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>367</v>
+        <v>542</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>368</v>
+        <v>543</v>
       </c>
       <c r="F155" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="156" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>56</v>
+        <v>606</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D156" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="F156" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.35">
+        <v>607</v>
+      </c>
+      <c r="F156" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A157" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>301</v>
+        <v>57</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="F157" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>60</v>
+      </c>
+      <c r="F157" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G157" s="2" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>765</v>
+        <v>311</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>766</v>
+        <v>312</v>
       </c>
       <c r="F158" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.35">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A159" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>612</v>
+        <v>390</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>613</v>
-      </c>
-      <c r="F159" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.35">
+        <v>393</v>
+      </c>
+      <c r="F159" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G159" s="2" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A160" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>509</v>
+        <v>391</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>783</v>
-      </c>
-      <c r="E160" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="F160" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.35">
+        <v>394</v>
+      </c>
+      <c r="F160" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G160" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A161" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>782</v>
+        <v>392</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>767</v>
-      </c>
-      <c r="F161" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.35">
+        <v>395</v>
+      </c>
+      <c r="F161" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G161" s="2" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A162" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>526</v>
+        <v>58</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>527</v>
+        <v>61</v>
+      </c>
+      <c r="D162" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="F162" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A163" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>590</v>
+        <v>376</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>591</v>
+        <v>340</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>341</v>
       </c>
       <c r="F163" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="164" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A164" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>57</v>
+        <v>388</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F164" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="G164" s="2" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A165" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="F164" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" s="17" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A165" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="B165" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="C165" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="F165" s="5" t="s">
-        <v>99</v>
+      <c r="B165" s="17" t="s">
+        <v>441</v>
+      </c>
+      <c r="C165" s="17" t="s">
+        <v>442</v>
+      </c>
+      <c r="F165" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="G165" s="17" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="166" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A166" s="2" t="s">
-        <v>55</v>
+        <v>404</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>377</v>
+        <v>406</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="F166" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G166" s="2" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="167" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A167" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B167" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="C167" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="F167" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G167" s="2" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="168" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>407</v>
+      </c>
+      <c r="D166" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="F166" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" s="17" customFormat="1" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A167" s="17" t="s">
+        <v>754</v>
+      </c>
+      <c r="B167" s="17" t="s">
+        <v>755</v>
+      </c>
+      <c r="C167" s="17" t="s">
+        <v>756</v>
+      </c>
+      <c r="D167" s="17" t="s">
+        <v>757</v>
+      </c>
+      <c r="F167" s="19" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168" s="2" t="s">
-        <v>55</v>
+        <v>357</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>379</v>
+        <v>359</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="F168" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G168" s="2" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="169" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>366</v>
+      </c>
+      <c r="F168" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169" s="2" t="s">
-        <v>55</v>
+        <v>357</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>58</v>
+        <v>360</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D169" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F169" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="170" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>367</v>
+      </c>
+      <c r="F169" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" s="2" t="s">
-        <v>55</v>
+        <v>357</v>
       </c>
       <c r="B170" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C170" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="F170" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A171" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="C171" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="D171" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="F171" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A172" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B172" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="C170" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="D170" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="F170" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="171" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A171" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B171" s="2" t="s">
+      <c r="C172" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="F172" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A173" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="C173" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="F173" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G173" s="2" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A174" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="C174" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="F174" s="6"/>
+      <c r="G174" s="2" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A175" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="C175" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="F175" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G175" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="C171" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="F171" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="172" spans="1:7" s="17" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A172" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="B172" s="17" t="s">
-        <v>428</v>
-      </c>
-      <c r="C172" s="17" t="s">
-        <v>429</v>
-      </c>
-      <c r="F172" s="22" t="s">
-        <v>140</v>
-      </c>
-      <c r="G172" s="17" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="173" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A173" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="B173" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="C173" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="D173" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="F173" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="174" spans="1:7" s="17" customFormat="1" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A174" s="17" t="s">
-        <v>740</v>
-      </c>
-      <c r="B174" s="17" t="s">
-        <v>741</v>
-      </c>
-      <c r="C174" s="17" t="s">
-        <v>742</v>
-      </c>
-      <c r="D174" s="17" t="s">
-        <v>743</v>
-      </c>
-      <c r="F174" s="19" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A175" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="B175" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="C175" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="F175" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A176" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="B176" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="C176" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="F176" s="4" t="s">
-        <v>98</v>
-      </c>
+    </row>
+    <row r="176" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A176" s="17" t="s">
+        <v>357</v>
+      </c>
+      <c r="B176" s="17" t="s">
+        <v>498</v>
+      </c>
+      <c r="C176" s="17" t="s">
+        <v>499</v>
+      </c>
+      <c r="D176" s="17"/>
+      <c r="E176" s="17"/>
+      <c r="F176" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="G176" s="17"/>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177" s="2" t="s">
-        <v>344</v>
+        <v>63</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>348</v>
+        <v>206</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="F177" s="4" t="s">
-        <v>98</v>
+        <v>207</v>
+      </c>
+      <c r="F177" s="12" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="178" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A178" s="2" t="s">
-        <v>344</v>
+        <v>63</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>349</v>
+        <v>518</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>356</v>
+        <v>519</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="F178" s="4" t="s">
-        <v>98</v>
+        <v>520</v>
+      </c>
+      <c r="F178" s="14" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="179" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A179" s="2" t="s">
-        <v>344</v>
+        <v>63</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>350</v>
+        <v>661</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>357</v>
+        <v>662</v>
+      </c>
+      <c r="D179" s="2" t="s">
+        <v>663</v>
       </c>
       <c r="F179" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.35">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A180" s="2" t="s">
-        <v>344</v>
+        <v>63</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>351</v>
+        <v>197</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="F180" s="6" t="s">
-        <v>140</v>
+        <v>198</v>
+      </c>
+      <c r="E180" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="F180" s="16" t="s">
+        <v>303</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="181" spans="1:7" s="17" customFormat="1" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A181" s="17" t="s">
-        <v>344</v>
-      </c>
-      <c r="B181" s="17" t="s">
-        <v>352</v>
-      </c>
-      <c r="C181" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="F181" s="22" t="s">
-        <v>140</v>
-      </c>
-      <c r="G181" s="17" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.35">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A181" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="C181" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="F181" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A182" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>808</v>
+        <v>64</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>809</v>
-      </c>
-      <c r="D182" s="2" t="s">
-        <v>810</v>
-      </c>
-      <c r="F182" s="5" t="s">
-        <v>99</v>
+        <v>67</v>
+      </c>
+      <c r="F182" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.35">
@@ -6271,13 +6201,13 @@
         <v>63</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>813</v>
+        <v>496</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>814</v>
-      </c>
-      <c r="F183" s="16" t="s">
-        <v>291</v>
+        <v>497</v>
+      </c>
+      <c r="F183" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.35">
@@ -6285,13 +6215,16 @@
         <v>63</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>815</v>
+        <v>65</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>816</v>
+        <v>68</v>
       </c>
       <c r="F184" s="16" t="s">
-        <v>291</v>
+        <v>303</v>
+      </c>
+      <c r="G184" s="2" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.35">
@@ -6299,27 +6232,27 @@
         <v>63</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>822</v>
+        <v>561</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>823</v>
-      </c>
-      <c r="F185" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="186" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>562</v>
+      </c>
+      <c r="F185" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A186" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>825</v>
+        <v>760</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>824</v>
-      </c>
-      <c r="F186" s="3" t="s">
-        <v>97</v>
+        <v>761</v>
+      </c>
+      <c r="F186" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.35">
@@ -6327,50 +6260,44 @@
         <v>63</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>791</v>
+        <v>766</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>793</v>
-      </c>
-      <c r="D187" s="2" t="s">
-        <v>792</v>
-      </c>
-      <c r="F187" s="12" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="188" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>767</v>
+      </c>
+      <c r="F187" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A188" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>502</v>
+        <v>515</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="D188" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="F188" s="14" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="189" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>516</v>
+      </c>
+      <c r="F188" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G188" s="2" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A189" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>646</v>
+        <v>199</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>647</v>
-      </c>
-      <c r="D189" s="2" t="s">
-        <v>648</v>
+        <v>200</v>
       </c>
       <c r="F189" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="190" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6378,72 +6305,78 @@
         <v>63</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>314</v>
+        <v>810</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="F190" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.35">
+        <v>811</v>
+      </c>
+      <c r="D190" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="F190" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G190" s="2" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A191" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>484</v>
+        <v>66</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="F191" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="192" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>69</v>
+      </c>
+      <c r="D191" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="F191" s="14" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A192" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>797</v>
+        <v>190</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>798</v>
+        <v>191</v>
       </c>
       <c r="F192" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.35">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A193" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>64</v>
+        <v>277</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F193" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G193" s="2" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.35">
+        <v>280</v>
+      </c>
+      <c r="F193" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A194" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>799</v>
+        <v>278</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>800</v>
-      </c>
-      <c r="F194" s="14" t="s">
-        <v>252</v>
+        <v>281</v>
+      </c>
+      <c r="F194" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="195" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6451,27 +6384,27 @@
         <v>63</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>805</v>
+        <v>279</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>806</v>
-      </c>
-      <c r="F195" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.35">
+        <v>282</v>
+      </c>
+      <c r="F195" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A196" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>801</v>
+        <v>566</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>802</v>
-      </c>
-      <c r="F196" s="14" t="s">
-        <v>252</v>
+        <v>567</v>
+      </c>
+      <c r="F196" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.35">
@@ -6479,1814 +6412,1611 @@
         <v>63</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>826</v>
+        <v>476</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>827</v>
+        <v>475</v>
       </c>
       <c r="F197" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="198" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A198" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>794</v>
+        <v>492</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>795</v>
-      </c>
-      <c r="D198" s="2" t="s">
-        <v>807</v>
+        <v>493</v>
       </c>
       <c r="F198" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="G198" s="2" t="s">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A199" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A199" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="B199" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="C199" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="F199" s="5" t="s">
-        <v>99</v>
-      </c>
+      <c r="B199" s="17" t="s">
+        <v>494</v>
+      </c>
+      <c r="C199" s="17" t="s">
+        <v>495</v>
+      </c>
+      <c r="D199" s="17"/>
+      <c r="E199" s="17"/>
+      <c r="F199" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="G199" s="17"/>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A200" s="2" t="s">
-        <v>63</v>
+        <v>420</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>746</v>
+        <v>793</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>747</v>
-      </c>
-      <c r="F200" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.35">
+        <v>794</v>
+      </c>
+      <c r="F200" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A201" s="2" t="s">
-        <v>63</v>
+        <v>420</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>752</v>
+        <v>558</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>753</v>
-      </c>
-      <c r="F201" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="202" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>559</v>
+      </c>
+      <c r="D201" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="F201" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A202" s="2" t="s">
-        <v>63</v>
+        <v>420</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>861</v>
+        <v>708</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>862</v>
-      </c>
-      <c r="F202" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="G202" s="2" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="203" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>709</v>
+      </c>
+      <c r="D202" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="F202" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A203" s="2" t="s">
-        <v>63</v>
+        <v>420</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>817</v>
+        <v>428</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>820</v>
-      </c>
-      <c r="D203" s="2" t="s">
-        <v>821</v>
-      </c>
-      <c r="F203" s="4" t="s">
-        <v>98</v>
+        <v>429</v>
+      </c>
+      <c r="F203" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A204" s="2" t="s">
-        <v>63</v>
+        <v>420</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>195</v>
+        <v>430</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="F204" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="205" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>431</v>
+      </c>
+      <c r="F204" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A205" s="2" t="s">
-        <v>63</v>
+        <v>420</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>840</v>
+        <v>401</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>841</v>
-      </c>
-      <c r="D205" s="2" t="s">
-        <v>842</v>
-      </c>
-      <c r="F205" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G205" s="2" t="s">
-        <v>843</v>
-      </c>
-    </row>
-    <row r="206" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>402</v>
+      </c>
+      <c r="F205" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A206" s="2" t="s">
-        <v>63</v>
+        <v>420</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>65</v>
+        <v>432</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D206" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="F206" s="14" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.35">
+        <v>433</v>
+      </c>
+      <c r="F206" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A207" s="2" t="s">
-        <v>63</v>
+        <v>420</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>188</v>
+        <v>612</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="F207" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="208" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>614</v>
+      </c>
+      <c r="D207" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="E207" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="F207" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A208" s="2" t="s">
-        <v>63</v>
+        <v>420</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>550</v>
+        <v>434</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>551</v>
-      </c>
-      <c r="F208" s="5" t="s">
+        <v>435</v>
+      </c>
+      <c r="F208" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="209" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A209" s="2" t="s">
-        <v>63</v>
+        <v>420</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>811</v>
+        <v>422</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>812</v>
-      </c>
-      <c r="F209" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.35">
+        <v>424</v>
+      </c>
+      <c r="F209" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A210" s="2" t="s">
-        <v>63</v>
+        <v>420</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>464</v>
+        <v>529</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="F210" s="4" t="s">
-        <v>98</v>
+        <v>530</v>
+      </c>
+      <c r="F210" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G210" s="2" t="s">
+        <v>531</v>
       </c>
     </row>
     <row r="211" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A211" s="2" t="s">
-        <v>63</v>
+        <v>420</v>
       </c>
       <c r="B211" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="C211" s="2" t="s">
         <v>480</v>
       </c>
-      <c r="C211" s="2" t="s">
+      <c r="D211" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="F211" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="212" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="F211" s="3"/>
+    </row>
+    <row r="212" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A212" s="2" t="s">
-        <v>63</v>
+        <v>420</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>818</v>
+        <v>527</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>819</v>
-      </c>
-      <c r="F212" s="5" t="s">
+        <v>528</v>
+      </c>
+      <c r="F212" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G212" s="2" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A213" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="B213" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="C213" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="E213" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="F213" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="213" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A213" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B213" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="C213" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="F213" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="214" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A214" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="B214" s="17" t="s">
-        <v>828</v>
-      </c>
-      <c r="C214" s="17" t="s">
-        <v>829</v>
-      </c>
-      <c r="D214" s="17"/>
-      <c r="E214" s="17"/>
-      <c r="F214" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="G214" s="17"/>
+    <row r="214" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A214" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="B214" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="C214" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="F214" s="5" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A215" s="2" t="s">
-        <v>407</v>
+        <v>420</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>784</v>
+        <v>466</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>785</v>
-      </c>
-      <c r="F215" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="216" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>467</v>
+      </c>
+      <c r="F215" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A216" s="2" t="s">
-        <v>407</v>
+        <v>420</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>542</v>
+        <v>423</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="D216" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="F216" s="3" t="s">
-        <v>97</v>
+        <v>425</v>
+      </c>
+      <c r="F216" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A217" s="2" t="s">
-        <v>407</v>
+        <v>420</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>693</v>
+        <v>468</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>694</v>
-      </c>
-      <c r="D217" s="2" t="s">
-        <v>692</v>
-      </c>
-      <c r="F217" s="3" t="s">
-        <v>97</v>
+        <v>469</v>
+      </c>
+      <c r="F217" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A218" s="2" t="s">
-        <v>407</v>
+        <v>420</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>415</v>
+        <v>540</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>416</v>
+        <v>541</v>
       </c>
       <c r="F218" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A219" s="2" t="s">
-        <v>407</v>
+        <v>420</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="F219" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.35">
+        <v>427</v>
+      </c>
+      <c r="F219" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G219" s="2" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A220" s="2" t="s">
-        <v>407</v>
+        <v>420</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>388</v>
+        <v>568</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="F220" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A221" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="B221" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="C221" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="F220" s="19" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A221" s="17" t="s">
         <v>420</v>
       </c>
-      <c r="F221" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="222" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="B221" s="17" t="s">
+        <v>490</v>
+      </c>
+      <c r="C221" s="17" t="s">
+        <v>491</v>
+      </c>
+      <c r="D221" s="17"/>
+      <c r="E221" s="17"/>
+      <c r="F221" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="G221" s="17"/>
+    </row>
+    <row r="222" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A222" s="2" t="s">
-        <v>407</v>
+        <v>93</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>596</v>
+        <v>209</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>598</v>
-      </c>
-      <c r="D222" s="2" t="s">
-        <v>597</v>
-      </c>
-      <c r="E222" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="F222" s="3" t="s">
-        <v>97</v>
+        <v>210</v>
+      </c>
+      <c r="F222" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A223" s="2" t="s">
-        <v>407</v>
+        <v>93</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>421</v>
+        <v>304</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="F223" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.35">
+        <v>305</v>
+      </c>
+      <c r="E223" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F223" s="12" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A224" s="2" t="s">
-        <v>407</v>
+        <v>93</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>409</v>
+        <v>211</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="F224" s="3" t="s">
-        <v>97</v>
+        <v>212</v>
+      </c>
+      <c r="F224" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="225" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A225" s="2" t="s">
-        <v>407</v>
+        <v>93</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>513</v>
+        <v>213</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>514</v>
+        <v>214</v>
       </c>
       <c r="F225" s="16" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="G225" s="2" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="226" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A226" s="2" t="s">
-        <v>407</v>
+        <v>93</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>467</v>
+        <v>215</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="D226" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="F226" s="3"/>
+        <v>220</v>
+      </c>
+      <c r="F226" s="5" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A227" s="2" t="s">
-        <v>407</v>
+        <v>93</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>511</v>
+        <v>94</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="F227" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="G227" s="2" t="s">
-        <v>516</v>
+        <v>97</v>
+      </c>
+      <c r="F227" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A228" s="2" t="s">
-        <v>407</v>
+        <v>93</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>488</v>
+        <v>216</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="E228" s="2" t="s">
-        <v>409</v>
+        <v>217</v>
       </c>
       <c r="F228" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A229" s="2" t="s">
-        <v>407</v>
+        <v>93</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>486</v>
+        <v>218</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="F229" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A230" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="B230" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="C230" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="F230" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.35">
+        <v>219</v>
+      </c>
+      <c r="F229" s="12" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A230" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="B230" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="C230" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="D230" s="17"/>
+      <c r="E230" s="17"/>
+      <c r="F230" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="G230" s="17"/>
+    </row>
+    <row r="231" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A231" s="2" t="s">
-        <v>407</v>
+        <v>70</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>410</v>
+        <v>71</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="F231" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.35">
+        <v>72</v>
+      </c>
+      <c r="F231" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G231" s="2" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A232" s="2" t="s">
-        <v>407</v>
+        <v>70</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>456</v>
+        <v>192</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="F232" s="5" t="s">
-        <v>99</v>
+        <v>194</v>
+      </c>
+      <c r="F232" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G232" s="2" t="s">
+        <v>546</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A233" s="2" t="s">
-        <v>407</v>
+        <v>70</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>524</v>
+        <v>741</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="F233" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="234" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A234" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="B234" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="C234" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="F234" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G234" s="2" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="235" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>742</v>
+      </c>
+      <c r="F233" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G233" s="2" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A234" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="B234" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="C234" s="17" t="s">
+        <v>195</v>
+      </c>
+      <c r="D234" s="17"/>
+      <c r="E234" s="17"/>
+      <c r="F234" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="G234" s="17" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A235" s="2" t="s">
-        <v>407</v>
+        <v>73</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>552</v>
+        <v>631</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="F235" s="19" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="236" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A236" s="17" t="s">
-        <v>407</v>
-      </c>
-      <c r="B236" s="17" t="s">
-        <v>478</v>
-      </c>
-      <c r="C236" s="17" t="s">
-        <v>479</v>
-      </c>
-      <c r="D236" s="17"/>
-      <c r="E236" s="17"/>
-      <c r="F236" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="G236" s="17"/>
+        <v>632</v>
+      </c>
+      <c r="F235" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A236" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B236" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C236" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="F236" s="5" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A237" s="2" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>203</v>
+        <v>74</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="F237" s="5" t="s">
-        <v>99</v>
+        <v>82</v>
+      </c>
+      <c r="F237" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A238" s="2" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>292</v>
+        <v>75</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="E238" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="F238" s="12" t="s">
-        <v>244</v>
+        <v>83</v>
+      </c>
+      <c r="F238" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="239" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A239" s="2" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>205</v>
+        <v>553</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>206</v>
+        <v>554</v>
       </c>
       <c r="F239" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A240" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B240" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="C240" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="F240" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A241" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B241" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="C241" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="F241" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A242" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B242" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="C242" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="F242" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A243" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B243" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C243" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="F243" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="240" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A240" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B240" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="C240" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="F240" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G240" s="2" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A241" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B241" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="C241" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="F241" s="5" t="s">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A244" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B244" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="C244" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="F244" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A242" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B242" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C242" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="F242" s="5" t="s">
+    <row r="245" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A245" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B245" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="C245" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="E245" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="F245" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A246" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B246" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="C246" s="2" t="s">
+        <v>796</v>
+      </c>
+      <c r="F246" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A243" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B243" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="C243" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="F243" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="244" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A244" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B244" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="C244" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="F244" s="12" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="245" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A245" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="B245" s="17" t="s">
-        <v>93</v>
-      </c>
-      <c r="C245" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="D245" s="17"/>
-      <c r="E245" s="17"/>
-      <c r="F245" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="G245" s="17"/>
-    </row>
-    <row r="246" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A246" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B246" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C246" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F246" s="6" t="s">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A247" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B247" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="C247" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="F247" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A248" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B248" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="C248" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="F248" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A249" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B249" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C249" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="F249" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A250" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B250" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C250" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="F250" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A251" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B251" s="2" t="s">
+        <v>829</v>
+      </c>
+      <c r="C251" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="F251" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="G246" s="2" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="247" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A247" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B247" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="C247" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="F247" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="G247" s="2" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A248" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B248" s="2" t="s">
-        <v>727</v>
-      </c>
-      <c r="C248" s="2" t="s">
-        <v>728</v>
-      </c>
-      <c r="F248" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="G248" s="2" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="249" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A249" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="B249" s="17" t="s">
-        <v>191</v>
-      </c>
-      <c r="C249" s="17" t="s">
-        <v>193</v>
-      </c>
-      <c r="D249" s="17"/>
-      <c r="E249" s="17"/>
-      <c r="F249" s="22" t="s">
-        <v>140</v>
-      </c>
-      <c r="G249" s="17" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A250" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B250" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="C250" s="2" t="s">
-        <v>616</v>
-      </c>
-      <c r="F250" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A251" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B251" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="C251" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="F251" s="5" t="s">
+    </row>
+    <row r="252" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A252" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B252" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="C252" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="D252" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="F252" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A253" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B253" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="C253" s="2" t="s">
+        <v>832</v>
+      </c>
+      <c r="F253" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A254" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B254" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="C254" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="F254" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A255" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B255" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="C255" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="F255" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A252" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B252" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C252" s="2" t="s">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A256" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B256" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="C256" s="2" t="s">
+        <v>706</v>
+      </c>
+      <c r="F256" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A257" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B257" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="C257" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="F257" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A258" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B258" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="C258" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="F258" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A259" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B259" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="C259" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="F259" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A260" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B260" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C260" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="F260" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A261" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B261" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C261" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="F261" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="G261" s="2" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="262" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A262" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B262" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C262" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F262" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A263" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B263" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C263" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F263" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="264" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A264" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B264" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C264" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F264" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A265" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B265" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C265" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F265" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A266" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B266" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="C266" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="D266" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="F266" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A267" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B267" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="C267" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="F267" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A268" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B268" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="C268" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="F268" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A269" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B269" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="C269" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="F269" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A270" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B270" s="2" t="s">
+        <v>735</v>
+      </c>
+      <c r="C270" s="2" t="s">
+        <v>736</v>
+      </c>
+      <c r="F270" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="271" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A271" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B271" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F252" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A253" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B253" s="2" t="s">
+      <c r="C271" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F271" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A272" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C253" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F253" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="254" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A254" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B254" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="C254" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="F254" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A255" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B255" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="C255" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="F255" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A256" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B256" s="2" t="s">
-        <v>659</v>
-      </c>
-      <c r="C256" s="2" t="s">
-        <v>660</v>
-      </c>
-      <c r="F256" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A257" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B257" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="C257" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="F257" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A258" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B258" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="C258" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="F258" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A259" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B259" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="C259" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="F259" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="260" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A260" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B260" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="C260" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="E260" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="F260" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A261" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B261" s="2" t="s">
-        <v>786</v>
-      </c>
-      <c r="C261" s="2" t="s">
-        <v>787</v>
-      </c>
-      <c r="F261" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A262" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B262" s="2" t="s">
-        <v>601</v>
-      </c>
-      <c r="C262" s="2" t="s">
-        <v>602</v>
-      </c>
-      <c r="F262" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A263" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B263" s="2" t="s">
-        <v>603</v>
-      </c>
-      <c r="C263" s="2" t="s">
-        <v>604</v>
-      </c>
-      <c r="F263" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A264" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B264" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="C264" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="F264" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A265" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B265" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="C265" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="F265" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A266" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B266" s="2" t="s">
-        <v>617</v>
-      </c>
-      <c r="C266" s="2" t="s">
-        <v>618</v>
-      </c>
-      <c r="D266" s="2" t="s">
-        <v>619</v>
-      </c>
-      <c r="F266" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A267" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B267" s="2" t="s">
-        <v>605</v>
-      </c>
-      <c r="C267" s="2" t="s">
-        <v>606</v>
-      </c>
-      <c r="F267" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A268" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B268" s="2" t="s">
-        <v>844</v>
-      </c>
-      <c r="C268" s="2" t="s">
-        <v>845</v>
-      </c>
-      <c r="F268" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A269" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B269" s="2" t="s">
-        <v>690</v>
-      </c>
-      <c r="C269" s="2" t="s">
-        <v>691</v>
-      </c>
-      <c r="F269" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A270" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B270" s="2" t="s">
-        <v>620</v>
-      </c>
-      <c r="C270" s="2" t="s">
-        <v>621</v>
-      </c>
-      <c r="F270" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A271" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B271" s="2" t="s">
-        <v>592</v>
-      </c>
-      <c r="C271" s="2" t="s">
-        <v>593</v>
-      </c>
-      <c r="F271" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A272" s="2" t="s">
-        <v>71</v>
-      </c>
       <c r="B272" s="2" t="s">
-        <v>572</v>
+        <v>547</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>573</v>
-      </c>
-      <c r="F272" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.35">
+        <v>548</v>
+      </c>
+      <c r="F272" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A273" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>235</v>
+        <v>293</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="F273" s="4" t="s">
-        <v>98</v>
+        <v>294</v>
+      </c>
+      <c r="F273" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G273" s="2" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="274" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A274" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>273</v>
+        <v>295</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="F274" s="6" t="s">
-        <v>275</v>
+        <v>296</v>
+      </c>
+      <c r="F274" s="16" t="s">
+        <v>303</v>
       </c>
       <c r="G274" s="2" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.35">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A275" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>74</v>
+        <v>239</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F275" s="5" t="s">
-        <v>99</v>
+        <v>240</v>
+      </c>
+      <c r="F275" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G275" s="2" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A276" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>75</v>
+        <v>230</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="F276" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.35">
+        <v>231</v>
+      </c>
+      <c r="E276" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F276" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A277" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>76</v>
+        <v>688</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>84</v>
+        <v>689</v>
       </c>
       <c r="F277" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.35">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A278" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F278" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A279" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>607</v>
+        <v>739</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>608</v>
-      </c>
-      <c r="D279" s="2" t="s">
-        <v>609</v>
-      </c>
-      <c r="F279" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.35">
+        <v>740</v>
+      </c>
+      <c r="F279" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A280" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="F280" s="4" t="s">
-        <v>98</v>
+        <v>444</v>
+      </c>
+      <c r="F280" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G280" s="2" t="s">
+        <v>377</v>
       </c>
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A281" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>465</v>
+        <v>640</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="F281" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="282" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>641</v>
+      </c>
+      <c r="F281" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A282" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>622</v>
+        <v>506</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>623</v>
+        <v>507</v>
       </c>
       <c r="F282" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.35">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A283" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>721</v>
+        <v>772</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>722</v>
-      </c>
-      <c r="F283" s="3" t="s">
-        <v>97</v>
+        <v>773</v>
+      </c>
+      <c r="F283" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G283" s="2" t="s">
+        <v>774</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A284" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>78</v>
+        <v>245</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F284" s="3" t="s">
-        <v>97</v>
+        <v>246</v>
+      </c>
+      <c r="F284" s="14" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A285" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>531</v>
+        <v>298</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>532</v>
+        <v>297</v>
       </c>
       <c r="F285" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="286" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A286" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>281</v>
+        <v>642</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="F286" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G286" s="2" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="287" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>643</v>
+      </c>
+      <c r="F286" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A287" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>283</v>
+        <v>234</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="F287" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G287" s="2" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="288" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>235</v>
+      </c>
+      <c r="F287" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="288" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A288" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>233</v>
+        <v>626</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="F288" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G288" s="2" t="s">
-        <v>323</v>
+        <v>627</v>
+      </c>
+      <c r="F288" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A289" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="E289" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="F289" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="290" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>227</v>
+      </c>
+      <c r="F289" s="12" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="290" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A290" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>673</v>
+        <v>523</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>674</v>
-      </c>
-      <c r="F290" s="5" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="291" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>524</v>
+      </c>
+      <c r="F290" s="14" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="291" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A291" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>79</v>
+        <v>521</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="F291" s="4" t="s">
-        <v>98</v>
+        <v>522</v>
+      </c>
+      <c r="E291" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="F291" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A292" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>725</v>
+        <v>224</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>726</v>
-      </c>
-      <c r="F292" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="293" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>225</v>
+      </c>
+      <c r="F292" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="293" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A293" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>430</v>
+        <v>644</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="F293" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="G293" s="2" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.35">
+        <v>645</v>
+      </c>
+      <c r="F293" s="20" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="294" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A294" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>624</v>
+        <v>583</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>625</v>
-      </c>
-      <c r="F294" s="5" t="s">
+        <v>585</v>
+      </c>
+      <c r="F294" s="3" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G294" s="2" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="295" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A295" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>492</v>
+        <v>584</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="F295" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="296" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A296" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B296" s="2" t="s">
-        <v>758</v>
-      </c>
-      <c r="C296" s="2" t="s">
-        <v>759</v>
-      </c>
-      <c r="F296" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G296" s="2" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.35">
+        <v>587</v>
+      </c>
+      <c r="F295" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G295" s="2" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="296" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A296" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="B296" s="17" t="s">
+        <v>306</v>
+      </c>
+      <c r="C296" s="17" t="s">
+        <v>307</v>
+      </c>
+      <c r="D296" s="17"/>
+      <c r="E296" s="17"/>
+      <c r="F296" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="G296" s="17"/>
+    </row>
+    <row r="297" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A297" s="2" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>239</v>
+        <v>91</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="F297" s="14" t="s">
-        <v>252</v>
+        <v>92</v>
+      </c>
+      <c r="D297" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="F297" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A298" s="2" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>286</v>
+        <v>222</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>285</v>
+        <v>221</v>
+      </c>
+      <c r="D298" s="2" t="s">
+        <v>403</v>
       </c>
       <c r="F298" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.35">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="299" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A299" s="2" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>626</v>
+        <v>247</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>627</v>
-      </c>
-      <c r="F299" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.35">
+        <v>248</v>
+      </c>
+      <c r="D299" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="F299" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="300" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A300" s="2" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>228</v>
+        <v>797</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="F300" s="5" t="s">
-        <v>99</v>
+        <v>798</v>
+      </c>
+      <c r="F300" s="25" t="s">
+        <v>799</v>
       </c>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A301" s="2" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>610</v>
+        <v>351</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>611</v>
-      </c>
-      <c r="F301" s="5" t="s">
-        <v>99</v>
+        <v>352</v>
+      </c>
+      <c r="F301" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A302" s="2" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>220</v>
+        <v>563</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="F302" s="12" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A303" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B303" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="C303" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="F303" s="14" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A304" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B304" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="C304" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="E304" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="F304" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A305" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B305" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="C305" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="F305" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="306" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A306" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B306" s="2" t="s">
-        <v>628</v>
-      </c>
-      <c r="C306" s="2" t="s">
-        <v>629</v>
-      </c>
-      <c r="F306" s="20" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="307" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A307" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B307" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="C307" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="F307" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="G307" s="2" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="308" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A308" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B308" s="2" t="s">
-        <v>568</v>
-      </c>
-      <c r="C308" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="F308" s="16" t="s">
+        <v>564</v>
+      </c>
+      <c r="D302" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="F302" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="303" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A303" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="B303" s="17" t="s">
         <v>291</v>
       </c>
-      <c r="G308" s="2" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="309" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A309" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="B309" s="17" t="s">
-        <v>294</v>
-      </c>
-      <c r="C309" s="17" t="s">
-        <v>295</v>
-      </c>
-      <c r="D309" s="17"/>
-      <c r="E309" s="17"/>
-      <c r="F309" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="G309" s="17"/>
-    </row>
-    <row r="310" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A310" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B310" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C310" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D310" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="F310" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="311" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A311" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B311" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="C311" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="D311" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="F311" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="312" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A312" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B312" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="C312" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="D312" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="F312" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="313" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A313" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B313" s="2" t="s">
-        <v>788</v>
-      </c>
-      <c r="C313" s="2" t="s">
-        <v>789</v>
-      </c>
-      <c r="F313" s="25" t="s">
-        <v>790</v>
-      </c>
-    </row>
-    <row r="314" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A314" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B314" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="C314" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="F314" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="315" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A315" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B315" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="C315" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="D315" s="2" t="s">
-        <v>549</v>
-      </c>
-      <c r="F315" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="316" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A316" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="B316" s="17" t="s">
-        <v>279</v>
-      </c>
-      <c r="C316" s="17" t="s">
-        <v>280</v>
-      </c>
-      <c r="D316" s="17" t="s">
-        <v>296</v>
-      </c>
-      <c r="E316" s="17"/>
-      <c r="F316" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="G316" s="17"/>
+      <c r="C303" s="17" t="s">
+        <v>292</v>
+      </c>
+      <c r="D303" s="17" t="s">
+        <v>308</v>
+      </c>
+      <c r="E303" s="17"/>
+      <c r="F303" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="G303" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8308,7 +8038,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
@@ -8316,7 +8046,7 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -8324,7 +8054,7 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -8332,31 +8062,31 @@
         <v>36</v>
       </c>
       <c r="B4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B5" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>400</v>
+        <v>413</v>
       </c>
       <c r="B6" t="s">
-        <v>401</v>
+        <v>414</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>472</v>
+        <v>484</v>
       </c>
       <c r="B7" t="s">
-        <v>473</v>
+        <v>485</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
@@ -8364,7 +8094,7 @@
         <v>38</v>
       </c>
       <c r="B8" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
@@ -8372,15 +8102,15 @@
         <v>43</v>
       </c>
       <c r="B9" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="B10" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
@@ -8388,23 +8118,23 @@
         <v>55</v>
       </c>
       <c r="B11" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>391</v>
+        <v>404</v>
       </c>
       <c r="B12" t="s">
-        <v>392</v>
+        <v>405</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>344</v>
+        <v>357</v>
       </c>
       <c r="B13" t="s">
-        <v>345</v>
+        <v>358</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
@@ -8412,47 +8142,47 @@
         <v>63</v>
       </c>
       <c r="B14" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>407</v>
+        <v>420</v>
       </c>
       <c r="B15" t="s">
-        <v>408</v>
+        <v>421</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B16" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B17" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B18" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B19" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
